--- a/MAX-SEAL-main/catalog/MAXSEAL_CATALOG.xlsx
+++ b/MAX-SEAL-main/catalog/MAXSEAL_CATALOG.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2684" uniqueCount="1059">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2714" uniqueCount="1147">
   <si>
     <t>Id</t>
   </si>
@@ -2094,157 +2094,421 @@
     <t>IndustryId</t>
   </si>
   <si>
+    <t>BestApplications</t>
+  </si>
+  <si>
+    <t>WhyItFits</t>
+  </si>
+  <si>
     <t>1</t>
   </si>
   <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>2</t>
   </si>
   <si>
-    <t>3</t>
+    <t>General chemical processing, corrosive liquids and automated chemical-transfer</t>
+  </si>
+  <si>
+    <t>Wafer or lug designs, low torque, epoxy-coated body and optional stainless</t>
+  </si>
+  <si>
+    <t>Chemical-process isolation requiring multiple seat options</t>
+  </si>
+  <si>
+    <t>BUNA, EPDM, Viton and PTFE seats allow configuration for different</t>
+  </si>
+  <si>
+    <t>Higher-pressure or higher-temperature chemical and petrochemical service</t>
+  </si>
+  <si>
+    <t>Soft-seat, metal-seat and fire-safe configurations with multiple ANSI classes.</t>
+  </si>
+  <si>
+    <t>Severe corrosion, high temperature and critical chemical isolation</t>
+  </si>
+  <si>
+    <t>Double- and triple-offset designs with broad special-alloy availability.</t>
+  </si>
+  <si>
+    <t>Cooling water, utility water, air and compatible low-pressure chemicals</t>
+  </si>
+  <si>
+    <t>Economical, low-torque automated butterfly valve for noncritical service.</t>
+  </si>
+  <si>
+    <t>Steam, condensate, feedwater, fuel gas and higher-pressure utility systems</t>
+  </si>
+  <si>
+    <t>Soft-seat, metal-seat and fire-safe options; available through ANSI Class 900.</t>
+  </si>
+  <si>
+    <t>Steam isolation, turbine auxiliaries and automated critical shutoff</t>
+  </si>
+  <si>
+    <t>Double-offset operation reduces seat wear and supports frequent cycling.</t>
+  </si>
+  <si>
+    <t>Main steam, hot reheat, extraction steam and other high-temperature systems</t>
+  </si>
+  <si>
+    <t>Metal-seated severe-service design with large sizes and special-alloy options.</t>
+  </si>
+  <si>
+    <t>Cooling water, circulating water, firewater and general utility water</t>
+  </si>
+  <si>
+    <t>Economical, low-torque butterfly valve for large, lower-pressure water lines.</t>
+  </si>
+  <si>
+    <t>Water treatment, chemical feed and compatible corrosive fluids</t>
+  </si>
+  <si>
+    <t>Multiple body, disc and seat options for chemical compatibility.</t>
+  </si>
+  <si>
+    <t>Mill water, cooling water, white water, firewater and general utilities</t>
+  </si>
+  <si>
+    <t>Economical large-line isolation with low operating torque.</t>
+  </si>
+  <si>
+    <t>Process water, stock-preparation utilities and general mill service</t>
+  </si>
+  <si>
+    <t>Practical resilient-seated butterfly valve for moderate pressure and</t>
+  </si>
+  <si>
+    <t>Steam, condensate, chemical recovery and higher-pressure process systems</t>
+  </si>
+  <si>
+    <t>Soft-seat, metal-seat and fire-safe configurations are available.</t>
+  </si>
+  <si>
+    <t>Higher-temperature isolation and frequently cycled automated service</t>
+  </si>
+  <si>
+    <t>Double-offset operation reduces seat wear and operating torque.</t>
+  </si>
+  <si>
+    <t>High-temperature steam, recovery-boiler systems and severe chemical service</t>
+  </si>
+  <si>
+    <t>Metal-seated design with special-alloy options for demanding applications.</t>
+  </si>
+  <si>
+    <t>Bleaching chemicals, chemical feed and compatible corrosive liquids</t>
+  </si>
+  <si>
+    <t>Multiple body, disc and seat materials support chemical-specific selection.</t>
+  </si>
+  <si>
+    <t>Raw water, process water, cooling water, firewater and dewatering systems</t>
+  </si>
+  <si>
+    <t>Cost-effective large-diameter isolation with low operating torque.</t>
+  </si>
+  <si>
+    <t>General plant water, air and compatible low-pressure process fluids</t>
+  </si>
+  <si>
+    <t>Economical resilient-seated butterfly-valve solution.</t>
+  </si>
+  <si>
+    <t>Higher-pressure process water, corrosive service and elevated-temperature</t>
+  </si>
+  <si>
+    <t>Soft-, metal-seated and special-material configurations are available.</t>
+  </si>
+  <si>
+    <t>High-pressure leach, corrosive processing and severe-temperature service</t>
+  </si>
+  <si>
+    <t>Double- and triple-offset designs with an extensive selection of special alloys.</t>
+  </si>
+  <si>
+    <t>Reagents, acids and compatible mineral-processing chemicals</t>
+  </si>
+  <si>
+    <t>Multiple disc and seat combinations allow chemical-specific selection.</t>
+  </si>
+  <si>
+    <t>Seawater cooling, ballast water, bilge water, fire mains and general water service</t>
+  </si>
+  <si>
+    <t>Compact wafer/lug design, low operating torque and easy automation.</t>
+  </si>
+  <si>
+    <t>Shipboard water, HVAC, cooling and utility systems</t>
+  </si>
+  <si>
+    <t>Economical resilient-seated butterfly valve for moderate service.</t>
+  </si>
+  <si>
+    <t>Fuel oil, steam, condensate, cargo systems and higher-pressure utilities</t>
+  </si>
+  <si>
+    <t>Soft-, metal-seated and fire-safe configurations; Classes 150–900.</t>
+  </si>
+  <si>
+    <t>Frequently cycled cargo, fuel, steam and automated isolation systems</t>
+  </si>
+  <si>
+    <t>Double-offset design reduces seat wear and operating torque.</t>
+  </si>
+  <si>
+    <t>Seawater, exhaust, steam and severe offshore service</t>
+  </si>
+  <si>
+    <t>Double- and triple-offset construction with corrosion-resistant alloy options.</t>
+  </si>
+  <si>
+    <t>Chilled water, condenser water, cooling towers and hot-water circulation</t>
+  </si>
+  <si>
+    <t>Low operating torque, high flow capacity and ISO 5211 direct mounting.</t>
+  </si>
+  <si>
+    <t>General commercial and industrial HVAC water systems</t>
+  </si>
+  <si>
+    <t>Economical resilient-seated butterfly valve for standard water service.</t>
+  </si>
+  <si>
+    <t>High-pressure hot water, district energy, steam and higher-temperature systems</t>
+  </si>
+  <si>
+    <t>Available in Classes 150/300 and higher, with soft- or metal-seat options.</t>
+  </si>
+  <si>
+    <t>Central energy plants, steam, high-temperature water and frequent cycling</t>
+  </si>
+  <si>
+    <t>District steam, high-temperature water and severe HVAC service</t>
+  </si>
+  <si>
+    <t>Double- and triple-offset configurations with metal seating and special alloys.</t>
+  </si>
+  <si>
+    <t>Chilled water, cooling water, washdown water and plant utilities</t>
+  </si>
+  <si>
+    <t>Economical large-line isolation with low torque.</t>
+  </si>
+  <si>
+    <t>Process water, utility water, HVAC and compatible liquid service</t>
+  </si>
+  <si>
+    <t>Resilient seating provides dependable shutoff.</t>
+  </si>
+  <si>
+    <t>Compatible food liquids, water and cleaning systems</t>
+  </si>
+  <si>
+    <t>PTFE, EPDM, Viton and BUNA seat options for application-specific selection.</t>
+  </si>
+  <si>
+    <t>Steam, high-temperature water and higher-pressure plant utilities</t>
+  </si>
+  <si>
+    <t>Soft- and metal-seated options for demanding temperature and pressure.</t>
+  </si>
+  <si>
+    <t>High-temperature steam and severe utility service</t>
+  </si>
+  <si>
+    <t>Double- and triple-offset designs with special material options.</t>
+  </si>
+  <si>
+    <t>Chilled water, condenser water, cooling water and general utilities</t>
+  </si>
+  <si>
+    <t>Cost-effective large-line isolation with easy automation.</t>
+  </si>
+  <si>
+    <t>HVAC water, utility water and compatible non-product-contact systems</t>
+  </si>
+  <si>
+    <t>Resilient-seated shutoff for general utility service.</t>
+  </si>
+  <si>
+    <t>Plant steam, high-temperature water and higher-pressure utilities</t>
+  </si>
+  <si>
+    <t>Soft- and metal-seated configurations for demanding service.</t>
+  </si>
+  <si>
+    <t>Waste treatment, chemical feed and compatible corrosive utility fluids</t>
+  </si>
+  <si>
+    <t>Multiple seat, disc and body material options.</t>
+  </si>
+  <si>
+    <t>High-temperature steam and severe chemical utility applications</t>
+  </si>
+  <si>
+    <t>Double- and triple-offset construction with special alloy.</t>
+  </si>
+  <si>
+    <t>Vehicle-wash water, firewater, stormwater, cooling and facility utilities</t>
+  </si>
+  <si>
+    <t>Economical large-line isolation.</t>
+  </si>
+  <si>
+    <t>Fuel terminals, steam, higher-pressure water and loading facilities</t>
+  </si>
+  <si>
+    <t>Soft-seat, metal-seat and fire-safe configurations.</t>
+  </si>
+  <si>
+    <t>Hot asphalt, severe fuel service and corrosive terminal applications</t>
+  </si>
+  <si>
+    <t>Double- and triple-offset designs with special-alloy options.</t>
+  </si>
+  <si>
+    <t>BodyMaterials</t>
+  </si>
+  <si>
+    <t>SeatLiningOptions</t>
+  </si>
+  <si>
+    <t>DiscAndStem</t>
+  </si>
+  <si>
+    <t>Configurations</t>
+  </si>
+  <si>
+    <t>Ductile Iron Body (Optional Stainless Steel Body)</t>
+  </si>
+  <si>
+    <t>PTFE seat; backing options: NBR, EPDM, Silicone, VITON</t>
+  </si>
+  <si>
+    <t>Disc: 316SS or 316SS / PTFE Lined</t>
+  </si>
+  <si>
+    <t>2-Piece Body Design, Wafer and Lug Available</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROD-008 </t>
+  </si>
+  <si>
+    <t>Ductile Iron</t>
+  </si>
+  <si>
+    <t>Discs: 316 Stainless Steel, DI/Nylon Coated, Aluminum Bronze, Special Alloy; 2-Piece Stem Design</t>
+  </si>
+  <si>
+    <t>Ductile Iron, standard</t>
+  </si>
+  <si>
+    <t>Phenolic Backed Cartridge Seats</t>
+  </si>
+  <si>
+    <t>316 Stainless Steel Standard (Special Duplex / Alloy 20 optional)</t>
+  </si>
+  <si>
+    <t>EPDM / Buna / PTFE / Viton</t>
+  </si>
+  <si>
+    <t>Semi-Lug Body (Wafer to Lug crossover); Model 53 (8"-10"-12"), Model 53A (6"-12", Direct Connect)</t>
+  </si>
+  <si>
+    <t>SS316 or CS-WCB standard; Special Duplex SS / Alloy 20 optional</t>
+  </si>
+  <si>
+    <t>PTFE, RPTFE, PEEK, SS316L+RPTFE, TFM, UHMWPE, or Metal seat (316L) — Fire-Safe to API 607 5th Edition</t>
+  </si>
+  <si>
+    <t>17-4PH Shaft</t>
+  </si>
+  <si>
+    <t>Wafer, Lug; Models BL630, BW630</t>
+  </si>
+  <si>
+    <t>Standard Seat: RPTFE</t>
+  </si>
+  <si>
+    <t>Standard Stem Packing: PTFE / Graphite; Stem: Stainless steel with hard chrome plating</t>
+  </si>
+  <si>
+    <t>Metal Seats; Class VI Shut-Off</t>
+  </si>
+  <si>
+    <t>316 SL / CF3M SL / WCB CS / WC6 W6</t>
+  </si>
+  <si>
+    <t>316SS + Graphite / Inconel 625 + Graphite / Solid Metal (Laminated Seal Ring)</t>
+  </si>
+  <si>
+    <t>Disc: 316 SL / CF3M / WCB / WC6; Stem: XM-19 / 17-4PH / SS410</t>
+  </si>
+  <si>
+    <t>Low Fugitive Emission V-Type PTFE or RTFE Gland Packing; GRAPHITE (standard and Live-Loaded); Lantern Ring option with double packing leak-off monitoring</t>
+  </si>
+  <si>
+    <t>Class 150, Class 300 (V Type, 150L/300L Series)</t>
+  </si>
+  <si>
+    <t>CF8 / 304 SS (CS Plated or WCB Plated, depending on bracket configuration)</t>
+  </si>
+  <si>
+    <t>304 SS (304 SS Plated for CPLR-200/210; 304 SS/CS Plated for CPLR-270)</t>
+  </si>
+  <si>
+    <t>Plated Steel</t>
+  </si>
+  <si>
+    <t>PrimaryProductId</t>
+  </si>
+  <si>
+    <t>RelatedProductIds</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>SizeLabel</t>
+  </si>
+  <si>
+    <t>Pages</t>
+  </si>
+  <si>
+    <t>PdfAssetPath</t>
+  </si>
+  <si>
+    <t>CoverAssetPath</t>
+  </si>
+  <si>
+    <t>ShowInCatalog</t>
+  </si>
+  <si>
+    <t>ShowInMarketing</t>
+  </si>
+  <si>
+    <t>d1</t>
+  </si>
+  <si>
+    <t>Catalog</t>
+  </si>
+  <si>
+    <t>Resilient Seated Series Catalog</t>
+  </si>
+  <si>
+    <t>PROD-010,PROD-011,PROD-012</t>
+  </si>
+  <si>
+    <t>May 2025</t>
+  </si>
+  <si>
+    <t>0.7 MB</t>
   </si>
   <si>
     <t>4</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>BodyMaterials</t>
-  </si>
-  <si>
-    <t>SeatLiningOptions</t>
-  </si>
-  <si>
-    <t>DiscAndStem</t>
-  </si>
-  <si>
-    <t>Configurations</t>
-  </si>
-  <si>
-    <t>Ductile Iron Body (Optional Stainless Steel Body)</t>
-  </si>
-  <si>
-    <t>PTFE seat; backing options: NBR, EPDM, Silicone, VITON</t>
-  </si>
-  <si>
-    <t>Disc: 316SS or 316SS / PTFE Lined</t>
-  </si>
-  <si>
-    <t>2-Piece Body Design, Wafer and Lug Available</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROD-008 </t>
-  </si>
-  <si>
-    <t>Ductile Iron</t>
-  </si>
-  <si>
-    <t>Discs: 316 Stainless Steel, DI/Nylon Coated, Aluminum Bronze, Special Alloy; 2-Piece Stem Design</t>
-  </si>
-  <si>
-    <t>Ductile Iron, standard</t>
-  </si>
-  <si>
-    <t>Phenolic Backed Cartridge Seats</t>
-  </si>
-  <si>
-    <t>316 Stainless Steel Standard (Special Duplex / Alloy 20 optional)</t>
-  </si>
-  <si>
-    <t>EPDM / Buna / PTFE / Viton</t>
-  </si>
-  <si>
-    <t>Semi-Lug Body (Wafer to Lug crossover); Model 53 (8"-10"-12"), Model 53A (6"-12", Direct Connect)</t>
-  </si>
-  <si>
-    <t>SS316 or CS-WCB standard; Special Duplex SS / Alloy 20 optional</t>
-  </si>
-  <si>
-    <t>PTFE, RPTFE, PEEK, SS316L+RPTFE, TFM, UHMWPE, or Metal seat (316L) — Fire-Safe to API 607 5th Edition</t>
-  </si>
-  <si>
-    <t>17-4PH Shaft</t>
-  </si>
-  <si>
-    <t>Wafer, Lug; Models BL630, BW630</t>
-  </si>
-  <si>
-    <t>Standard Seat: RPTFE</t>
-  </si>
-  <si>
-    <t>Standard Stem Packing: PTFE / Graphite; Stem: Stainless steel with hard chrome plating</t>
-  </si>
-  <si>
-    <t>Metal Seats; Class VI Shut-Off</t>
-  </si>
-  <si>
-    <t>316 SL / CF3M SL / WCB CS / WC6 W6</t>
-  </si>
-  <si>
-    <t>316SS + Graphite / Inconel 625 + Graphite / Solid Metal (Laminated Seal Ring)</t>
-  </si>
-  <si>
-    <t>Disc: 316 SL / CF3M / WCB / WC6; Stem: XM-19 / 17-4PH / SS410</t>
-  </si>
-  <si>
-    <t>Low Fugitive Emission V-Type PTFE or RTFE Gland Packing; GRAPHITE (standard and Live-Loaded); Lantern Ring option with double packing leak-off monitoring</t>
-  </si>
-  <si>
-    <t>Class 150, Class 300 (V Type, 150L/300L Series)</t>
-  </si>
-  <si>
-    <t>CF8 / 304 SS (CS Plated or WCB Plated, depending on bracket configuration)</t>
-  </si>
-  <si>
-    <t>304 SS (304 SS Plated for CPLR-200/210; 304 SS/CS Plated for CPLR-270)</t>
-  </si>
-  <si>
-    <t>Plated Steel</t>
-  </si>
-  <si>
-    <t>PrimaryProductId</t>
-  </si>
-  <si>
-    <t>RelatedProductIds</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>SizeLabel</t>
-  </si>
-  <si>
-    <t>Pages</t>
-  </si>
-  <si>
-    <t>PdfAssetPath</t>
-  </si>
-  <si>
-    <t>CoverAssetPath</t>
-  </si>
-  <si>
-    <t>ShowInCatalog</t>
-  </si>
-  <si>
-    <t>ShowInMarketing</t>
-  </si>
-  <si>
-    <t>d1</t>
-  </si>
-  <si>
-    <t>Catalog</t>
-  </si>
-  <si>
-    <t>Resilient Seated Series Catalog</t>
-  </si>
-  <si>
-    <t>PROD-010,PROD-011,PROD-012</t>
-  </si>
-  <si>
-    <t>May 2025</t>
-  </si>
-  <si>
-    <t>0.7 MB</t>
   </si>
   <si>
     <t>/assets/maxseal/docs/resilient-seated-catalog.pdf</t>
@@ -3692,7 +3956,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:N34"/>
+  <dimension ref="A1:M34"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.453125"/>
   <cols>
     <col min="1" max="1" width="8.01" style="1" customWidth="1"/>
@@ -3707,7 +3971,7 @@
     <col min="12" max="12" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" ht="18.75" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -3721,606 +3985,606 @@
         <v>614</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>721</v>
+        <v>808</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>722</v>
+        <v>809</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>723</v>
+        <v>810</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>724</v>
+        <v>811</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>725</v>
+        <v>812</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>726</v>
+        <v>813</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>727</v>
+        <v>814</v>
       </c>
       <c r="L1" s="13" t="s">
-        <v>728</v>
+        <v>815</v>
       </c>
       <c r="M1" t="s">
-        <v>729</v>
-      </c>
-    </row>
-    <row r="2" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="2" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>730</v>
+        <v>817</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>32</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>731</v>
+        <v>818</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>732</v>
+        <v>819</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>220</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>733</v>
+        <v>820</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>734</v>
+        <v>821</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>735</v>
+        <v>822</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>688</v>
+        <v>823</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>736</v>
+        <v>824</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>737</v>
+        <v>825</v>
       </c>
       <c r="L2" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="3" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="3" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>739</v>
+        <v>827</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>44</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>731</v>
+        <v>818</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>740</v>
+        <v>828</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>150</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>741</v>
+        <v>829</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>742</v>
+        <v>830</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>743</v>
+        <v>831</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>744</v>
+        <v>832</v>
       </c>
       <c r="L3" t="s">
         <v>619</v>
       </c>
     </row>
-    <row r="4" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>745</v>
+        <v>833</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>38</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>731</v>
+        <v>818</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>746</v>
+        <v>834</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>137</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>747</v>
+        <v>835</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>748</v>
+        <v>836</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>749</v>
+        <v>837</v>
       </c>
       <c r="L4" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="5" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="5" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>750</v>
+        <v>838</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>751</v>
+        <v>839</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>731</v>
+        <v>818</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>752</v>
+        <v>840</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>160</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>753</v>
+        <v>841</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>754</v>
+        <v>842</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>755</v>
+        <v>843</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>756</v>
+        <v>844</v>
       </c>
       <c r="L5" t="s">
         <v>619</v>
       </c>
     </row>
-    <row r="6" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>757</v>
+        <v>845</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>758</v>
+        <v>846</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>759</v>
+        <v>847</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>760</v>
+        <v>848</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>187</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>761</v>
+        <v>849</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>762</v>
+        <v>850</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>763</v>
+        <v>851</v>
       </c>
       <c r="L6" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="7" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="7" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>764</v>
+        <v>852</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>53</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>731</v>
+        <v>818</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>765</v>
+        <v>853</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>173</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>766</v>
+        <v>854</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>767</v>
+        <v>855</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>768</v>
+        <v>856</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>769</v>
+        <v>857</v>
       </c>
       <c r="L7" t="s">
         <v>619</v>
       </c>
     </row>
-    <row r="8" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>770</v>
+        <v>858</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>771</v>
+        <v>859</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>772</v>
+        <v>860</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>773</v>
+        <v>861</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>120</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>734</v>
+        <v>821</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>774</v>
+        <v>862</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="L8" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="9" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="9" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>775</v>
+        <v>863</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>776</v>
+        <v>864</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>777</v>
+        <v>865</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>778</v>
+        <v>866</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>779</v>
+        <v>867</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>741</v>
+        <v>829</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>780</v>
+        <v>868</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>781</v>
+        <v>869</v>
       </c>
       <c r="L9" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="10" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="10" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>782</v>
+        <v>870</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>783</v>
+        <v>871</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>784</v>
+        <v>872</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>785</v>
+        <v>873</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>779</v>
+        <v>867</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>747</v>
+        <v>835</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>786</v>
+        <v>874</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>787</v>
+        <v>875</v>
       </c>
       <c r="L10" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="11" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="11" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>788</v>
+        <v>876</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>789</v>
+        <v>877</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>790</v>
+        <v>878</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>791</v>
+        <v>879</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>160</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>753</v>
+        <v>841</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>792</v>
+        <v>880</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>793</v>
+        <v>881</v>
       </c>
       <c r="L11" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>794</v>
+        <v>882</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>795</v>
+        <v>883</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>731</v>
+        <v>818</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>796</v>
+        <v>884</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>220</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>797</v>
+        <v>885</v>
       </c>
       <c r="L12" t="s">
         <v>619</v>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>798</v>
+        <v>886</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>799</v>
+        <v>887</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>731</v>
+        <v>818</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>800</v>
+        <v>888</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>230</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>801</v>
+        <v>889</v>
       </c>
       <c r="L13" t="s">
         <v>619</v>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>802</v>
+        <v>890</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>803</v>
+        <v>891</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>731</v>
+        <v>818</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>804</v>
+        <v>892</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>248</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>805</v>
+        <v>893</v>
       </c>
       <c r="L14" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>806</v>
+        <v>894</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>807</v>
+        <v>895</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>731</v>
+        <v>818</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>808</v>
+        <v>896</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>187</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>809</v>
+        <v>897</v>
       </c>
       <c r="L15" t="s">
         <v>619</v>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>810</v>
+        <v>898</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>811</v>
+        <v>899</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>731</v>
+        <v>818</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>812</v>
+        <v>900</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>261</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>813</v>
+        <v>901</v>
       </c>
       <c r="L16" t="s">
         <v>619</v>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>814</v>
+        <v>902</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>815</v>
+        <v>903</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>731</v>
+        <v>818</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>816</v>
+        <v>904</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>271</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>817</v>
+        <v>905</v>
       </c>
       <c r="L17" t="s">
         <v>619</v>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
+        <v>906</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>907</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>818</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>819</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>731</v>
-      </c>
       <c r="D18" s="1" t="s">
-        <v>820</v>
+        <v>908</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>279</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>821</v>
+        <v>909</v>
       </c>
       <c r="L18" t="s">
         <v>619</v>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>822</v>
+        <v>910</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>823</v>
+        <v>911</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>731</v>
+        <v>818</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>824</v>
+        <v>912</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>289</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>825</v>
+        <v>913</v>
       </c>
       <c r="L19" t="s">
         <v>619</v>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>826</v>
+        <v>914</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>827</v>
+        <v>915</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>731</v>
+        <v>818</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>828</v>
+        <v>916</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>300</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>829</v>
+        <v>917</v>
       </c>
       <c r="L20" t="s">
         <v>619</v>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>830</v>
+        <v>918</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>831</v>
+        <v>919</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>731</v>
+        <v>818</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>832</v>
+        <v>920</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>309</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>833</v>
+        <v>921</v>
       </c>
       <c r="L21" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>834</v>
+        <v>922</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>835</v>
+        <v>923</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>731</v>
+        <v>818</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>836</v>
+        <v>924</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>240</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>837</v>
+        <v>925</v>
       </c>
       <c r="L22" t="s">
         <v>619</v>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>838</v>
+        <v>926</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>839</v>
+        <v>927</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>731</v>
+        <v>818</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>840</v>
+        <v>928</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>196</v>
@@ -4329,347 +4593,347 @@
         <v>321</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>841</v>
+        <v>929</v>
       </c>
       <c r="L23" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>842</v>
+        <v>930</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>843</v>
+        <v>931</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>731</v>
+        <v>818</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>844</v>
+        <v>932</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>208</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>845</v>
+        <v>933</v>
       </c>
       <c r="L24" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>846</v>
+        <v>934</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>731</v>
+        <v>818</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>848</v>
+        <v>936</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>344</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>849</v>
+        <v>937</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>850</v>
+        <v>938</v>
       </c>
       <c r="L25" t="s">
         <v>619</v>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>851</v>
+        <v>939</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>852</v>
+        <v>940</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>731</v>
+        <v>818</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>853</v>
+        <v>941</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>351</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>854</v>
+        <v>942</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>855</v>
+        <v>943</v>
       </c>
       <c r="L26" t="s">
         <v>619</v>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>856</v>
+        <v>944</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>857</v>
+        <v>945</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>731</v>
+        <v>818</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>858</v>
+        <v>946</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>415</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>859</v>
+        <v>947</v>
       </c>
       <c r="J27" s="1" t="s">
+        <v>948</v>
+      </c>
+      <c r="L27" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>949</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>950</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>818</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>951</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>952</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>953</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>954</v>
+      </c>
+      <c r="L28" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>955</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>956</v>
+      </c>
+      <c r="C29" s="1" t="s">
         <v>860</v>
       </c>
-      <c r="L27" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="28" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>861</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>862</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>731</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>863</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>779</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>864</v>
-      </c>
-      <c r="H28" s="1" t="s">
-        <v>865</v>
-      </c>
-      <c r="J28" s="1" t="s">
-        <v>866</v>
-      </c>
-      <c r="L28" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="29" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>868</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>772</v>
-      </c>
       <c r="D29" s="1" t="s">
-        <v>869</v>
+        <v>957</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>271</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>864</v>
+        <v>952</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>870</v>
+        <v>958</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>871</v>
+        <v>959</v>
       </c>
       <c r="L29" t="s">
         <v>619</v>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>872</v>
+        <v>960</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>873</v>
+        <v>961</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>731</v>
+        <v>818</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>874</v>
+        <v>962</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>279</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>864</v>
+        <v>952</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>875</v>
+        <v>963</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>876</v>
+        <v>964</v>
       </c>
       <c r="L30" t="s">
         <v>619</v>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>877</v>
+        <v>965</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>878</v>
+        <v>966</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>731</v>
+        <v>818</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>879</v>
+        <v>967</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>309</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>864</v>
+        <v>952</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>880</v>
+        <v>968</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>881</v>
+        <v>969</v>
       </c>
       <c r="L31" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>882</v>
+        <v>970</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>883</v>
+        <v>971</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>884</v>
+        <v>972</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>885</v>
+        <v>973</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>220</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>886</v>
+        <v>974</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>886</v>
+        <v>974</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>887</v>
+        <v>975</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>886</v>
+        <v>974</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>888</v>
+        <v>976</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>886</v>
+        <v>974</v>
       </c>
       <c r="L32" t="s">
-        <v>738</v>
+        <v>826</v>
       </c>
       <c r="M32" t="s">
         <v>619</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>889</v>
+        <v>977</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>890</v>
+        <v>978</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>884</v>
+        <v>972</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>891</v>
+        <v>979</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>779</v>
+        <v>867</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>886</v>
+        <v>974</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>886</v>
+        <v>974</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>892</v>
+        <v>980</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>886</v>
+        <v>974</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>893</v>
+        <v>981</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>886</v>
+        <v>974</v>
       </c>
       <c r="L33" t="s">
-        <v>738</v>
+        <v>826</v>
       </c>
       <c r="M33" t="s">
         <v>619</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>894</v>
+        <v>982</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>895</v>
+        <v>983</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>772</v>
+        <v>860</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>896</v>
+        <v>984</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>220</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>886</v>
+        <v>974</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>886</v>
+        <v>974</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>897</v>
+        <v>985</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>886</v>
+        <v>974</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>898</v>
+        <v>986</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>886</v>
+        <v>974</v>
       </c>
       <c r="L34" t="s">
-        <v>738</v>
+        <v>826</v>
       </c>
       <c r="M34" t="s">
         <v>619</v>
@@ -4709,22 +4973,22 @@
         <v>435</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>899</v>
+        <v>987</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>900</v>
+        <v>988</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>901</v>
+        <v>989</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>902</v>
+        <v>990</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>724</v>
+        <v>811</v>
       </c>
       <c r="I1" t="s">
-        <v>726</v>
+        <v>813</v>
       </c>
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4739,60 +5003,60 @@
     </row>
     <row r="3" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>903</v>
+        <v>991</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>904</v>
+        <v>992</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>779</v>
+        <v>867</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>905</v>
+        <v>993</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>905</v>
+        <v>993</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>906</v>
+        <v>994</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>907</v>
+        <v>995</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>908</v>
+        <v>996</v>
       </c>
       <c r="I3" t="s">
-        <v>860</v>
+        <v>948</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>909</v>
+        <v>997</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>910</v>
+        <v>998</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>779</v>
+        <v>867</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>911</v>
+        <v>999</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>912</v>
+        <v>1000</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>913</v>
+        <v>1001</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>907</v>
+        <v>995</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>865</v>
+        <v>953</v>
       </c>
       <c r="I4" t="s">
-        <v>866</v>
+        <v>954</v>
       </c>
     </row>
   </sheetData>
@@ -4831,63 +5095,63 @@
         <v>437</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>914</v>
+        <v>1002</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>915</v>
+        <v>1003</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>916</v>
+        <v>1004</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>917</v>
+        <v>1005</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>725</v>
+        <v>812</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>918</v>
+        <v>1006</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>919</v>
+        <v>1007</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>920</v>
+        <v>1008</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>723</v>
+        <v>810</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>899</v>
+        <v>987</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>900</v>
+        <v>988</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>902</v>
+        <v>990</v>
       </c>
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>921</v>
+        <v>1009</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>731</v>
+        <v>818</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>922</v>
+        <v>1010</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>923</v>
+        <v>1011</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>924</v>
+        <v>1012</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>925</v>
+        <v>1013</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>926</v>
+        <v>1014</v>
       </c>
       <c r="H2" s="6" t="s">
         <v>32</v>
@@ -4895,48 +5159,48 @@
     </row>
     <row r="3" ht="18.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>927</v>
+        <v>1015</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>928</v>
+        <v>1016</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>929</v>
+        <v>1017</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>930</v>
+        <v>1018</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>884</v>
+        <v>972</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>931</v>
+        <v>1019</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>741</v>
+        <v>829</v>
       </c>
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>932</v>
+        <v>1020</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>933</v>
+        <v>1021</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>934</v>
+        <v>1022</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>935</v>
+        <v>1023</v>
       </c>
       <c r="L4" s="6" t="s">
-        <v>936</v>
+        <v>1024</v>
       </c>
       <c r="M4" s="6" t="s">
-        <v>937</v>
+        <v>1025</v>
       </c>
       <c r="N4" s="6" t="s">
-        <v>938</v>
+        <v>1026</v>
       </c>
     </row>
   </sheetData>
@@ -4963,7 +5227,7 @@
         <v>435</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>939</v>
+        <v>1027</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>6</v>
@@ -4977,7 +5241,7 @@
         <v>160</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="3" ht="18.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -4988,7 +5252,7 @@
         <v>150</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -4999,7 +5263,7 @@
         <v>150</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="5" ht="18.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -5010,7 +5274,7 @@
         <v>150</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="6" ht="18.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -5021,7 +5285,7 @@
         <v>150</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -5883,45 +6147,45 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>940</v>
+        <v>1028</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>941</v>
+        <v>1029</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>942</v>
+        <v>1030</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>943</v>
+        <v>1031</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>944</v>
+        <v>1032</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>945</v>
+        <v>1033</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>946</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>947</v>
+        <v>1035</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>948</v>
+        <v>1036</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>949</v>
+        <v>1037</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>950</v>
+        <v>1038</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>951</v>
+        <v>1039</v>
       </c>
       <c r="G2" s="6" t="s">
         <v>120</v>
@@ -5929,22 +6193,22 @@
     </row>
     <row r="3" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>952</v>
+        <v>1040</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>948</v>
+        <v>1036</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>953</v>
+        <v>1041</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>41</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>954</v>
+        <v>1042</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>951</v>
+        <v>1039</v>
       </c>
       <c r="G3" s="6" t="s">
         <v>137</v>
@@ -5952,22 +6216,22 @@
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>955</v>
+        <v>1043</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>948</v>
+        <v>1036</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>956</v>
+        <v>1044</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>957</v>
+        <v>1045</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>958</v>
+        <v>1046</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>951</v>
+        <v>1039</v>
       </c>
       <c r="G4" s="6" t="s">
         <v>150</v>
@@ -5975,22 +6239,22 @@
     </row>
     <row r="5" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>959</v>
+        <v>1047</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>948</v>
+        <v>1036</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>960</v>
+        <v>1048</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>961</v>
+        <v>1049</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>962</v>
+        <v>1050</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>951</v>
+        <v>1039</v>
       </c>
       <c r="G5" s="6" t="s">
         <v>160</v>
@@ -5998,22 +6262,22 @@
     </row>
     <row r="6" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>963</v>
+        <v>1051</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>948</v>
+        <v>1036</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>964</v>
+        <v>1052</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>54</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>965</v>
+        <v>1053</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>951</v>
+        <v>1039</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>173</v>
@@ -6021,22 +6285,22 @@
     </row>
     <row r="7" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>966</v>
+        <v>1054</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>948</v>
+        <v>1036</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>967</v>
+        <v>1055</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>968</v>
+        <v>1056</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>969</v>
+        <v>1057</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>951</v>
+        <v>1039</v>
       </c>
       <c r="G7" s="6" t="s">
         <v>187</v>
@@ -6044,22 +6308,22 @@
     </row>
     <row r="8" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>970</v>
+        <v>1058</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>948</v>
+        <v>1036</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>971</v>
+        <v>1059</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>972</v>
+        <v>1060</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>973</v>
+        <v>1061</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>951</v>
+        <v>1039</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>196</v>
@@ -6067,22 +6331,22 @@
     </row>
     <row r="9" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>974</v>
+        <v>1062</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>948</v>
+        <v>1036</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>975</v>
+        <v>1063</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>634</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>976</v>
+        <v>1064</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>977</v>
+        <v>1065</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>632</v>
@@ -6090,22 +6354,22 @@
     </row>
     <row r="10" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>978</v>
+        <v>1066</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>948</v>
+        <v>1036</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>979</v>
+        <v>1067</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>638</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>980</v>
+        <v>1068</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>977</v>
+        <v>1065</v>
       </c>
       <c r="G10" s="6" t="s">
         <v>636</v>
@@ -6113,22 +6377,22 @@
     </row>
     <row r="11" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>981</v>
+        <v>1069</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>948</v>
+        <v>1036</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>982</v>
+        <v>1070</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>642</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>983</v>
+        <v>1071</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>977</v>
+        <v>1065</v>
       </c>
       <c r="G11" s="6" t="s">
         <v>640</v>
@@ -6136,22 +6400,22 @@
     </row>
     <row r="12" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>984</v>
+        <v>1072</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>948</v>
+        <v>1036</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>985</v>
+        <v>1073</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>646</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>986</v>
+        <v>1074</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>977</v>
+        <v>1065</v>
       </c>
       <c r="G12" s="6" t="s">
         <v>644</v>
@@ -6159,22 +6423,22 @@
     </row>
     <row r="13" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>987</v>
+        <v>1075</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>948</v>
+        <v>1036</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>988</v>
+        <v>1076</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>650</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>989</v>
+        <v>1077</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>977</v>
+        <v>1065</v>
       </c>
       <c r="G13" s="6" t="s">
         <v>648</v>
@@ -6182,22 +6446,22 @@
     </row>
     <row r="14" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>990</v>
+        <v>1078</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>948</v>
+        <v>1036</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>991</v>
+        <v>1079</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>654</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>992</v>
+        <v>1080</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>977</v>
+        <v>1065</v>
       </c>
       <c r="G14" s="6" t="s">
         <v>652</v>
@@ -6205,22 +6469,22 @@
     </row>
     <row r="15" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>993</v>
+        <v>1081</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>948</v>
+        <v>1036</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>994</v>
+        <v>1082</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>658</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>995</v>
+        <v>1083</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>977</v>
+        <v>1065</v>
       </c>
       <c r="G15" s="6" t="s">
         <v>656</v>
@@ -6228,22 +6492,22 @@
     </row>
     <row r="16" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>996</v>
+        <v>1084</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>948</v>
+        <v>1036</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>997</v>
+        <v>1085</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>662</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>998</v>
+        <v>1086</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>977</v>
+        <v>1065</v>
       </c>
       <c r="G16" s="6" t="s">
         <v>660</v>
@@ -6251,22 +6515,22 @@
     </row>
     <row r="17" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>999</v>
+        <v>1087</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>948</v>
+        <v>1036</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>1000</v>
+        <v>1088</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>666</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>1001</v>
+        <v>1089</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>977</v>
+        <v>1065</v>
       </c>
       <c r="G17" s="6" t="s">
         <v>664</v>
@@ -6274,22 +6538,22 @@
     </row>
     <row r="18" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>1002</v>
+        <v>1090</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>948</v>
+        <v>1036</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>1003</v>
+        <v>1091</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>670</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>1004</v>
+        <v>1092</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>977</v>
+        <v>1065</v>
       </c>
       <c r="G18" s="6" t="s">
         <v>668</v>
@@ -6297,22 +6561,22 @@
     </row>
     <row r="19" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>1005</v>
+        <v>1093</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>948</v>
+        <v>1036</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>1006</v>
+        <v>1094</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>674</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>1007</v>
+        <v>1095</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>977</v>
+        <v>1065</v>
       </c>
       <c r="G19" s="6" t="s">
         <v>672</v>
@@ -6320,22 +6584,22 @@
     </row>
     <row r="20" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>1008</v>
+        <v>1096</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>948</v>
+        <v>1036</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>1009</v>
+        <v>1097</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>678</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>1010</v>
+        <v>1098</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>977</v>
+        <v>1065</v>
       </c>
       <c r="G20" s="6" t="s">
         <v>676</v>
@@ -6343,22 +6607,22 @@
     </row>
     <row r="21" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>1011</v>
+        <v>1099</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>948</v>
+        <v>1036</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>1012</v>
+        <v>1100</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>682</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>1013</v>
+        <v>1101</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>977</v>
+        <v>1065</v>
       </c>
       <c r="G21" s="6" t="s">
         <v>680</v>
@@ -6366,71 +6630,71 @@
     </row>
     <row r="22" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>1014</v>
+        <v>1102</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>948</v>
+        <v>1036</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>1015</v>
+        <v>1103</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>1016</v>
+        <v>1104</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>1017</v>
+        <v>1105</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>1018</v>
+        <v>1106</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>1019</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="23" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>1020</v>
+        <v>1108</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>1021</v>
+        <v>1109</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>1022</v>
+        <v>1110</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>736</v>
+        <v>824</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>1023</v>
+        <v>1111</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>1024</v>
+        <v>1112</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>730</v>
+        <v>817</v>
       </c>
     </row>
     <row r="24" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>1025</v>
+        <v>1113</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>948</v>
+        <v>1036</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>1026</v>
+        <v>1114</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>737</v>
+        <v>825</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>1027</v>
+        <v>1115</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>1024</v>
+        <v>1112</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>730</v>
+        <v>817</v>
       </c>
     </row>
   </sheetData>
@@ -6475,7 +6739,7 @@
         <v>35</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>1028</v>
+        <v>1116</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -6489,7 +6753,7 @@
         <v>35</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>1029</v>
+        <v>1117</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -6503,7 +6767,7 @@
         <v>35</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>1030</v>
+        <v>1118</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -6517,7 +6781,7 @@
         <v>41</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>1028</v>
+        <v>1116</v>
       </c>
       <c r="D5" s="1">
         <v>1</v>
@@ -6531,7 +6795,7 @@
         <v>41</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>1029</v>
+        <v>1117</v>
       </c>
       <c r="D6" s="1">
         <v>2</v>
@@ -6545,7 +6809,7 @@
         <v>41</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>1030</v>
+        <v>1118</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -6559,7 +6823,7 @@
         <v>46</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>1028</v>
+        <v>1116</v>
       </c>
       <c r="D8" s="1">
         <v>1</v>
@@ -6573,7 +6837,7 @@
         <v>46</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>1029</v>
+        <v>1117</v>
       </c>
       <c r="D9" s="1">
         <v>2</v>
@@ -6587,7 +6851,7 @@
         <v>46</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>1030</v>
+        <v>1118</v>
       </c>
       <c r="D10" s="1">
         <v>3</v>
@@ -6601,7 +6865,7 @@
         <v>50</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>1028</v>
+        <v>1116</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
@@ -6615,7 +6879,7 @@
         <v>50</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>1029</v>
+        <v>1117</v>
       </c>
       <c r="D12" s="1">
         <v>2</v>
@@ -6629,7 +6893,7 @@
         <v>50</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>1030</v>
+        <v>1118</v>
       </c>
       <c r="D13" s="1">
         <v>3</v>
@@ -6643,7 +6907,7 @@
         <v>54</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>1028</v>
+        <v>1116</v>
       </c>
       <c r="D14" s="1">
         <v>1</v>
@@ -6657,7 +6921,7 @@
         <v>54</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>1029</v>
+        <v>1117</v>
       </c>
       <c r="D15" s="1">
         <v>2</v>
@@ -6671,7 +6935,7 @@
         <v>54</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>1030</v>
+        <v>1118</v>
       </c>
       <c r="D16" s="1">
         <v>3</v>
@@ -6685,7 +6949,7 @@
         <v>58</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>1028</v>
+        <v>1116</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
@@ -6699,7 +6963,7 @@
         <v>58</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>1029</v>
+        <v>1117</v>
       </c>
       <c r="D18" s="1">
         <v>2</v>
@@ -6713,7 +6977,7 @@
         <v>58</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>1030</v>
+        <v>1118</v>
       </c>
       <c r="D19" s="1">
         <v>3</v>
@@ -6727,7 +6991,7 @@
         <v>63</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>1028</v>
+        <v>1116</v>
       </c>
       <c r="D20" s="1">
         <v>1</v>
@@ -6741,7 +7005,7 @@
         <v>63</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>1029</v>
+        <v>1117</v>
       </c>
       <c r="D21" s="1">
         <v>2</v>
@@ -6755,7 +7019,7 @@
         <v>63</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>1030</v>
+        <v>1118</v>
       </c>
       <c r="D22" s="1">
         <v>3</v>
@@ -6769,7 +7033,7 @@
         <v>68</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>1028</v>
+        <v>1116</v>
       </c>
       <c r="D23" s="1">
         <v>1</v>
@@ -6783,7 +7047,7 @@
         <v>68</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>1029</v>
+        <v>1117</v>
       </c>
       <c r="D24" s="1">
         <v>2</v>
@@ -6797,7 +7061,7 @@
         <v>68</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>1030</v>
+        <v>1118</v>
       </c>
       <c r="D25" s="1">
         <v>3</v>
@@ -6811,7 +7075,7 @@
         <v>227</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>1028</v>
+        <v>1116</v>
       </c>
       <c r="D26" s="1">
         <v>1</v>
@@ -6825,7 +7089,7 @@
         <v>227</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>1029</v>
+        <v>1117</v>
       </c>
       <c r="D27" s="1">
         <v>2</v>
@@ -6839,7 +7103,7 @@
         <v>227</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>1030</v>
+        <v>1118</v>
       </c>
       <c r="D28" s="1">
         <v>3</v>
@@ -6853,7 +7117,7 @@
         <v>237</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>1028</v>
+        <v>1116</v>
       </c>
       <c r="D29" s="1">
         <v>1</v>
@@ -6867,7 +7131,7 @@
         <v>237</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>1029</v>
+        <v>1117</v>
       </c>
       <c r="D30" s="1">
         <v>2</v>
@@ -6881,7 +7145,7 @@
         <v>237</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>1030</v>
+        <v>1118</v>
       </c>
       <c r="D31" s="1">
         <v>3</v>
@@ -6895,7 +7159,7 @@
         <v>247</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>1028</v>
+        <v>1116</v>
       </c>
       <c r="D32" s="1">
         <v>1</v>
@@ -6909,7 +7173,7 @@
         <v>247</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>1029</v>
+        <v>1117</v>
       </c>
       <c r="D33" s="1">
         <v>2</v>
@@ -6923,7 +7187,7 @@
         <v>247</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>1030</v>
+        <v>1118</v>
       </c>
       <c r="D34" s="1">
         <v>3</v>
@@ -6937,7 +7201,7 @@
         <v>255</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>1028</v>
+        <v>1116</v>
       </c>
       <c r="D35" s="1">
         <v>1</v>
@@ -6951,7 +7215,7 @@
         <v>255</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>1029</v>
+        <v>1117</v>
       </c>
       <c r="D36" s="1">
         <v>2</v>
@@ -6965,7 +7229,7 @@
         <v>255</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>1030</v>
+        <v>1118</v>
       </c>
       <c r="D37" s="1">
         <v>3</v>
@@ -6979,7 +7243,7 @@
         <v>268</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>1028</v>
+        <v>1116</v>
       </c>
       <c r="D38" s="1">
         <v>1</v>
@@ -6993,7 +7257,7 @@
         <v>268</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>1029</v>
+        <v>1117</v>
       </c>
       <c r="D39" s="1">
         <v>2</v>
@@ -7007,7 +7271,7 @@
         <v>268</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>1030</v>
+        <v>1118</v>
       </c>
       <c r="D40" s="1">
         <v>3</v>
@@ -7021,7 +7285,7 @@
         <v>278</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>1028</v>
+        <v>1116</v>
       </c>
       <c r="D41" s="1">
         <v>1</v>
@@ -7035,7 +7299,7 @@
         <v>278</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>1029</v>
+        <v>1117</v>
       </c>
       <c r="D42" s="1">
         <v>2</v>
@@ -7049,7 +7313,7 @@
         <v>278</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>1030</v>
+        <v>1118</v>
       </c>
       <c r="D43" s="1">
         <v>3</v>
@@ -7063,7 +7327,7 @@
         <v>286</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>1028</v>
+        <v>1116</v>
       </c>
       <c r="D44" s="1">
         <v>1</v>
@@ -7077,7 +7341,7 @@
         <v>286</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>1029</v>
+        <v>1117</v>
       </c>
       <c r="D45" s="1">
         <v>2</v>
@@ -7091,7 +7355,7 @@
         <v>286</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>1030</v>
+        <v>1118</v>
       </c>
       <c r="D46" s="1">
         <v>3</v>
@@ -7105,7 +7369,7 @@
         <v>296</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>1028</v>
+        <v>1116</v>
       </c>
       <c r="D47" s="1">
         <v>1</v>
@@ -7119,7 +7383,7 @@
         <v>296</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>1029</v>
+        <v>1117</v>
       </c>
       <c r="D48" s="1">
         <v>2</v>
@@ -7133,7 +7397,7 @@
         <v>296</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>1030</v>
+        <v>1118</v>
       </c>
       <c r="D49" s="1">
         <v>3</v>
@@ -7147,7 +7411,7 @@
         <v>307</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>1028</v>
+        <v>1116</v>
       </c>
       <c r="D50" s="1">
         <v>1</v>
@@ -7161,7 +7425,7 @@
         <v>307</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>1029</v>
+        <v>1117</v>
       </c>
       <c r="D51" s="1">
         <v>2</v>
@@ -7175,7 +7439,7 @@
         <v>307</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>1030</v>
+        <v>1118</v>
       </c>
       <c r="D52" s="1">
         <v>3</v>
@@ -7189,7 +7453,7 @@
         <v>41</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>1028</v>
+        <v>1116</v>
       </c>
       <c r="D53" s="1">
         <v>1</v>
@@ -7203,7 +7467,7 @@
         <v>41</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>1029</v>
+        <v>1117</v>
       </c>
       <c r="D54" s="1">
         <v>2</v>
@@ -7217,7 +7481,7 @@
         <v>41</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>1030</v>
+        <v>1118</v>
       </c>
       <c r="D55" s="1">
         <v>3</v>
@@ -7231,7 +7495,7 @@
         <v>73</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>1028</v>
+        <v>1116</v>
       </c>
       <c r="D56" s="1">
         <v>1</v>
@@ -7245,7 +7509,7 @@
         <v>73</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>1029</v>
+        <v>1117</v>
       </c>
       <c r="D57" s="1">
         <v>2</v>
@@ -7259,7 +7523,7 @@
         <v>73</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>1030</v>
+        <v>1118</v>
       </c>
       <c r="D58" s="1">
         <v>3</v>
@@ -7273,7 +7537,7 @@
         <v>77</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>1028</v>
+        <v>1116</v>
       </c>
       <c r="D59" s="1">
         <v>1</v>
@@ -7287,7 +7551,7 @@
         <v>77</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>1029</v>
+        <v>1117</v>
       </c>
       <c r="D60" s="1">
         <v>2</v>
@@ -7301,7 +7565,7 @@
         <v>77</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>1030</v>
+        <v>1118</v>
       </c>
       <c r="D61" s="1">
         <v>3</v>
@@ -7315,7 +7579,7 @@
         <v>81</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>1028</v>
+        <v>1116</v>
       </c>
       <c r="D62" s="1">
         <v>1</v>
@@ -7329,7 +7593,7 @@
         <v>81</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>1029</v>
+        <v>1117</v>
       </c>
       <c r="D63" s="1">
         <v>2</v>
@@ -7343,7 +7607,7 @@
         <v>81</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>1030</v>
+        <v>1118</v>
       </c>
       <c r="D64" s="1">
         <v>3</v>
@@ -7357,7 +7621,7 @@
         <v>85</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>1028</v>
+        <v>1116</v>
       </c>
       <c r="D65" s="1">
         <v>1</v>
@@ -7371,7 +7635,7 @@
         <v>85</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>1029</v>
+        <v>1117</v>
       </c>
       <c r="D66" s="1">
         <v>2</v>
@@ -7385,7 +7649,7 @@
         <v>85</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>1030</v>
+        <v>1118</v>
       </c>
       <c r="D67" s="1">
         <v>3</v>
@@ -7399,7 +7663,7 @@
         <v>90</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>1028</v>
+        <v>1116</v>
       </c>
       <c r="D68" s="1">
         <v>1</v>
@@ -7413,7 +7677,7 @@
         <v>90</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>1029</v>
+        <v>1117</v>
       </c>
       <c r="D69" s="1">
         <v>2</v>
@@ -7427,7 +7691,7 @@
         <v>90</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>1030</v>
+        <v>1118</v>
       </c>
       <c r="D70" s="1">
         <v>3</v>
@@ -7441,7 +7705,7 @@
         <v>27</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>1028</v>
+        <v>1116</v>
       </c>
       <c r="D71" s="1">
         <v>1</v>
@@ -7455,7 +7719,7 @@
         <v>27</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>1029</v>
+        <v>1117</v>
       </c>
       <c r="D72" s="1">
         <v>2</v>
@@ -7469,7 +7733,7 @@
         <v>27</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>1030</v>
+        <v>1118</v>
       </c>
       <c r="D73" s="1">
         <v>3</v>
@@ -7495,114 +7759,114 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>1031</v>
+        <v>1119</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>1032</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>1033</v>
+        <v>1121</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>1034</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="3" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>1035</v>
+        <v>1123</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>1036</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>1037</v>
+        <v>1125</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>1038</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="5" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>1039</v>
+        <v>1127</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>1040</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="6" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>1041</v>
+        <v>1129</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>1042</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="7" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>1043</v>
+        <v>1131</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>1044</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="8" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>1045</v>
+        <v>1133</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>1046</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="9" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>1047</v>
+        <v>1135</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>1048</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="10" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>1049</v>
+        <v>1137</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>1050</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="11" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>1051</v>
+        <v>1139</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>1052</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="12" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>1053</v>
+        <v>1141</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>1054</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="13" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>1055</v>
+        <v>1143</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>1056</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="14" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>1057</v>
+        <v>1145</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>1058</v>
+        <v>1146</v>
       </c>
     </row>
   </sheetData>
@@ -12877,7 +13141,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C122"/>
+  <dimension ref="A1:E122"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.453125"/>
   <cols>
     <col min="1" max="1" width="14.01" style="1" customWidth="1"/>
@@ -12885,7 +13149,7 @@
     <col min="3" max="3" width="10.01" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>435</v>
       </c>
@@ -12895,8 +13159,14 @@
       <c r="C1" s="4" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" ht="18.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1" t="s">
+        <v>685</v>
+      </c>
+      <c r="E1" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="2" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>120</v>
       </c>
@@ -12904,1328 +13174,1478 @@
         <v>632</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="3" ht="18.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="3" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>668</v>
+        <v>636</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="4" ht="18.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="4" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>656</v>
-      </c>
-      <c r="C4" s="6" t="s">
+        <v>640</v>
+      </c>
+      <c r="C4" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>636</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>687</v>
       </c>
     </row>
-    <row r="5" ht="18.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>680</v>
-      </c>
-      <c r="C5" s="6" t="s">
+    <row r="6" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>640</v>
+      </c>
+      <c r="C6" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>644</v>
+      </c>
+      <c r="C7" s="6" t="s">
         <v>688</v>
       </c>
     </row>
-    <row r="6" ht="18.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>672</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="7" ht="18.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="B7" s="6" t="s">
+    <row r="8" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>644</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="9" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>644</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="10" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>632</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="11" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>636</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="8" ht="18.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>640</v>
-      </c>
-      <c r="C8" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" ht="18.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>652</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="10" ht="18.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>668</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>688</v>
-      </c>
-    </row>
-    <row r="11" ht="18.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>656</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>689</v>
       </c>
     </row>
-    <row r="12" ht="18.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>150</v>
+        <v>208</v>
       </c>
       <c r="B12" s="6" t="s">
+        <v>640</v>
+      </c>
+      <c r="C12" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>632</v>
+      </c>
+      <c r="C13" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>632</v>
+      </c>
+      <c r="C14" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>632</v>
+      </c>
+      <c r="C15" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>632</v>
+      </c>
+      <c r="C16" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="B17" s="6" t="s">
         <v>636</v>
       </c>
-      <c r="C12" s="6" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="13" ht="18.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="B13" s="6" t="s">
+      <c r="C17" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="B18" s="6" t="s">
         <v>640</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C18" s="6">
         <v>2</v>
       </c>
     </row>
-    <row r="14" ht="18.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>644</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="15" ht="18.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>652</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>688</v>
-      </c>
-    </row>
-    <row r="16" ht="18.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>644</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="17" ht="18.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>648</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="18" ht="18.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>676</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="19" ht="18.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>160</v>
+        <v>271</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>672</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>688</v>
-      </c>
-    </row>
-    <row r="20" ht="18.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+        <v>636</v>
+      </c>
+      <c r="C19" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>173</v>
+        <v>271</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>664</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="21" ht="18.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+        <v>640</v>
+      </c>
+      <c r="C20" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>173</v>
+        <v>279</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>648</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="22" ht="18.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+        <v>636</v>
+      </c>
+      <c r="C21" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>173</v>
+        <v>279</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>644</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="23" ht="18.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+        <v>640</v>
+      </c>
+      <c r="C22" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>173</v>
+        <v>300</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>676</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>688</v>
-      </c>
-    </row>
-    <row r="24" ht="18.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+        <v>636</v>
+      </c>
+      <c r="C23" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>187</v>
+        <v>300</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>632</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="25" ht="18.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+        <v>640</v>
+      </c>
+      <c r="C24" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>187</v>
+        <v>309</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>636</v>
       </c>
-      <c r="C25" s="6" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="26" ht="18.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C25" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>187</v>
+        <v>309</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>652</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="27" ht="18.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+        <v>640</v>
+      </c>
+      <c r="C26" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>187</v>
+        <v>289</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>668</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>688</v>
-      </c>
-    </row>
-    <row r="28" ht="18.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+        <v>640</v>
+      </c>
+      <c r="C27" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>187</v>
+        <v>289</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>656</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="29" ht="18.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+        <v>644</v>
+      </c>
+      <c r="C28" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>196</v>
+        <v>321</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>648</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="30" ht="18.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+        <v>636</v>
+      </c>
+      <c r="C29" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>196</v>
+        <v>321</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>660</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="31" ht="18.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+        <v>640</v>
+      </c>
+      <c r="C30" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>196</v>
+        <v>330</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>664</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="32" ht="18.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+        <v>636</v>
+      </c>
+      <c r="C31" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>196</v>
+        <v>330</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>676</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>688</v>
-      </c>
-    </row>
-    <row r="33" ht="18.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+        <v>640</v>
+      </c>
+      <c r="C32" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>196</v>
+        <v>344</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>672</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="34" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+        <v>632</v>
+      </c>
+      <c r="C33" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>208</v>
+        <v>361</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>660</v>
+        <v>636</v>
       </c>
       <c r="C34" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="35" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>208</v>
+        <v>361</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>640</v>
       </c>
       <c r="C35" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>220</v>
+        <v>369</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="C36" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="37" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>220</v>
+        <v>369</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>668</v>
+        <v>640</v>
       </c>
       <c r="C37" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>220</v>
+        <v>369</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>656</v>
+        <v>644</v>
       </c>
       <c r="C38" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>220</v>
+        <v>351</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>680</v>
+        <v>636</v>
       </c>
       <c r="C39" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="C40" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>636</v>
+      </c>
+      <c r="C41" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>672</v>
-      </c>
-      <c r="C40" s="1">
+    <row r="42" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="C42" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="41" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>632</v>
-      </c>
-      <c r="C41" s="1">
+    <row r="43" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>636</v>
+      </c>
+      <c r="C43" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="44" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="C44" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>636</v>
+      </c>
+      <c r="C45" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="C46" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="47" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>636</v>
+      </c>
+      <c r="C47" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="48" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="C48" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="49" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>636</v>
+      </c>
+      <c r="C49" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>668</v>
-      </c>
-      <c r="C42" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="43" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>656</v>
-      </c>
-      <c r="C43" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="44" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>680</v>
-      </c>
-      <c r="C44" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="45" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>672</v>
-      </c>
-      <c r="C45" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="46" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>632</v>
-      </c>
-      <c r="C46" s="1">
+    <row r="50" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="C50" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="47" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>668</v>
-      </c>
-      <c r="C47" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="48" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>656</v>
-      </c>
-      <c r="C48" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="49" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>680</v>
-      </c>
-      <c r="C49" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="50" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>672</v>
-      </c>
-      <c r="C50" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="51" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>248</v>
+        <v>431</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>632</v>
+        <v>644</v>
       </c>
       <c r="C51" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="52" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>248</v>
+        <v>187</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>668</v>
+        <v>648</v>
       </c>
       <c r="C52" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="53" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="D52" t="s">
+        <v>690</v>
+      </c>
+      <c r="E52" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="53" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>248</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>656</v>
+        <v>648</v>
       </c>
       <c r="C53" s="1">
+        <v>2</v>
+      </c>
+      <c r="D53" t="s">
+        <v>692</v>
+      </c>
+      <c r="E53" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="54" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="C54" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="54" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>680</v>
-      </c>
-      <c r="C54" s="1">
+      <c r="D54" t="s">
+        <v>694</v>
+      </c>
+      <c r="E54" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="55" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="C55" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>672</v>
-      </c>
-      <c r="C55" s="1">
+      <c r="D55" t="s">
+        <v>696</v>
+      </c>
+      <c r="E55" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="56" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="C56" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="56" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>636</v>
-      </c>
-      <c r="C56" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D56" t="s">
+        <v>698</v>
+      </c>
+      <c r="E56" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="57" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>261</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>640</v>
+        <v>652</v>
       </c>
       <c r="C57" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="58" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="D57" t="s">
+        <v>700</v>
+      </c>
+      <c r="E57" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="58" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>652</v>
       </c>
       <c r="C58" s="1">
+        <v>2</v>
+      </c>
+      <c r="D58" t="s">
+        <v>702</v>
+      </c>
+      <c r="E58" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="59" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="C59" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="1" t="s">
+      <c r="D59" t="s">
+        <v>704</v>
+      </c>
+      <c r="E59" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="60" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="C60" s="1">
+        <v>4</v>
+      </c>
+      <c r="D60" t="s">
+        <v>706</v>
+      </c>
+      <c r="E60" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="61" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="C61" s="1">
+        <v>5</v>
+      </c>
+      <c r="D61" t="s">
+        <v>708</v>
+      </c>
+      <c r="E61" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="62" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="C62" s="1">
+        <v>6</v>
+      </c>
+      <c r="D62" t="s">
+        <v>708</v>
+      </c>
+      <c r="E62" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="63" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="C63" s="1">
+        <v>1</v>
+      </c>
+      <c r="D63" t="s">
+        <v>710</v>
+      </c>
+      <c r="E63" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="64" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="C64" s="1">
+        <v>2</v>
+      </c>
+      <c r="D64" t="s">
+        <v>712</v>
+      </c>
+      <c r="E64" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="65" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
         <v>261</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>668</v>
-      </c>
-      <c r="C59" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="60" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>656</v>
-      </c>
-      <c r="C60" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="61" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>636</v>
-      </c>
-      <c r="C61" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>640</v>
-      </c>
-      <c r="C62" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="63" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>652</v>
-      </c>
-      <c r="C63" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="64" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>668</v>
-      </c>
-      <c r="C64" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="65" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="1" t="s">
-        <v>271</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>656</v>
       </c>
       <c r="C65" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="66" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="D65" t="s">
+        <v>714</v>
+      </c>
+      <c r="E65" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="66" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>636</v>
+        <v>656</v>
       </c>
       <c r="C66" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="D66" t="s">
+        <v>716</v>
+      </c>
+      <c r="E66" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="67" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>279</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>640</v>
+        <v>656</v>
       </c>
       <c r="C67" s="1">
+        <v>5</v>
+      </c>
+      <c r="D67" t="s">
+        <v>718</v>
+      </c>
+      <c r="E67" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="68" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="C68" s="1">
+        <v>6</v>
+      </c>
+      <c r="D68" t="s">
+        <v>720</v>
+      </c>
+      <c r="E68" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="69" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="C69" s="1">
+        <v>7</v>
+      </c>
+      <c r="D69" t="s">
+        <v>720</v>
+      </c>
+      <c r="E69" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="70" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="C70" s="1">
+        <v>1</v>
+      </c>
+      <c r="D70" t="s">
+        <v>722</v>
+      </c>
+      <c r="E70" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="71" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="C71" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="68" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" s="1" t="s">
+      <c r="D71" t="s">
+        <v>724</v>
+      </c>
+      <c r="E71" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="72" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="C72" s="1">
+        <v>3</v>
+      </c>
+      <c r="D72" t="s">
+        <v>726</v>
+      </c>
+      <c r="E72" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="73" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="B68" s="1" t="s">
-        <v>652</v>
-      </c>
-      <c r="C68" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="69" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>668</v>
-      </c>
-      <c r="C69" s="1">
+      <c r="B73" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="C73" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="70" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>656</v>
-      </c>
-      <c r="C70" s="1">
+      <c r="D73" t="s">
+        <v>728</v>
+      </c>
+      <c r="E73" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="74" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="C74" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="71" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A71" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>636</v>
-      </c>
-      <c r="C71" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>640</v>
-      </c>
-      <c r="C72" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="73" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A73" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>652</v>
-      </c>
-      <c r="C73" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="74" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A74" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>668</v>
-      </c>
-      <c r="C74" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="75" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D74" t="s">
+        <v>730</v>
+      </c>
+      <c r="E74" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="75" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>300</v>
+        <v>248</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="C75" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="76" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="D75" t="s">
+        <v>730</v>
+      </c>
+      <c r="E75" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="76" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>309</v>
+        <v>230</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>636</v>
+        <v>664</v>
       </c>
       <c r="C76" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="77" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D76" t="s">
+        <v>732</v>
+      </c>
+      <c r="E76" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="77" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>309</v>
+        <v>220</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>640</v>
+        <v>664</v>
       </c>
       <c r="C77" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="78" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D77" t="s">
+        <v>734</v>
+      </c>
+      <c r="E77" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="78" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>309</v>
+        <v>261</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>652</v>
+        <v>664</v>
       </c>
       <c r="C78" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="79" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D78" t="s">
+        <v>736</v>
+      </c>
+      <c r="E78" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="79" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>309</v>
+        <v>271</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="C79" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="80" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D79" t="s">
+        <v>738</v>
+      </c>
+      <c r="E79" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="80" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>309</v>
+        <v>279</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>656</v>
+        <v>664</v>
       </c>
       <c r="C80" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="81" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D80" t="s">
+        <v>740</v>
+      </c>
+      <c r="E80" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="81" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>289</v>
+        <v>230</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>652</v>
+        <v>668</v>
       </c>
       <c r="C81" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="82" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D81" t="s">
+        <v>742</v>
+      </c>
+      <c r="E81" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="82" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>289</v>
+        <v>220</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>640</v>
+        <v>668</v>
       </c>
       <c r="C82" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="83" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D82" t="s">
+        <v>744</v>
+      </c>
+      <c r="E82" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="83" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>289</v>
+        <v>261</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>644</v>
+        <v>668</v>
       </c>
       <c r="C83" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D83" t="s">
+        <v>746</v>
+      </c>
+      <c r="E83" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="84" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>648</v>
+        <v>668</v>
       </c>
       <c r="C84" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="85" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D84" t="s">
+        <v>748</v>
+      </c>
+      <c r="E84" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="85" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>656</v>
+        <v>668</v>
       </c>
       <c r="C85" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="86" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D85" t="s">
+        <v>749</v>
+      </c>
+      <c r="E85" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="86" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>321</v>
+        <v>230</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>636</v>
+        <v>672</v>
       </c>
       <c r="C86" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="87" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D86" t="s">
+        <v>751</v>
+      </c>
+      <c r="E86" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="87" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>321</v>
+        <v>220</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>640</v>
+        <v>672</v>
       </c>
       <c r="C87" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="88" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D87" t="s">
+        <v>753</v>
+      </c>
+      <c r="E87" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="88" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>321</v>
+        <v>248</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>652</v>
+        <v>672</v>
       </c>
       <c r="C88" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="89" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D88" t="s">
+        <v>755</v>
+      </c>
+      <c r="E88" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="89" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>330</v>
+        <v>271</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>636</v>
+        <v>672</v>
       </c>
       <c r="C89" s="1">
+        <v>4</v>
+      </c>
+      <c r="D89" t="s">
+        <v>757</v>
+      </c>
+      <c r="E89" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="90" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>672</v>
+      </c>
+      <c r="C90" s="1">
+        <v>5</v>
+      </c>
+      <c r="D90" t="s">
+        <v>759</v>
+      </c>
+      <c r="E90" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="91" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>676</v>
+      </c>
+      <c r="C91" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="90" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A90" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>640</v>
-      </c>
-      <c r="C90" s="1">
+      <c r="D91" t="s">
+        <v>761</v>
+      </c>
+      <c r="E91" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="92" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>676</v>
+      </c>
+      <c r="C92" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="91" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A91" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>652</v>
-      </c>
-      <c r="C91" s="1">
+      <c r="D92" t="s">
+        <v>763</v>
+      </c>
+      <c r="E92" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="93" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>676</v>
+      </c>
+      <c r="C93" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A92" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>668</v>
-      </c>
-      <c r="C92" s="1">
+      <c r="D93" t="s">
+        <v>765</v>
+      </c>
+      <c r="E93" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="94" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>676</v>
+      </c>
+      <c r="C94" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="93" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A93" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="B93" s="1" t="s">
-        <v>668</v>
-      </c>
-      <c r="C93" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="94" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A94" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="B94" s="1" t="s">
-        <v>632</v>
-      </c>
-      <c r="C94" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="95" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D94" t="s">
+        <v>767</v>
+      </c>
+      <c r="E94" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="95" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>344</v>
+        <v>248</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="C95" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="96" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+      <c r="D95" t="s">
+        <v>767</v>
+      </c>
+      <c r="E95" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="96" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>344</v>
+        <v>279</v>
       </c>
       <c r="B96" s="1" t="s">
+        <v>676</v>
+      </c>
+      <c r="C96" s="1">
+        <v>6</v>
+      </c>
+      <c r="D96" t="s">
+        <v>769</v>
+      </c>
+      <c r="E96" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="97" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B97" s="1" t="s">
         <v>680</v>
-      </c>
-      <c r="C96" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="97" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A97" s="1" t="s">
-        <v>361</v>
-      </c>
-      <c r="B97" s="1" t="s">
-        <v>636</v>
       </c>
       <c r="C97" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="98" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D97" t="s">
+        <v>771</v>
+      </c>
+      <c r="E97" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="98" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>361</v>
+        <v>261</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>640</v>
+        <v>680</v>
       </c>
       <c r="C98" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="99" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D98" t="s">
+        <v>773</v>
+      </c>
+      <c r="E98" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="99" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>361</v>
+        <v>279</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>652</v>
+        <v>680</v>
       </c>
       <c r="C99" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="100" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A100" s="1" t="s">
-        <v>369</v>
-      </c>
-      <c r="B100" s="1" t="s">
-        <v>636</v>
-      </c>
-      <c r="C100" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="101" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A101" s="1" t="s">
-        <v>369</v>
-      </c>
-      <c r="B101" s="1" t="s">
-        <v>640</v>
-      </c>
-      <c r="C101" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="102" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A102" s="1" t="s">
-        <v>369</v>
-      </c>
-      <c r="B102" s="1" t="s">
-        <v>652</v>
-      </c>
-      <c r="C102" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="103" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A103" s="1" t="s">
-        <v>369</v>
-      </c>
-      <c r="B103" s="1" t="s">
-        <v>644</v>
-      </c>
-      <c r="C103" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="104" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A104" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="B104" s="1" t="s">
-        <v>636</v>
-      </c>
-      <c r="C104" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="105" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A105" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="B105" s="1" t="s">
-        <v>640</v>
-      </c>
-      <c r="C105" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="106" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A106" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="B106" s="1" t="s">
-        <v>652</v>
-      </c>
-      <c r="C106" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="107" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A107" s="1" t="s">
-        <v>379</v>
-      </c>
-      <c r="B107" s="1" t="s">
-        <v>636</v>
-      </c>
-      <c r="C107" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="108" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A108" s="1" t="s">
-        <v>379</v>
-      </c>
-      <c r="B108" s="1" t="s">
-        <v>640</v>
-      </c>
-      <c r="C108" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="109" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A109" s="1" t="s">
-        <v>379</v>
-      </c>
-      <c r="B109" s="1" t="s">
-        <v>652</v>
-      </c>
-      <c r="C109" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="110" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A110" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="B110" s="1" t="s">
-        <v>636</v>
-      </c>
-      <c r="C110" s="1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="111" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A111" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="B111" s="1" t="s">
-        <v>640</v>
-      </c>
-      <c r="C111" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="112" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A112" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="B112" s="1" t="s">
-        <v>652</v>
-      </c>
-      <c r="C112" s="1">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="113" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A113" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="B113" s="1" t="s">
-        <v>636</v>
-      </c>
-      <c r="C113" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="114" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A114" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="B114" s="1" t="s">
-        <v>640</v>
-      </c>
-      <c r="C114" s="1">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="115" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A115" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="B115" s="1" t="s">
-        <v>652</v>
-      </c>
-      <c r="C115" s="1">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="116" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A116" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="B116" s="1" t="s">
-        <v>636</v>
-      </c>
-      <c r="C116" s="1">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="117" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A117" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="B117" s="1" t="s">
-        <v>640</v>
-      </c>
-      <c r="C117" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="118" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A118" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="B118" s="1" t="s">
-        <v>652</v>
-      </c>
-      <c r="C118" s="1">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="119" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A119" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="B119" s="1" t="s">
-        <v>636</v>
-      </c>
-      <c r="C119" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="120" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A120" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="B120" s="1" t="s">
-        <v>640</v>
-      </c>
-      <c r="C120" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="121" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A121" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="B121" s="1" t="s">
-        <v>652</v>
-      </c>
-      <c r="C121" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="122" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A122" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="B122" s="1" t="s">
-        <v>644</v>
-      </c>
-      <c r="C122" s="1">
-        <v>1</v>
-      </c>
+      <c r="D99" t="s">
+        <v>775</v>
+      </c>
+      <c r="E99" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="100" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100" s="1"/>
+      <c r="B100" s="1"/>
+      <c r="C100" s="1"/>
+    </row>
+    <row r="101" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A101" s="1"/>
+      <c r="B101" s="1"/>
+      <c r="C101" s="1"/>
+    </row>
+    <row r="102" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A102" s="1"/>
+      <c r="B102" s="1"/>
+      <c r="C102" s="1"/>
+    </row>
+    <row r="103" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A103" s="1"/>
+      <c r="B103" s="1"/>
+      <c r="C103" s="1"/>
+    </row>
+    <row r="104" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A104" s="1"/>
+      <c r="B104" s="1"/>
+      <c r="C104" s="1"/>
+    </row>
+    <row r="105" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A105" s="1"/>
+      <c r="B105" s="1"/>
+      <c r="C105" s="1"/>
+    </row>
+    <row r="106" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A106" s="1"/>
+      <c r="B106" s="1"/>
+      <c r="C106" s="1"/>
+    </row>
+    <row r="107" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A107" s="1"/>
+      <c r="B107" s="1"/>
+      <c r="C107" s="1"/>
+    </row>
+    <row r="108" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A108" s="1"/>
+      <c r="B108" s="1"/>
+      <c r="C108" s="1"/>
+    </row>
+    <row r="109" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A109" s="1"/>
+      <c r="B109" s="1"/>
+      <c r="C109" s="1"/>
+    </row>
+    <row r="110" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A110" s="1"/>
+      <c r="B110" s="1"/>
+      <c r="C110" s="1"/>
+    </row>
+    <row r="111" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A111" s="1"/>
+      <c r="B111" s="1"/>
+      <c r="C111" s="1"/>
+    </row>
+    <row r="112" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A112" s="1"/>
+      <c r="B112" s="1"/>
+      <c r="C112" s="1"/>
+    </row>
+    <row r="113" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A113" s="1"/>
+      <c r="B113" s="1"/>
+      <c r="C113" s="1"/>
+    </row>
+    <row r="114" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A114" s="1"/>
+      <c r="B114" s="1"/>
+      <c r="C114" s="1"/>
+    </row>
+    <row r="115" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A115" s="1"/>
+      <c r="B115" s="1"/>
+      <c r="C115" s="1"/>
+    </row>
+    <row r="116" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A116" s="1"/>
+      <c r="B116" s="1"/>
+      <c r="C116" s="1"/>
+    </row>
+    <row r="117" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A117" s="1"/>
+      <c r="B117" s="1"/>
+      <c r="C117" s="1"/>
+    </row>
+    <row r="118" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A118" s="1"/>
+      <c r="B118" s="1"/>
+      <c r="C118" s="1"/>
+    </row>
+    <row r="119" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A119" s="1"/>
+      <c r="B119" s="1"/>
+      <c r="C119" s="1"/>
+    </row>
+    <row r="120" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A120" s="1"/>
+      <c r="B120" s="1"/>
+      <c r="C120" s="1"/>
+    </row>
+    <row r="121" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A121" s="1"/>
+      <c r="B121" s="1"/>
+      <c r="C121" s="1"/>
+    </row>
+    <row r="122" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A122" s="1"/>
+      <c r="B122" s="1"/>
+      <c r="C122" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -14250,16 +14670,16 @@
         <v>435</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>690</v>
+        <v>777</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>691</v>
+        <v>778</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>692</v>
+        <v>779</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>693</v>
+        <v>780</v>
       </c>
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -14369,21 +14789,21 @@
         <v>196</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>694</v>
+        <v>781</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>695</v>
+        <v>782</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>696</v>
+        <v>783</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>697</v>
+        <v>784</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>698</v>
+        <v>785</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>136</v>
@@ -14403,10 +14823,10 @@
         <v>220</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>699</v>
+        <v>786</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>700</v>
+        <v>787</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>455</v>
@@ -14417,10 +14837,10 @@
         <v>230</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>701</v>
+        <v>788</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>702</v>
+        <v>789</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>472</v>
@@ -14431,13 +14851,13 @@
         <v>248</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>703</v>
+        <v>790</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>704</v>
+        <v>791</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>705</v>
+        <v>792</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -14445,16 +14865,16 @@
         <v>261</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>706</v>
+        <v>793</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>707</v>
+        <v>794</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>708</v>
+        <v>795</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>709</v>
+        <v>796</v>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -14462,10 +14882,10 @@
         <v>271</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>710</v>
+        <v>797</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>711</v>
+        <v>798</v>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -14473,7 +14893,7 @@
         <v>279</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>712</v>
+        <v>799</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>547</v>
@@ -14484,13 +14904,13 @@
         <v>289</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>713</v>
+        <v>800</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>714</v>
+        <v>801</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>715</v>
+        <v>802</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>557</v>
@@ -14509,10 +14929,10 @@
         <v>309</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>716</v>
+        <v>803</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>717</v>
+        <v>804</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -14520,7 +14940,7 @@
         <v>351</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>718</v>
+        <v>805</v>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -14528,7 +14948,7 @@
         <v>379</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>719</v>
+        <v>806</v>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -14536,7 +14956,7 @@
         <v>388</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>720</v>
+        <v>807</v>
       </c>
     </row>
   </sheetData>

--- a/MAX-SEAL-main/catalog/MAXSEAL_CATALOG.xlsx
+++ b/MAX-SEAL-main/catalog/MAXSEAL_CATALOG.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2714" uniqueCount="1147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2739" uniqueCount="1151">
   <si>
     <t>Id</t>
   </si>
@@ -2904,51 +2904,6 @@
     <t>/assets/maxseal/docs/Flo-Tite 2023 FINAL General Price Guide_12_20_2022 COMPRESSED.pdf</t>
   </si>
   <si>
-    <t>d28</t>
-  </si>
-  <si>
-    <t>tri-max-series-updated</t>
-  </si>
-  <si>
-    <t>Tri-Max Series Technical Bulletin — Updated (500-25-Max-Seal-HP-Butterfly-Valve-TB-2025-V25-final-new.pdf)</t>
-  </si>
-  <si>
-    <t>7.8 MB</t>
-  </si>
-  <si>
-    <t>/assets/maxseal/docs/500-25-Max-Seal-HP-Butterfly-Valve-TB-2025-V25-final-new.pdf</t>
-  </si>
-  <si>
-    <t>d29</t>
-  </si>
-  <si>
-    <t>hi-tek-series-alt</t>
-  </si>
-  <si>
-    <t>Hi-Tek Series Catalog — Alternate (502-24-HiTek-Double-Triple-Offsets_v01-COMPRESSED.pdf)</t>
-  </si>
-  <si>
-    <t>6.2 MB</t>
-  </si>
-  <si>
-    <t>/assets/maxseal/docs/502-24-HiTek-Double-Triple-Offsets_v01-COMPRESSED.pdf</t>
-  </si>
-  <si>
-    <t>d30</t>
-  </si>
-  <si>
-    <t>cryogenic-series-alt</t>
-  </si>
-  <si>
-    <t>Cryogenic Series Catalog — Alternate (154-23 CRYOGENIC BF Valve Catalog Low-temperature V100L200L_20220409_MAXSEAL R2 COMPRESSED (1).pdf)</t>
-  </si>
-  <si>
-    <t>11.0 MB</t>
-  </si>
-  <si>
-    <t>/assets/maxseal/docs/154-23 CRYOGENIC BF Valve Catalog Low-temperature V100L200L_20220409_MAXSEAL R2 COMPRESSED (1).pdf</t>
-  </si>
-  <si>
     <t>d31</t>
   </si>
   <si>
@@ -2998,6 +2953,63 @@
   </si>
   <si>
     <t>/assets/maxseal/docs/MT-MaxSeal_Performance_Series_Upgrade_Bulletin_R6.pdf</t>
+  </si>
+  <si>
+    <t>d34</t>
+  </si>
+  <si>
+    <t>chem-flo-v02</t>
+  </si>
+  <si>
+    <t>Chem-Flo Series Catalog — v02 (110-22 Chem-Flo_v02 MaxSeal COMPRESSED.pdf)</t>
+  </si>
+  <si>
+    <t>/assets/maxseal/docs/110-22 Chem-Flo_v02 MaxSeal COMPRESSED.pdf</t>
+  </si>
+  <si>
+    <t>d35</t>
+  </si>
+  <si>
+    <t>bfv-bolting</t>
+  </si>
+  <si>
+    <t>Butterfly Valve Bolting Torque Bulletin (608-19 BFV Bolting COMPRESSED.pdf)</t>
+  </si>
+  <si>
+    <t>0.5 MB</t>
+  </si>
+  <si>
+    <t>/assets/maxseal/docs/608-19 BFV Bolting COMPRESSED.pdf</t>
+  </si>
+  <si>
+    <t>d36</t>
+  </si>
+  <si>
+    <t>valve-body-selection-guide</t>
+  </si>
+  <si>
+    <t>Valve Body Selection Guide (610-25 VALVE BODY SELECTION GUIDE Compressed.pdf)</t>
+  </si>
+  <si>
+    <t>0.3 MB</t>
+  </si>
+  <si>
+    <t>/assets/maxseal/docs/610-25 VALVE BODY SELECTION GUIDE Compressed.pdf</t>
+  </si>
+  <si>
+    <t>d37</t>
+  </si>
+  <si>
+    <t>terms-and-conditions</t>
+  </si>
+  <si>
+    <t>Terms and Conditions</t>
+  </si>
+  <si>
+    <t>Terms and Conditions (100-19 Term and Conditions_2019 COMPRESSED.pdf)</t>
+  </si>
+  <si>
+    <t>/assets/maxseal/docs/100-19 Term and Conditions_2019 COMPRESSED.pdf</t>
   </si>
   <si>
     <t>Effective</t>
@@ -3956,7 +3968,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:M34"/>
+  <dimension ref="A1:M38"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.453125"/>
   <cols>
     <col min="1" max="1" width="8.01" style="1" customWidth="1"/>
@@ -4012,7 +4024,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="2" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" ht="18.75" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>817</v>
       </c>
@@ -4050,7 +4062,7 @@
         <v>826</v>
       </c>
     </row>
-    <row r="3" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" ht="18.75" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>827</v>
       </c>
@@ -4066,6 +4078,7 @@
       <c r="E3" s="6" t="s">
         <v>150</v>
       </c>
+      <c r="F3" s="1"/>
       <c r="G3" s="6" t="s">
         <v>829</v>
       </c>
@@ -4078,11 +4091,12 @@
       <c r="J3" s="1" t="s">
         <v>832</v>
       </c>
+      <c r="K3" s="1"/>
       <c r="L3" t="s">
         <v>619</v>
       </c>
     </row>
-    <row r="4" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" ht="18.75" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>833</v>
       </c>
@@ -4098,6 +4112,7 @@
       <c r="E4" s="6" t="s">
         <v>137</v>
       </c>
+      <c r="F4" s="1"/>
       <c r="G4" s="6" t="s">
         <v>835</v>
       </c>
@@ -4107,11 +4122,13 @@
       <c r="I4" s="6" t="s">
         <v>837</v>
       </c>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
       <c r="L4" t="s">
         <v>826</v>
       </c>
     </row>
-    <row r="5" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" ht="18.75" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>838</v>
       </c>
@@ -4127,6 +4144,7 @@
       <c r="E5" s="6" t="s">
         <v>160</v>
       </c>
+      <c r="F5" s="1"/>
       <c r="G5" s="6" t="s">
         <v>841</v>
       </c>
@@ -4139,11 +4157,12 @@
       <c r="J5" s="1" t="s">
         <v>844</v>
       </c>
+      <c r="K5" s="1"/>
       <c r="L5" t="s">
         <v>619</v>
       </c>
     </row>
-    <row r="6" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" ht="18.75" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>845</v>
       </c>
@@ -4159,6 +4178,7 @@
       <c r="E6" s="6" t="s">
         <v>187</v>
       </c>
+      <c r="F6" s="1"/>
       <c r="G6" s="6" t="s">
         <v>849</v>
       </c>
@@ -4168,11 +4188,13 @@
       <c r="I6" s="6" t="s">
         <v>851</v>
       </c>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
       <c r="L6" t="s">
         <v>826</v>
       </c>
     </row>
-    <row r="7" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" ht="18.75" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>852</v>
       </c>
@@ -4188,6 +4210,7 @@
       <c r="E7" s="6" t="s">
         <v>173</v>
       </c>
+      <c r="F7" s="1"/>
       <c r="G7" s="6" t="s">
         <v>854</v>
       </c>
@@ -4200,11 +4223,12 @@
       <c r="J7" s="1" t="s">
         <v>857</v>
       </c>
+      <c r="K7" s="1"/>
       <c r="L7" t="s">
         <v>619</v>
       </c>
     </row>
-    <row r="8" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" ht="18.75" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>858</v>
       </c>
@@ -4220,6 +4244,7 @@
       <c r="E8" s="6" t="s">
         <v>120</v>
       </c>
+      <c r="F8" s="1"/>
       <c r="G8" s="6" t="s">
         <v>821</v>
       </c>
@@ -4229,11 +4254,13 @@
       <c r="I8" s="6" t="s">
         <v>688</v>
       </c>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
       <c r="L8" t="s">
         <v>826</v>
       </c>
     </row>
-    <row r="9" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" ht="18.75" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>863</v>
       </c>
@@ -4249,6 +4276,7 @@
       <c r="E9" s="6" t="s">
         <v>867</v>
       </c>
+      <c r="F9" s="1"/>
       <c r="G9" s="6" t="s">
         <v>829</v>
       </c>
@@ -4258,11 +4286,13 @@
       <c r="I9" s="6" t="s">
         <v>869</v>
       </c>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
       <c r="L9" t="s">
         <v>826</v>
       </c>
     </row>
-    <row r="10" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" ht="18.75" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
         <v>870</v>
       </c>
@@ -4278,6 +4308,7 @@
       <c r="E10" s="6" t="s">
         <v>867</v>
       </c>
+      <c r="F10" s="1"/>
       <c r="G10" s="6" t="s">
         <v>835</v>
       </c>
@@ -4287,11 +4318,13 @@
       <c r="I10" s="6" t="s">
         <v>875</v>
       </c>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
       <c r="L10" t="s">
         <v>826</v>
       </c>
     </row>
-    <row r="11" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" ht="18.75" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
         <v>876</v>
       </c>
@@ -4307,6 +4340,7 @@
       <c r="E11" s="6" t="s">
         <v>160</v>
       </c>
+      <c r="F11" s="1"/>
       <c r="G11" s="6" t="s">
         <v>841</v>
       </c>
@@ -4316,11 +4350,13 @@
       <c r="I11" s="6" t="s">
         <v>881</v>
       </c>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
       <c r="L11" t="s">
         <v>826</v>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>882</v>
       </c>
@@ -4336,14 +4372,19 @@
       <c r="E12" s="1" t="s">
         <v>220</v>
       </c>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
       <c r="J12" s="1" t="s">
         <v>885</v>
       </c>
+      <c r="K12" s="1"/>
       <c r="L12" t="s">
         <v>619</v>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" ht="15" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>886</v>
       </c>
@@ -4359,14 +4400,19 @@
       <c r="E13" s="1" t="s">
         <v>230</v>
       </c>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
       <c r="J13" s="1" t="s">
         <v>889</v>
       </c>
+      <c r="K13" s="1"/>
       <c r="L13" t="s">
         <v>619</v>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>890</v>
       </c>
@@ -4382,14 +4428,19 @@
       <c r="E14" s="1" t="s">
         <v>248</v>
       </c>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
       <c r="J14" s="1" t="s">
         <v>893</v>
       </c>
+      <c r="K14" s="1"/>
       <c r="L14" t="s">
-        <v>826</v>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>894</v>
       </c>
@@ -4405,14 +4456,19 @@
       <c r="E15" s="1" t="s">
         <v>187</v>
       </c>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
       <c r="J15" s="1" t="s">
         <v>897</v>
       </c>
+      <c r="K15" s="1"/>
       <c r="L15" t="s">
         <v>619</v>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>898</v>
       </c>
@@ -4428,14 +4484,19 @@
       <c r="E16" s="1" t="s">
         <v>261</v>
       </c>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
       <c r="J16" s="1" t="s">
         <v>901</v>
       </c>
+      <c r="K16" s="1"/>
       <c r="L16" t="s">
         <v>619</v>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" ht="15" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>902</v>
       </c>
@@ -4451,14 +4512,19 @@
       <c r="E17" s="1" t="s">
         <v>271</v>
       </c>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
       <c r="J17" s="1" t="s">
         <v>905</v>
       </c>
+      <c r="K17" s="1"/>
       <c r="L17" t="s">
         <v>619</v>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>906</v>
       </c>
@@ -4474,14 +4540,19 @@
       <c r="E18" s="1" t="s">
         <v>279</v>
       </c>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
       <c r="J18" s="1" t="s">
         <v>909</v>
       </c>
+      <c r="K18" s="1"/>
       <c r="L18" t="s">
         <v>619</v>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" ht="15" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>910</v>
       </c>
@@ -4497,14 +4568,19 @@
       <c r="E19" s="1" t="s">
         <v>289</v>
       </c>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
       <c r="J19" s="1" t="s">
         <v>913</v>
       </c>
+      <c r="K19" s="1"/>
       <c r="L19" t="s">
         <v>619</v>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>914</v>
       </c>
@@ -4520,14 +4596,19 @@
       <c r="E20" s="1" t="s">
         <v>300</v>
       </c>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
       <c r="J20" s="1" t="s">
         <v>917</v>
       </c>
+      <c r="K20" s="1"/>
       <c r="L20" t="s">
         <v>619</v>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" ht="15" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>918</v>
       </c>
@@ -4543,14 +4624,19 @@
       <c r="E21" s="1" t="s">
         <v>309</v>
       </c>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
       <c r="J21" s="1" t="s">
         <v>921</v>
       </c>
+      <c r="K21" s="1"/>
       <c r="L21" t="s">
-        <v>826</v>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>922</v>
       </c>
@@ -4566,14 +4652,19 @@
       <c r="E22" s="1" t="s">
         <v>240</v>
       </c>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
       <c r="J22" s="1" t="s">
         <v>925</v>
       </c>
+      <c r="K22" s="1"/>
       <c r="L22" t="s">
         <v>619</v>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" ht="15" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>926</v>
       </c>
@@ -4592,14 +4683,18 @@
       <c r="F23" s="1" t="s">
         <v>321</v>
       </c>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
       <c r="J23" s="1" t="s">
         <v>929</v>
       </c>
+      <c r="K23" s="1"/>
       <c r="L23" t="s">
-        <v>826</v>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>930</v>
       </c>
@@ -4615,14 +4710,19 @@
       <c r="E24" s="1" t="s">
         <v>208</v>
       </c>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
       <c r="J24" s="1" t="s">
         <v>933</v>
       </c>
+      <c r="K24" s="1"/>
       <c r="L24" t="s">
-        <v>826</v>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>934</v>
       </c>
@@ -4641,14 +4741,18 @@
       <c r="F25" s="1" t="s">
         <v>937</v>
       </c>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
       <c r="J25" s="1" t="s">
         <v>938</v>
       </c>
+      <c r="K25" s="1"/>
       <c r="L25" t="s">
         <v>619</v>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>939</v>
       </c>
@@ -4667,14 +4771,18 @@
       <c r="F26" s="1" t="s">
         <v>942</v>
       </c>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
       <c r="J26" s="1" t="s">
         <v>943</v>
       </c>
+      <c r="K26" s="1"/>
       <c r="L26" t="s">
         <v>619</v>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" ht="15" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>944</v>
       </c>
@@ -4693,14 +4801,18 @@
       <c r="F27" s="1" t="s">
         <v>947</v>
       </c>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
       <c r="J27" s="1" t="s">
         <v>948</v>
       </c>
+      <c r="K27" s="1"/>
       <c r="L27" t="s">
         <v>826</v>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>949</v>
       </c>
@@ -4716,20 +4828,23 @@
       <c r="E28" s="1" t="s">
         <v>867</v>
       </c>
+      <c r="F28" s="1"/>
       <c r="G28" s="1" t="s">
         <v>952</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>953</v>
       </c>
+      <c r="I28" s="1"/>
       <c r="J28" s="1" t="s">
         <v>954</v>
       </c>
+      <c r="K28" s="1"/>
       <c r="L28" t="s">
         <v>826</v>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" ht="15" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>955</v>
       </c>
@@ -4737,207 +4852,323 @@
         <v>956</v>
       </c>
       <c r="C29" s="1" t="s">
+        <v>957</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>958</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>959</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>959</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>960</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>959</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>961</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>959</v>
+      </c>
+      <c r="L29" t="s">
+        <v>826</v>
+      </c>
+      <c r="M29" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>962</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>963</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>957</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>964</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>959</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>959</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>965</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>959</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>966</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>959</v>
+      </c>
+      <c r="L30" t="s">
+        <v>826</v>
+      </c>
+      <c r="M30" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>967</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>968</v>
+      </c>
+      <c r="C31" s="1" t="s">
         <v>860</v>
       </c>
-      <c r="D29" s="1" t="s">
-        <v>957</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>952</v>
-      </c>
-      <c r="H29" s="1" t="s">
-        <v>958</v>
-      </c>
-      <c r="J29" s="1" t="s">
+      <c r="D31" s="1" t="s">
+        <v>969</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="F31" s="1" t="s">
         <v>959</v>
       </c>
-      <c r="L29" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="30" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>960</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>961</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>818</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>962</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>952</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>963</v>
-      </c>
-      <c r="J30" s="1" t="s">
-        <v>964</v>
-      </c>
-      <c r="L30" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="31" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>965</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>966</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>818</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>967</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>309</v>
-      </c>
       <c r="G31" s="1" t="s">
-        <v>952</v>
+        <v>959</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>968</v>
+        <v>970</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>959</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>969</v>
+        <v>971</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>959</v>
       </c>
       <c r="L31" t="s">
         <v>826</v>
       </c>
+      <c r="M31" t="s">
+        <v>619</v>
+      </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>972</v>
+        <v>818</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>220</v>
+        <v>187</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>974</v>
+        <v>959</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>974</v>
+        <v>959</v>
       </c>
       <c r="H32" s="1" t="s">
+        <v>868</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>959</v>
+      </c>
+      <c r="J32" s="1" t="s">
         <v>975</v>
       </c>
-      <c r="I32" s="1" t="s">
-        <v>974</v>
-      </c>
-      <c r="J32" s="1" t="s">
-        <v>976</v>
-      </c>
       <c r="K32" s="1" t="s">
-        <v>974</v>
+        <v>959</v>
       </c>
       <c r="L32" t="s">
-        <v>826</v>
+        <v>619</v>
       </c>
       <c r="M32" t="s">
-        <v>619</v>
+        <v>959</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
+        <v>976</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="C33" s="1" t="s">
+        <v>860</v>
+      </c>
+      <c r="D33" s="1" t="s">
         <v>978</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>972</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>979</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>867</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>974</v>
+        <v>959</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>974</v>
+        <v>959</v>
       </c>
       <c r="H33" s="1" t="s">
+        <v>979</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>959</v>
+      </c>
+      <c r="J33" s="1" t="s">
         <v>980</v>
       </c>
-      <c r="I33" s="1" t="s">
-        <v>974</v>
-      </c>
-      <c r="J33" s="1" t="s">
-        <v>981</v>
-      </c>
       <c r="K33" s="1" t="s">
-        <v>974</v>
+        <v>959</v>
       </c>
       <c r="L33" t="s">
-        <v>826</v>
+        <v>619</v>
       </c>
       <c r="M33" t="s">
-        <v>619</v>
+        <v>959</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
+        <v>981</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="C34" s="1" t="s">
+        <v>847</v>
+      </c>
+      <c r="D34" s="1" t="s">
         <v>983</v>
       </c>
-      <c r="C34" s="1" t="s">
-        <v>860</v>
-      </c>
-      <c r="D34" s="1" t="s">
+      <c r="E34" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>959</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>959</v>
+      </c>
+      <c r="H34" s="1" t="s">
         <v>984</v>
       </c>
-      <c r="E34" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>974</v>
-      </c>
-      <c r="G34" s="1" t="s">
-        <v>974</v>
-      </c>
-      <c r="H34" s="1" t="s">
+      <c r="I34" s="1" t="s">
+        <v>959</v>
+      </c>
+      <c r="J34" s="1" t="s">
         <v>985</v>
       </c>
-      <c r="I34" s="1" t="s">
-        <v>974</v>
-      </c>
-      <c r="J34" s="1" t="s">
+      <c r="K34" s="1" t="s">
+        <v>959</v>
+      </c>
+      <c r="L34" t="s">
+        <v>619</v>
+      </c>
+      <c r="M34" t="s">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
         <v>986</v>
       </c>
-      <c r="K34" s="1" t="s">
-        <v>974</v>
-      </c>
-      <c r="L34" t="s">
-        <v>826</v>
-      </c>
-      <c r="M34" t="s">
+      <c r="B35" s="1" t="s">
+        <v>987</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>988</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>989</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>959</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>959</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>959</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>990</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>959</v>
+      </c>
+      <c r="L35" t="s">
         <v>619</v>
       </c>
+      <c r="M35" t="s">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A36" s="1"/>
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
+      <c r="J36" s="1"/>
+      <c r="K36" s="1"/>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A37" s="1"/>
+      <c r="B37" s="1"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="1"/>
+      <c r="J37" s="1"/>
+      <c r="K37" s="1"/>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A38" s="1"/>
+      <c r="B38" s="1"/>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1"/>
+      <c r="J38" s="1"/>
+      <c r="K38" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4973,16 +5204,16 @@
         <v>435</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>987</v>
+        <v>991</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>988</v>
+        <v>992</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>989</v>
+        <v>993</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>990</v>
+        <v>994</v>
       </c>
       <c r="H1" s="4" t="s">
         <v>811</v>
@@ -5003,28 +5234,28 @@
     </row>
     <row r="3" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>991</v>
+        <v>995</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>992</v>
+        <v>996</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>867</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>993</v>
+        <v>997</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>993</v>
+        <v>997</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>994</v>
+        <v>998</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>995</v>
+        <v>999</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>996</v>
+        <v>1000</v>
       </c>
       <c r="I3" t="s">
         <v>948</v>
@@ -5032,25 +5263,25 @@
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>997</v>
+        <v>1001</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>998</v>
+        <v>1002</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>867</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>1003</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>1004</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>1005</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>999</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>1000</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>1001</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>995</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>953</v>
@@ -5095,63 +5326,63 @@
         <v>437</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>1002</v>
+        <v>1006</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>1003</v>
+        <v>1007</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>1004</v>
+        <v>1008</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>1005</v>
+        <v>1009</v>
       </c>
       <c r="G1" s="4" t="s">
         <v>812</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>1006</v>
+        <v>1010</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>1007</v>
+        <v>1011</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>1008</v>
+        <v>1012</v>
       </c>
       <c r="K1" s="4" t="s">
         <v>810</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>987</v>
+        <v>991</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>988</v>
+        <v>992</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>990</v>
+        <v>994</v>
       </c>
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>1009</v>
+        <v>1013</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>818</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>1010</v>
+        <v>1014</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>1011</v>
+        <v>1015</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>1012</v>
+        <v>1016</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>1013</v>
+        <v>1017</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>1014</v>
+        <v>1018</v>
       </c>
       <c r="H2" s="6" t="s">
         <v>32</v>
@@ -5159,22 +5390,22 @@
     </row>
     <row r="3" ht="18.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>1015</v>
+        <v>1019</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>1016</v>
+        <v>1020</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>1017</v>
+        <v>1021</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>1018</v>
+        <v>1022</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>972</v>
+        <v>957</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>1019</v>
+        <v>1023</v>
       </c>
       <c r="K3" s="6" t="s">
         <v>829</v>
@@ -5182,25 +5413,25 @@
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>1020</v>
+        <v>1024</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>1021</v>
+        <v>1025</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>1022</v>
+        <v>1026</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>1023</v>
+        <v>1027</v>
       </c>
       <c r="L4" s="6" t="s">
-        <v>1024</v>
+        <v>1028</v>
       </c>
       <c r="M4" s="6" t="s">
-        <v>1025</v>
+        <v>1029</v>
       </c>
       <c r="N4" s="6" t="s">
-        <v>1026</v>
+        <v>1030</v>
       </c>
     </row>
   </sheetData>
@@ -5227,7 +5458,7 @@
         <v>435</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>1027</v>
+        <v>1031</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>6</v>
@@ -6147,45 +6378,45 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>1028</v>
+        <v>1032</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>1029</v>
+        <v>1033</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>1030</v>
+        <v>1034</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>1031</v>
+        <v>1035</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>1033</v>
+        <v>1037</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>1034</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>1035</v>
+        <v>1039</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>1036</v>
+        <v>1040</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>1037</v>
+        <v>1041</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>1039</v>
+        <v>1043</v>
       </c>
       <c r="G2" s="6" t="s">
         <v>120</v>
@@ -6193,22 +6424,22 @@
     </row>
     <row r="3" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>1040</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>1036</v>
-      </c>
       <c r="C3" s="6" t="s">
-        <v>1041</v>
+        <v>1045</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>41</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>1042</v>
+        <v>1046</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>1039</v>
+        <v>1043</v>
       </c>
       <c r="G3" s="6" t="s">
         <v>137</v>
@@ -6216,22 +6447,22 @@
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>1048</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>1049</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>1050</v>
+      </c>
+      <c r="F4" s="6" t="s">
         <v>1043</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>1036</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>1044</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>1045</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>1046</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>1039</v>
       </c>
       <c r="G4" s="6" t="s">
         <v>150</v>
@@ -6239,22 +6470,22 @@
     </row>
     <row r="5" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>1047</v>
+        <v>1051</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>1036</v>
+        <v>1040</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>1048</v>
+        <v>1052</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>1049</v>
+        <v>1053</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>1050</v>
+        <v>1054</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>1039</v>
+        <v>1043</v>
       </c>
       <c r="G5" s="6" t="s">
         <v>160</v>
@@ -6262,22 +6493,22 @@
     </row>
     <row r="6" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>1051</v>
+        <v>1055</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>1036</v>
+        <v>1040</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>1052</v>
+        <v>1056</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>54</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>1053</v>
+        <v>1057</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>1039</v>
+        <v>1043</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>173</v>
@@ -6285,22 +6516,22 @@
     </row>
     <row r="7" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>1054</v>
+        <v>1058</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>1036</v>
+        <v>1040</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>1055</v>
+        <v>1059</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>1056</v>
+        <v>1060</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>1057</v>
+        <v>1061</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>1039</v>
+        <v>1043</v>
       </c>
       <c r="G7" s="6" t="s">
         <v>187</v>
@@ -6308,22 +6539,22 @@
     </row>
     <row r="8" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>1058</v>
+        <v>1062</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>1036</v>
+        <v>1040</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>1059</v>
+        <v>1063</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>1060</v>
+        <v>1064</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>1061</v>
+        <v>1065</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>1039</v>
+        <v>1043</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>196</v>
@@ -6331,22 +6562,22 @@
     </row>
     <row r="9" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>1062</v>
+        <v>1066</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>1036</v>
+        <v>1040</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>1063</v>
+        <v>1067</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>634</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>1064</v>
+        <v>1068</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>1065</v>
+        <v>1069</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>632</v>
@@ -6354,22 +6585,22 @@
     </row>
     <row r="10" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>1066</v>
+        <v>1070</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>1036</v>
+        <v>1040</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>1067</v>
+        <v>1071</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>638</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>1068</v>
+        <v>1072</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>1065</v>
+        <v>1069</v>
       </c>
       <c r="G10" s="6" t="s">
         <v>636</v>
@@ -6377,22 +6608,22 @@
     </row>
     <row r="11" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>1069</v>
+        <v>1073</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>1036</v>
+        <v>1040</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>1070</v>
+        <v>1074</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>642</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>1071</v>
+        <v>1075</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>1065</v>
+        <v>1069</v>
       </c>
       <c r="G11" s="6" t="s">
         <v>640</v>
@@ -6400,22 +6631,22 @@
     </row>
     <row r="12" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>1072</v>
+        <v>1076</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>1036</v>
+        <v>1040</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>1073</v>
+        <v>1077</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>646</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>1065</v>
+        <v>1069</v>
       </c>
       <c r="G12" s="6" t="s">
         <v>644</v>
@@ -6423,22 +6654,22 @@
     </row>
     <row r="13" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>1036</v>
+        <v>1040</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>1076</v>
+        <v>1080</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>650</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>1077</v>
+        <v>1081</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>1065</v>
+        <v>1069</v>
       </c>
       <c r="G13" s="6" t="s">
         <v>648</v>
@@ -6446,22 +6677,22 @@
     </row>
     <row r="14" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>1078</v>
+        <v>1082</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>1036</v>
+        <v>1040</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>1079</v>
+        <v>1083</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>654</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>1080</v>
+        <v>1084</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>1065</v>
+        <v>1069</v>
       </c>
       <c r="G14" s="6" t="s">
         <v>652</v>
@@ -6469,22 +6700,22 @@
     </row>
     <row r="15" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>1081</v>
+        <v>1085</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>1036</v>
+        <v>1040</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>1082</v>
+        <v>1086</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>658</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>1083</v>
+        <v>1087</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>1065</v>
+        <v>1069</v>
       </c>
       <c r="G15" s="6" t="s">
         <v>656</v>
@@ -6492,22 +6723,22 @@
     </row>
     <row r="16" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>1084</v>
+        <v>1088</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>1036</v>
+        <v>1040</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>1085</v>
+        <v>1089</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>662</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>1086</v>
+        <v>1090</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>1065</v>
+        <v>1069</v>
       </c>
       <c r="G16" s="6" t="s">
         <v>660</v>
@@ -6515,22 +6746,22 @@
     </row>
     <row r="17" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>1087</v>
+        <v>1091</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>1036</v>
+        <v>1040</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>1088</v>
+        <v>1092</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>666</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>1089</v>
+        <v>1093</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>1065</v>
+        <v>1069</v>
       </c>
       <c r="G17" s="6" t="s">
         <v>664</v>
@@ -6538,22 +6769,22 @@
     </row>
     <row r="18" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>1090</v>
+        <v>1094</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>1036</v>
+        <v>1040</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>1091</v>
+        <v>1095</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>670</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>1092</v>
+        <v>1096</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>1065</v>
+        <v>1069</v>
       </c>
       <c r="G18" s="6" t="s">
         <v>668</v>
@@ -6561,22 +6792,22 @@
     </row>
     <row r="19" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>1093</v>
+        <v>1097</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>1036</v>
+        <v>1040</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>1094</v>
+        <v>1098</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>674</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>1095</v>
+        <v>1099</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>1065</v>
+        <v>1069</v>
       </c>
       <c r="G19" s="6" t="s">
         <v>672</v>
@@ -6584,22 +6815,22 @@
     </row>
     <row r="20" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>1096</v>
+        <v>1100</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>1036</v>
+        <v>1040</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>1097</v>
+        <v>1101</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>678</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>1098</v>
+        <v>1102</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>1065</v>
+        <v>1069</v>
       </c>
       <c r="G20" s="6" t="s">
         <v>676</v>
@@ -6607,22 +6838,22 @@
     </row>
     <row r="21" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>1099</v>
+        <v>1103</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>1036</v>
+        <v>1040</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>1100</v>
+        <v>1104</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>682</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>1101</v>
+        <v>1105</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>1065</v>
+        <v>1069</v>
       </c>
       <c r="G21" s="6" t="s">
         <v>680</v>
@@ -6630,45 +6861,45 @@
     </row>
     <row r="22" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>1102</v>
+        <v>1106</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>1036</v>
+        <v>1040</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>1103</v>
+        <v>1107</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>1104</v>
+        <v>1108</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>1105</v>
+        <v>1109</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>1106</v>
+        <v>1110</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>1107</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="23" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>1108</v>
+        <v>1112</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>1110</v>
+        <v>1114</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>824</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>1111</v>
+        <v>1115</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>1112</v>
+        <v>1116</v>
       </c>
       <c r="G23" s="6" t="s">
         <v>817</v>
@@ -6676,22 +6907,22 @@
     </row>
     <row r="24" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>1113</v>
+        <v>1117</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>1036</v>
+        <v>1040</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>1114</v>
+        <v>1118</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>825</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>1115</v>
+        <v>1119</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>1112</v>
+        <v>1116</v>
       </c>
       <c r="G24" s="6" t="s">
         <v>817</v>
@@ -6739,7 +6970,7 @@
         <v>35</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>1116</v>
+        <v>1120</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -6753,7 +6984,7 @@
         <v>35</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>1117</v>
+        <v>1121</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -6767,7 +6998,7 @@
         <v>35</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>1118</v>
+        <v>1122</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -6781,7 +7012,7 @@
         <v>41</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>1116</v>
+        <v>1120</v>
       </c>
       <c r="D5" s="1">
         <v>1</v>
@@ -6795,7 +7026,7 @@
         <v>41</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>1117</v>
+        <v>1121</v>
       </c>
       <c r="D6" s="1">
         <v>2</v>
@@ -6809,7 +7040,7 @@
         <v>41</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>1118</v>
+        <v>1122</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -6823,7 +7054,7 @@
         <v>46</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>1116</v>
+        <v>1120</v>
       </c>
       <c r="D8" s="1">
         <v>1</v>
@@ -6837,7 +7068,7 @@
         <v>46</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>1117</v>
+        <v>1121</v>
       </c>
       <c r="D9" s="1">
         <v>2</v>
@@ -6851,7 +7082,7 @@
         <v>46</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>1118</v>
+        <v>1122</v>
       </c>
       <c r="D10" s="1">
         <v>3</v>
@@ -6865,7 +7096,7 @@
         <v>50</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>1116</v>
+        <v>1120</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
@@ -6879,7 +7110,7 @@
         <v>50</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>1117</v>
+        <v>1121</v>
       </c>
       <c r="D12" s="1">
         <v>2</v>
@@ -6893,7 +7124,7 @@
         <v>50</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>1118</v>
+        <v>1122</v>
       </c>
       <c r="D13" s="1">
         <v>3</v>
@@ -6907,7 +7138,7 @@
         <v>54</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>1116</v>
+        <v>1120</v>
       </c>
       <c r="D14" s="1">
         <v>1</v>
@@ -6921,7 +7152,7 @@
         <v>54</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>1117</v>
+        <v>1121</v>
       </c>
       <c r="D15" s="1">
         <v>2</v>
@@ -6935,7 +7166,7 @@
         <v>54</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>1118</v>
+        <v>1122</v>
       </c>
       <c r="D16" s="1">
         <v>3</v>
@@ -6949,7 +7180,7 @@
         <v>58</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>1116</v>
+        <v>1120</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
@@ -6963,7 +7194,7 @@
         <v>58</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>1117</v>
+        <v>1121</v>
       </c>
       <c r="D18" s="1">
         <v>2</v>
@@ -6977,7 +7208,7 @@
         <v>58</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>1118</v>
+        <v>1122</v>
       </c>
       <c r="D19" s="1">
         <v>3</v>
@@ -6991,7 +7222,7 @@
         <v>63</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>1116</v>
+        <v>1120</v>
       </c>
       <c r="D20" s="1">
         <v>1</v>
@@ -7005,7 +7236,7 @@
         <v>63</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>1117</v>
+        <v>1121</v>
       </c>
       <c r="D21" s="1">
         <v>2</v>
@@ -7019,7 +7250,7 @@
         <v>63</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>1118</v>
+        <v>1122</v>
       </c>
       <c r="D22" s="1">
         <v>3</v>
@@ -7033,7 +7264,7 @@
         <v>68</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>1116</v>
+        <v>1120</v>
       </c>
       <c r="D23" s="1">
         <v>1</v>
@@ -7047,7 +7278,7 @@
         <v>68</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>1117</v>
+        <v>1121</v>
       </c>
       <c r="D24" s="1">
         <v>2</v>
@@ -7061,7 +7292,7 @@
         <v>68</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>1118</v>
+        <v>1122</v>
       </c>
       <c r="D25" s="1">
         <v>3</v>
@@ -7075,7 +7306,7 @@
         <v>227</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>1116</v>
+        <v>1120</v>
       </c>
       <c r="D26" s="1">
         <v>1</v>
@@ -7089,7 +7320,7 @@
         <v>227</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>1117</v>
+        <v>1121</v>
       </c>
       <c r="D27" s="1">
         <v>2</v>
@@ -7103,7 +7334,7 @@
         <v>227</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>1118</v>
+        <v>1122</v>
       </c>
       <c r="D28" s="1">
         <v>3</v>
@@ -7117,7 +7348,7 @@
         <v>237</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>1116</v>
+        <v>1120</v>
       </c>
       <c r="D29" s="1">
         <v>1</v>
@@ -7131,7 +7362,7 @@
         <v>237</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>1117</v>
+        <v>1121</v>
       </c>
       <c r="D30" s="1">
         <v>2</v>
@@ -7145,7 +7376,7 @@
         <v>237</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>1118</v>
+        <v>1122</v>
       </c>
       <c r="D31" s="1">
         <v>3</v>
@@ -7159,7 +7390,7 @@
         <v>247</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>1116</v>
+        <v>1120</v>
       </c>
       <c r="D32" s="1">
         <v>1</v>
@@ -7173,7 +7404,7 @@
         <v>247</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>1117</v>
+        <v>1121</v>
       </c>
       <c r="D33" s="1">
         <v>2</v>
@@ -7187,7 +7418,7 @@
         <v>247</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>1118</v>
+        <v>1122</v>
       </c>
       <c r="D34" s="1">
         <v>3</v>
@@ -7201,7 +7432,7 @@
         <v>255</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>1116</v>
+        <v>1120</v>
       </c>
       <c r="D35" s="1">
         <v>1</v>
@@ -7215,7 +7446,7 @@
         <v>255</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>1117</v>
+        <v>1121</v>
       </c>
       <c r="D36" s="1">
         <v>2</v>
@@ -7229,7 +7460,7 @@
         <v>255</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>1118</v>
+        <v>1122</v>
       </c>
       <c r="D37" s="1">
         <v>3</v>
@@ -7243,7 +7474,7 @@
         <v>268</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>1116</v>
+        <v>1120</v>
       </c>
       <c r="D38" s="1">
         <v>1</v>
@@ -7257,7 +7488,7 @@
         <v>268</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>1117</v>
+        <v>1121</v>
       </c>
       <c r="D39" s="1">
         <v>2</v>
@@ -7271,7 +7502,7 @@
         <v>268</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>1118</v>
+        <v>1122</v>
       </c>
       <c r="D40" s="1">
         <v>3</v>
@@ -7285,7 +7516,7 @@
         <v>278</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>1116</v>
+        <v>1120</v>
       </c>
       <c r="D41" s="1">
         <v>1</v>
@@ -7299,7 +7530,7 @@
         <v>278</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>1117</v>
+        <v>1121</v>
       </c>
       <c r="D42" s="1">
         <v>2</v>
@@ -7313,7 +7544,7 @@
         <v>278</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>1118</v>
+        <v>1122</v>
       </c>
       <c r="D43" s="1">
         <v>3</v>
@@ -7327,7 +7558,7 @@
         <v>286</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>1116</v>
+        <v>1120</v>
       </c>
       <c r="D44" s="1">
         <v>1</v>
@@ -7341,7 +7572,7 @@
         <v>286</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>1117</v>
+        <v>1121</v>
       </c>
       <c r="D45" s="1">
         <v>2</v>
@@ -7355,7 +7586,7 @@
         <v>286</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>1118</v>
+        <v>1122</v>
       </c>
       <c r="D46" s="1">
         <v>3</v>
@@ -7369,7 +7600,7 @@
         <v>296</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>1116</v>
+        <v>1120</v>
       </c>
       <c r="D47" s="1">
         <v>1</v>
@@ -7383,7 +7614,7 @@
         <v>296</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>1117</v>
+        <v>1121</v>
       </c>
       <c r="D48" s="1">
         <v>2</v>
@@ -7397,7 +7628,7 @@
         <v>296</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>1118</v>
+        <v>1122</v>
       </c>
       <c r="D49" s="1">
         <v>3</v>
@@ -7411,7 +7642,7 @@
         <v>307</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>1116</v>
+        <v>1120</v>
       </c>
       <c r="D50" s="1">
         <v>1</v>
@@ -7425,7 +7656,7 @@
         <v>307</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>1117</v>
+        <v>1121</v>
       </c>
       <c r="D51" s="1">
         <v>2</v>
@@ -7439,7 +7670,7 @@
         <v>307</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>1118</v>
+        <v>1122</v>
       </c>
       <c r="D52" s="1">
         <v>3</v>
@@ -7453,7 +7684,7 @@
         <v>41</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>1116</v>
+        <v>1120</v>
       </c>
       <c r="D53" s="1">
         <v>1</v>
@@ -7467,7 +7698,7 @@
         <v>41</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>1117</v>
+        <v>1121</v>
       </c>
       <c r="D54" s="1">
         <v>2</v>
@@ -7481,7 +7712,7 @@
         <v>41</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>1118</v>
+        <v>1122</v>
       </c>
       <c r="D55" s="1">
         <v>3</v>
@@ -7495,7 +7726,7 @@
         <v>73</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>1116</v>
+        <v>1120</v>
       </c>
       <c r="D56" s="1">
         <v>1</v>
@@ -7509,7 +7740,7 @@
         <v>73</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>1117</v>
+        <v>1121</v>
       </c>
       <c r="D57" s="1">
         <v>2</v>
@@ -7523,7 +7754,7 @@
         <v>73</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>1118</v>
+        <v>1122</v>
       </c>
       <c r="D58" s="1">
         <v>3</v>
@@ -7537,7 +7768,7 @@
         <v>77</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>1116</v>
+        <v>1120</v>
       </c>
       <c r="D59" s="1">
         <v>1</v>
@@ -7551,7 +7782,7 @@
         <v>77</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>1117</v>
+        <v>1121</v>
       </c>
       <c r="D60" s="1">
         <v>2</v>
@@ -7565,7 +7796,7 @@
         <v>77</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>1118</v>
+        <v>1122</v>
       </c>
       <c r="D61" s="1">
         <v>3</v>
@@ -7579,7 +7810,7 @@
         <v>81</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>1116</v>
+        <v>1120</v>
       </c>
       <c r="D62" s="1">
         <v>1</v>
@@ -7593,7 +7824,7 @@
         <v>81</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>1117</v>
+        <v>1121</v>
       </c>
       <c r="D63" s="1">
         <v>2</v>
@@ -7607,7 +7838,7 @@
         <v>81</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>1118</v>
+        <v>1122</v>
       </c>
       <c r="D64" s="1">
         <v>3</v>
@@ -7621,7 +7852,7 @@
         <v>85</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>1116</v>
+        <v>1120</v>
       </c>
       <c r="D65" s="1">
         <v>1</v>
@@ -7635,7 +7866,7 @@
         <v>85</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>1117</v>
+        <v>1121</v>
       </c>
       <c r="D66" s="1">
         <v>2</v>
@@ -7649,7 +7880,7 @@
         <v>85</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>1118</v>
+        <v>1122</v>
       </c>
       <c r="D67" s="1">
         <v>3</v>
@@ -7663,7 +7894,7 @@
         <v>90</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>1116</v>
+        <v>1120</v>
       </c>
       <c r="D68" s="1">
         <v>1</v>
@@ -7677,7 +7908,7 @@
         <v>90</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>1117</v>
+        <v>1121</v>
       </c>
       <c r="D69" s="1">
         <v>2</v>
@@ -7691,7 +7922,7 @@
         <v>90</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>1118</v>
+        <v>1122</v>
       </c>
       <c r="D70" s="1">
         <v>3</v>
@@ -7705,7 +7936,7 @@
         <v>27</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>1116</v>
+        <v>1120</v>
       </c>
       <c r="D71" s="1">
         <v>1</v>
@@ -7719,7 +7950,7 @@
         <v>27</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>1117</v>
+        <v>1121</v>
       </c>
       <c r="D72" s="1">
         <v>2</v>
@@ -7733,7 +7964,7 @@
         <v>27</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>1118</v>
+        <v>1122</v>
       </c>
       <c r="D73" s="1">
         <v>3</v>
@@ -7759,114 +7990,114 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>1119</v>
+        <v>1123</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>1120</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>1121</v>
+        <v>1125</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>1122</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="3" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>1123</v>
+        <v>1127</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>1124</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>1125</v>
+        <v>1129</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>1126</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="5" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>1127</v>
+        <v>1131</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="6" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>1129</v>
+        <v>1133</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>1130</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="7" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>1132</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="8" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>1133</v>
+        <v>1137</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>1134</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="9" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>1135</v>
+        <v>1139</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>1136</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="10" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>1137</v>
+        <v>1141</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>1138</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="11" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>1139</v>
+        <v>1143</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>1140</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="12" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>1141</v>
+        <v>1145</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>1142</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="13" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>1143</v>
+        <v>1147</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>1144</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="14" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>1145</v>
+        <v>1149</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>1146</v>
+        <v>1150</v>
       </c>
     </row>
   </sheetData>
@@ -13166,7 +13397,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="2" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" ht="18.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>120</v>
       </c>
@@ -13177,7 +13408,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="3" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" ht="18.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>137</v>
       </c>
@@ -13188,7 +13419,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="4" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" ht="18.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>137</v>
       </c>
@@ -13199,7 +13430,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" ht="18.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>150</v>
       </c>
@@ -13210,7 +13441,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="6" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" ht="18.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>150</v>
       </c>
@@ -13221,7 +13452,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" ht="18.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>150</v>
       </c>
@@ -13232,7 +13463,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="8" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" ht="18.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>160</v>
       </c>
@@ -13243,7 +13474,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="9" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" ht="18.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>173</v>
       </c>
@@ -13254,7 +13485,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="10" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" ht="18.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
         <v>187</v>
       </c>
@@ -13265,7 +13496,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="11" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" ht="18.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
         <v>187</v>
       </c>
@@ -13276,7 +13507,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="12" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" ht="18.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
         <v>208</v>
       </c>
@@ -13287,7 +13518,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" ht="18.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
         <v>220</v>
       </c>
@@ -13298,7 +13529,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" ht="18.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
         <v>230</v>
       </c>
@@ -13309,7 +13540,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" ht="18.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
         <v>240</v>
       </c>
@@ -13320,7 +13551,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" ht="18.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>248</v>
       </c>
@@ -13331,7 +13562,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" ht="18.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
         <v>261</v>
       </c>
@@ -13342,7 +13573,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" ht="18.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>261</v>
       </c>
@@ -13353,7 +13584,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" ht="18.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
         <v>271</v>
       </c>
@@ -13364,7 +13595,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" ht="18.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
         <v>271</v>
       </c>
@@ -13375,7 +13606,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" ht="18.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
         <v>279</v>
       </c>
@@ -13386,7 +13617,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" ht="18.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
         <v>279</v>
       </c>
@@ -13397,7 +13628,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" ht="18.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
         <v>300</v>
       </c>
@@ -13408,7 +13639,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" ht="18.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
         <v>300</v>
       </c>
@@ -13419,7 +13650,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" ht="18.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
         <v>309</v>
       </c>
@@ -13430,7 +13661,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" ht="18.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
         <v>309</v>
       </c>
@@ -13441,7 +13672,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" ht="18.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
         <v>289</v>
       </c>
@@ -13452,7 +13683,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" ht="18.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
         <v>289</v>
       </c>
@@ -13463,7 +13694,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" ht="18.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
         <v>321</v>
       </c>
@@ -13474,7 +13705,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" ht="18.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
         <v>321</v>
       </c>
@@ -13485,7 +13716,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" ht="18.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
         <v>330</v>
       </c>
@@ -13496,7 +13727,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" ht="18.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
         <v>330</v>
       </c>
@@ -13507,7 +13738,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" ht="18.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
         <v>344</v>
       </c>
@@ -13518,7 +13749,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>361</v>
       </c>
@@ -13529,7 +13760,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>361</v>
       </c>
@@ -13540,7 +13771,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>369</v>
       </c>
@@ -13551,7 +13782,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>369</v>
       </c>
@@ -13562,7 +13793,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>369</v>
       </c>
@@ -13573,7 +13804,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="39" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>351</v>
       </c>
@@ -13584,7 +13815,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>351</v>
       </c>
@@ -13595,7 +13826,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>379</v>
       </c>
@@ -13606,7 +13837,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="42" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>379</v>
       </c>
@@ -13617,7 +13848,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>388</v>
       </c>
@@ -13628,7 +13859,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="44" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>388</v>
       </c>
@@ -13639,7 +13870,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="45" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>397</v>
       </c>
@@ -13650,7 +13881,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="46" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>397</v>
       </c>
@@ -13661,7 +13892,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="47" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>406</v>
       </c>
@@ -13672,7 +13903,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="48" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>406</v>
       </c>
@@ -13683,7 +13914,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="49" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>431</v>
       </c>
@@ -13694,7 +13925,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>431</v>
       </c>
@@ -13705,7 +13936,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>431</v>
       </c>
@@ -14532,117 +14763,117 @@
         <v>776</v>
       </c>
     </row>
-    <row r="100" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="100" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
     </row>
-    <row r="101" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="101" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
     </row>
-    <row r="102" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="102" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
     </row>
-    <row r="103" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="103" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
     </row>
-    <row r="104" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="104" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
     </row>
-    <row r="105" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="105" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
     </row>
-    <row r="106" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="106" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
     </row>
-    <row r="107" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="107" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
     </row>
-    <row r="108" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="108" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
     </row>
-    <row r="109" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="109" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
     </row>
-    <row r="110" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="110" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
     </row>
-    <row r="111" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="111" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
     </row>
-    <row r="112" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="112" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
     </row>
-    <row r="113" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="113" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
     </row>
-    <row r="114" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="114" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
     </row>
-    <row r="115" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="115" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
     </row>
-    <row r="116" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="116" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
     </row>
-    <row r="117" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="117" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
     </row>
-    <row r="118" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="118" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
     </row>
-    <row r="119" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="119" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
     </row>
-    <row r="120" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="120" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
     </row>
-    <row r="121" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="121" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
     </row>
-    <row r="122" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="122" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>

--- a/MAX-SEAL-main/catalog/MAXSEAL_CATALOG.xlsx
+++ b/MAX-SEAL-main/catalog/MAXSEAL_CATALOG.xlsx
@@ -4024,7 +4024,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="2" ht="18.75" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>817</v>
       </c>
@@ -4062,7 +4062,7 @@
         <v>826</v>
       </c>
     </row>
-    <row r="3" ht="18.75" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>827</v>
       </c>
@@ -4096,7 +4096,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="4" ht="18.75" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>833</v>
       </c>
@@ -4128,7 +4128,7 @@
         <v>826</v>
       </c>
     </row>
-    <row r="5" ht="18.75" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>838</v>
       </c>
@@ -4162,7 +4162,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="6" ht="18.75" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>845</v>
       </c>
@@ -4194,7 +4194,7 @@
         <v>826</v>
       </c>
     </row>
-    <row r="7" ht="18.75" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>852</v>
       </c>
@@ -4228,7 +4228,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="8" ht="18.75" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>858</v>
       </c>
@@ -4260,7 +4260,7 @@
         <v>826</v>
       </c>
     </row>
-    <row r="9" ht="18.75" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>863</v>
       </c>
@@ -4292,7 +4292,7 @@
         <v>826</v>
       </c>
     </row>
-    <row r="10" ht="18.75" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
         <v>870</v>
       </c>
@@ -4324,7 +4324,7 @@
         <v>826</v>
       </c>
     </row>
-    <row r="11" ht="18.75" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
         <v>876</v>
       </c>
@@ -4356,7 +4356,7 @@
         <v>826</v>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>882</v>
       </c>
@@ -4384,7 +4384,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>886</v>
       </c>
@@ -4412,7 +4412,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>890</v>
       </c>
@@ -4440,7 +4440,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>894</v>
       </c>
@@ -4468,7 +4468,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>898</v>
       </c>
@@ -4496,7 +4496,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="17" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>902</v>
       </c>
@@ -4524,7 +4524,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>906</v>
       </c>
@@ -4552,7 +4552,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>910</v>
       </c>
@@ -4580,7 +4580,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>914</v>
       </c>
@@ -4608,7 +4608,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="21" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>918</v>
       </c>
@@ -4636,7 +4636,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>922</v>
       </c>
@@ -4664,7 +4664,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="23" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>926</v>
       </c>
@@ -4694,7 +4694,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>930</v>
       </c>
@@ -4722,7 +4722,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>934</v>
       </c>
@@ -4752,7 +4752,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>939</v>
       </c>
@@ -4782,7 +4782,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="27" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>944</v>
       </c>
@@ -4812,7 +4812,7 @@
         <v>826</v>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>949</v>
       </c>
@@ -5125,13 +5125,13 @@
         <v>959</v>
       </c>
       <c r="L35" t="s">
-        <v>619</v>
+        <v>826</v>
       </c>
       <c r="M35" t="s">
         <v>959</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -5144,7 +5144,7 @@
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -5157,7 +5157,7 @@
       <c r="J37" s="1"/>
       <c r="K37" s="1"/>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>

--- a/MAX-SEAL-main/catalog/MAXSEAL_CATALOG.xlsx
+++ b/MAX-SEAL-main/catalog/MAXSEAL_CATALOG.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2739" uniqueCount="1151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2795" uniqueCount="1166">
   <si>
     <t>Id</t>
   </si>
@@ -2100,6 +2100,9 @@
     <t>WhyItFits</t>
   </si>
   <si>
+    <t>Segment</t>
+  </si>
+  <si>
     <t>1</t>
   </si>
   <si>
@@ -2370,6 +2373,51 @@
     <t>Double- and triple-offset designs with special-alloy options.</t>
   </si>
   <si>
+    <t>Refinery and petrochemical process isolation</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>DS</t>
+  </si>
+  <si>
+    <t>Compressor stations, terminals, LNG plants and gas-processing systems</t>
+  </si>
+  <si>
+    <t>MS</t>
+  </si>
+  <si>
+    <t>Offshore platforms, production equipment and higher-pressure utility lines</t>
+  </si>
+  <si>
+    <t>UP</t>
+  </si>
+  <si>
+    <t>High-cycle process isolation and automated shutoff</t>
+  </si>
+  <si>
+    <t>Larger-diameter automated isolation and emergency-shutdown applications</t>
+  </si>
+  <si>
+    <t>Hot hydrocarbons, steam and severe refinery service</t>
+  </si>
+  <si>
+    <t>LNG, high-temperature gas processing and large pipeline-related systems</t>
+  </si>
+  <si>
+    <t>Sour gas, produced water, seawater injection and corrosive offshore service</t>
+  </si>
+  <si>
+    <t>Cooling towers, utility water, firewater and plant air systems</t>
+  </si>
+  <si>
+    <t>Firewater, cooling water and noncritical terminal utilities</t>
+  </si>
+  <si>
+    <t>Cooling water, firewater, utility water and compressed air—not critical hydrocarbon isolation</t>
+  </si>
+  <si>
     <t>BodyMaterials</t>
   </si>
   <si>
@@ -2914,9 +2962,6 @@
   </si>
   <si>
     <t>Why Buy Maxseal Performance Series Butterfly Valves</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>2.0 MB</t>
@@ -3997,99 +4042,99 @@
         <v>614</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>808</v>
+        <v>824</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>809</v>
+        <v>825</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>810</v>
+        <v>826</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>811</v>
+        <v>827</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>812</v>
+        <v>828</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>813</v>
+        <v>829</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>814</v>
+        <v>830</v>
       </c>
       <c r="L1" s="13" t="s">
-        <v>815</v>
+        <v>831</v>
       </c>
       <c r="M1" t="s">
-        <v>816</v>
+        <v>832</v>
       </c>
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>817</v>
+        <v>833</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>32</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>818</v>
+        <v>834</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>819</v>
+        <v>835</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>220</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>820</v>
+        <v>836</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>821</v>
+        <v>837</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>822</v>
+        <v>838</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>823</v>
+        <v>839</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>824</v>
+        <v>840</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>825</v>
+        <v>841</v>
       </c>
       <c r="L2" t="s">
-        <v>826</v>
+        <v>842</v>
       </c>
     </row>
     <row r="3" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>827</v>
+        <v>843</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>44</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>818</v>
+        <v>834</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>828</v>
+        <v>844</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>150</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="6" t="s">
-        <v>829</v>
+        <v>845</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>830</v>
+        <v>846</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>831</v>
+        <v>847</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>832</v>
+        <v>848</v>
       </c>
       <c r="K3" s="1"/>
       <c r="L3" t="s">
@@ -4098,64 +4143,64 @@
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>833</v>
+        <v>849</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>38</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>818</v>
+        <v>834</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>834</v>
+        <v>850</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>137</v>
       </c>
       <c r="F4" s="1"/>
       <c r="G4" s="6" t="s">
-        <v>835</v>
+        <v>851</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>836</v>
+        <v>852</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>837</v>
+        <v>853</v>
       </c>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
       <c r="L4" t="s">
-        <v>826</v>
+        <v>842</v>
       </c>
     </row>
     <row r="5" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>838</v>
+        <v>854</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>839</v>
+        <v>855</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>818</v>
+        <v>834</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>840</v>
+        <v>856</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>160</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="6" t="s">
-        <v>841</v>
+        <v>857</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>842</v>
+        <v>858</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>843</v>
+        <v>859</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>844</v>
+        <v>860</v>
       </c>
       <c r="K5" s="1"/>
       <c r="L5" t="s">
@@ -4164,64 +4209,64 @@
     </row>
     <row r="6" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>845</v>
+        <v>861</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>846</v>
+        <v>862</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>847</v>
+        <v>863</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>848</v>
+        <v>864</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>187</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="6" t="s">
-        <v>849</v>
+        <v>865</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>850</v>
+        <v>866</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>851</v>
+        <v>867</v>
       </c>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
       <c r="L6" t="s">
-        <v>826</v>
+        <v>842</v>
       </c>
     </row>
     <row r="7" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>852</v>
+        <v>868</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>53</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>818</v>
+        <v>834</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>853</v>
+        <v>869</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>173</v>
       </c>
       <c r="F7" s="1"/>
       <c r="G7" s="6" t="s">
-        <v>854</v>
+        <v>870</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>855</v>
+        <v>871</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>856</v>
+        <v>872</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>857</v>
+        <v>873</v>
       </c>
       <c r="K7" s="1"/>
       <c r="L7" t="s">
@@ -4230,144 +4275,144 @@
     </row>
     <row r="8" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>858</v>
+        <v>874</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>859</v>
+        <v>875</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>860</v>
+        <v>876</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>861</v>
+        <v>877</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>120</v>
       </c>
       <c r="F8" s="1"/>
       <c r="G8" s="6" t="s">
-        <v>821</v>
+        <v>837</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>862</v>
+        <v>878</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
       <c r="L8" t="s">
-        <v>826</v>
+        <v>842</v>
       </c>
     </row>
     <row r="9" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>863</v>
+        <v>879</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>864</v>
+        <v>880</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>865</v>
+        <v>881</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>866</v>
+        <v>882</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>867</v>
+        <v>883</v>
       </c>
       <c r="F9" s="1"/>
       <c r="G9" s="6" t="s">
-        <v>829</v>
+        <v>845</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>868</v>
+        <v>884</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>869</v>
+        <v>885</v>
       </c>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
       <c r="L9" t="s">
-        <v>826</v>
+        <v>842</v>
       </c>
     </row>
     <row r="10" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>870</v>
+        <v>886</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>871</v>
+        <v>887</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>872</v>
+        <v>888</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>873</v>
+        <v>889</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>867</v>
+        <v>883</v>
       </c>
       <c r="F10" s="1"/>
       <c r="G10" s="6" t="s">
-        <v>835</v>
+        <v>851</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>874</v>
+        <v>890</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>875</v>
+        <v>891</v>
       </c>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
       <c r="L10" t="s">
-        <v>826</v>
+        <v>842</v>
       </c>
     </row>
     <row r="11" ht="18.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>876</v>
+        <v>892</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>877</v>
+        <v>893</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>878</v>
+        <v>894</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>879</v>
+        <v>895</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>160</v>
       </c>
       <c r="F11" s="1"/>
       <c r="G11" s="6" t="s">
-        <v>841</v>
+        <v>857</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>880</v>
+        <v>896</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>881</v>
+        <v>897</v>
       </c>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
       <c r="L11" t="s">
-        <v>826</v>
+        <v>842</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>882</v>
+        <v>898</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>883</v>
+        <v>899</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>818</v>
+        <v>834</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>884</v>
+        <v>900</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>220</v>
@@ -4377,7 +4422,7 @@
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1" t="s">
-        <v>885</v>
+        <v>901</v>
       </c>
       <c r="K12" s="1"/>
       <c r="L12" t="s">
@@ -4386,16 +4431,16 @@
     </row>
     <row r="13" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>886</v>
+        <v>902</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>887</v>
+        <v>903</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>818</v>
+        <v>834</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>888</v>
+        <v>904</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>230</v>
@@ -4405,7 +4450,7 @@
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1" t="s">
-        <v>889</v>
+        <v>905</v>
       </c>
       <c r="K13" s="1"/>
       <c r="L13" t="s">
@@ -4414,16 +4459,16 @@
     </row>
     <row r="14" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>890</v>
+        <v>906</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>891</v>
+        <v>907</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>818</v>
+        <v>834</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>892</v>
+        <v>908</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>248</v>
@@ -4433,7 +4478,7 @@
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1" t="s">
-        <v>893</v>
+        <v>909</v>
       </c>
       <c r="K14" s="1"/>
       <c r="L14" t="s">
@@ -4442,16 +4487,16 @@
     </row>
     <row r="15" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>894</v>
+        <v>910</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>895</v>
+        <v>911</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>818</v>
+        <v>834</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>896</v>
+        <v>912</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>187</v>
@@ -4461,7 +4506,7 @@
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1" t="s">
-        <v>897</v>
+        <v>913</v>
       </c>
       <c r="K15" s="1"/>
       <c r="L15" t="s">
@@ -4470,16 +4515,16 @@
     </row>
     <row r="16" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>898</v>
+        <v>914</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>899</v>
+        <v>915</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>818</v>
+        <v>834</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>900</v>
+        <v>916</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>261</v>
@@ -4489,7 +4534,7 @@
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1" t="s">
-        <v>901</v>
+        <v>917</v>
       </c>
       <c r="K16" s="1"/>
       <c r="L16" t="s">
@@ -4498,16 +4543,16 @@
     </row>
     <row r="17" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>902</v>
+        <v>918</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>903</v>
+        <v>919</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>818</v>
+        <v>834</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>271</v>
@@ -4517,7 +4562,7 @@
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1" t="s">
-        <v>905</v>
+        <v>921</v>
       </c>
       <c r="K17" s="1"/>
       <c r="L17" t="s">
@@ -4526,16 +4571,16 @@
     </row>
     <row r="18" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>906</v>
+        <v>922</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>907</v>
+        <v>923</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>818</v>
+        <v>834</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>908</v>
+        <v>924</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>279</v>
@@ -4545,7 +4590,7 @@
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
       <c r="J18" s="1" t="s">
-        <v>909</v>
+        <v>925</v>
       </c>
       <c r="K18" s="1"/>
       <c r="L18" t="s">
@@ -4554,16 +4599,16 @@
     </row>
     <row r="19" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>910</v>
+        <v>926</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>911</v>
+        <v>927</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>818</v>
+        <v>834</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>912</v>
+        <v>928</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>289</v>
@@ -4573,7 +4618,7 @@
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
       <c r="J19" s="1" t="s">
-        <v>913</v>
+        <v>929</v>
       </c>
       <c r="K19" s="1"/>
       <c r="L19" t="s">
@@ -4582,16 +4627,16 @@
     </row>
     <row r="20" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>914</v>
+        <v>930</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>915</v>
+        <v>931</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>818</v>
+        <v>834</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>916</v>
+        <v>932</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>300</v>
@@ -4601,7 +4646,7 @@
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1" t="s">
-        <v>917</v>
+        <v>933</v>
       </c>
       <c r="K20" s="1"/>
       <c r="L20" t="s">
@@ -4610,16 +4655,16 @@
     </row>
     <row r="21" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>918</v>
+        <v>934</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>919</v>
+        <v>935</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>818</v>
+        <v>834</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>920</v>
+        <v>936</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>309</v>
@@ -4629,7 +4674,7 @@
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1" t="s">
-        <v>921</v>
+        <v>937</v>
       </c>
       <c r="K21" s="1"/>
       <c r="L21" t="s">
@@ -4638,16 +4683,16 @@
     </row>
     <row r="22" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>922</v>
+        <v>938</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>923</v>
+        <v>939</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>818</v>
+        <v>834</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>924</v>
+        <v>940</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>240</v>
@@ -4657,7 +4702,7 @@
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1" t="s">
-        <v>925</v>
+        <v>941</v>
       </c>
       <c r="K22" s="1"/>
       <c r="L22" t="s">
@@ -4666,16 +4711,16 @@
     </row>
     <row r="23" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>926</v>
+        <v>942</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>927</v>
+        <v>943</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>818</v>
+        <v>834</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>928</v>
+        <v>944</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>196</v>
@@ -4687,7 +4732,7 @@
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1" t="s">
-        <v>929</v>
+        <v>945</v>
       </c>
       <c r="K23" s="1"/>
       <c r="L23" t="s">
@@ -4696,16 +4741,16 @@
     </row>
     <row r="24" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>930</v>
+        <v>946</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>931</v>
+        <v>947</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>818</v>
+        <v>834</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>932</v>
+        <v>948</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>208</v>
@@ -4715,7 +4760,7 @@
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1" t="s">
-        <v>933</v>
+        <v>949</v>
       </c>
       <c r="K24" s="1"/>
       <c r="L24" t="s">
@@ -4724,28 +4769,28 @@
     </row>
     <row r="25" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>934</v>
+        <v>950</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>935</v>
+        <v>951</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>818</v>
+        <v>834</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>936</v>
+        <v>952</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>344</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>937</v>
+        <v>953</v>
       </c>
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1" t="s">
-        <v>938</v>
+        <v>954</v>
       </c>
       <c r="K25" s="1"/>
       <c r="L25" t="s">
@@ -4754,28 +4799,28 @@
     </row>
     <row r="26" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>939</v>
+        <v>955</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>940</v>
+        <v>956</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>818</v>
+        <v>834</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>941</v>
+        <v>957</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>351</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>942</v>
+        <v>958</v>
       </c>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1" t="s">
-        <v>943</v>
+        <v>959</v>
       </c>
       <c r="K26" s="1"/>
       <c r="L26" t="s">
@@ -4784,102 +4829,102 @@
     </row>
     <row r="27" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>944</v>
+        <v>960</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>945</v>
+        <v>961</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>818</v>
+        <v>834</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>946</v>
+        <v>962</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>415</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>947</v>
+        <v>963</v>
       </c>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1" t="s">
-        <v>948</v>
+        <v>964</v>
       </c>
       <c r="K27" s="1"/>
       <c r="L27" t="s">
-        <v>826</v>
+        <v>842</v>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>949</v>
+        <v>965</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>950</v>
+        <v>966</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>818</v>
+        <v>834</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>951</v>
+        <v>967</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>867</v>
+        <v>883</v>
       </c>
       <c r="F28" s="1"/>
       <c r="G28" s="1" t="s">
-        <v>952</v>
+        <v>968</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>953</v>
+        <v>969</v>
       </c>
       <c r="I28" s="1"/>
       <c r="J28" s="1" t="s">
-        <v>954</v>
+        <v>970</v>
       </c>
       <c r="K28" s="1"/>
       <c r="L28" t="s">
-        <v>826</v>
+        <v>842</v>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>955</v>
+        <v>971</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>956</v>
+        <v>972</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>957</v>
+        <v>973</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>958</v>
+        <v>974</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>220</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>959</v>
+        <v>779</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>959</v>
+        <v>779</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>960</v>
+        <v>975</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>959</v>
+        <v>779</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>961</v>
+        <v>976</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>959</v>
+        <v>779</v>
       </c>
       <c r="L29" t="s">
-        <v>826</v>
+        <v>842</v>
       </c>
       <c r="M29" t="s">
         <v>619</v>
@@ -4887,40 +4932,40 @@
     </row>
     <row r="30" ht="15" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>963</v>
+        <v>978</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>957</v>
+        <v>973</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>964</v>
+        <v>979</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>867</v>
+        <v>883</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>959</v>
+        <v>779</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>959</v>
+        <v>779</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>965</v>
+        <v>980</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>959</v>
+        <v>779</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>966</v>
+        <v>981</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>959</v>
+        <v>779</v>
       </c>
       <c r="L30" t="s">
-        <v>826</v>
+        <v>842</v>
       </c>
       <c r="M30" t="s">
         <v>619</v>
@@ -4928,40 +4973,40 @@
     </row>
     <row r="31" ht="15" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>967</v>
+        <v>982</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>968</v>
+        <v>983</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>860</v>
+        <v>876</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>969</v>
+        <v>984</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>220</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>959</v>
+        <v>779</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>959</v>
+        <v>779</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>970</v>
+        <v>985</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>959</v>
+        <v>779</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>971</v>
+        <v>986</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>959</v>
+        <v>779</v>
       </c>
       <c r="L31" t="s">
-        <v>826</v>
+        <v>842</v>
       </c>
       <c r="M31" t="s">
         <v>619</v>
@@ -4969,166 +5014,166 @@
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>972</v>
+        <v>987</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>973</v>
+        <v>988</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>818</v>
+        <v>834</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>974</v>
+        <v>989</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>187</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>959</v>
+        <v>779</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>959</v>
+        <v>779</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>868</v>
+        <v>884</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>959</v>
+        <v>779</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>975</v>
+        <v>990</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>959</v>
+        <v>779</v>
       </c>
       <c r="L32" t="s">
         <v>619</v>
       </c>
       <c r="M32" t="s">
-        <v>959</v>
+        <v>779</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>976</v>
+        <v>991</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>977</v>
+        <v>992</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>860</v>
+        <v>876</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>978</v>
+        <v>993</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>867</v>
+        <v>883</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>959</v>
+        <v>779</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>959</v>
+        <v>779</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>979</v>
+        <v>994</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>959</v>
+        <v>779</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>980</v>
+        <v>995</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>959</v>
+        <v>779</v>
       </c>
       <c r="L33" t="s">
         <v>619</v>
       </c>
       <c r="M33" t="s">
-        <v>959</v>
+        <v>779</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>981</v>
+        <v>996</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>982</v>
+        <v>997</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>847</v>
+        <v>863</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>983</v>
+        <v>998</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>867</v>
+        <v>883</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>959</v>
+        <v>779</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>959</v>
+        <v>779</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>984</v>
+        <v>999</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>959</v>
+        <v>779</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>985</v>
+        <v>1000</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>959</v>
+        <v>779</v>
       </c>
       <c r="L34" t="s">
         <v>619</v>
       </c>
       <c r="M34" t="s">
-        <v>959</v>
+        <v>779</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>986</v>
+        <v>1001</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>987</v>
+        <v>1002</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>988</v>
+        <v>1003</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>989</v>
+        <v>1004</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>867</v>
+        <v>883</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>959</v>
+        <v>779</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>959</v>
+        <v>779</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>822</v>
+        <v>838</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>959</v>
+        <v>779</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>990</v>
+        <v>1005</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>959</v>
+        <v>779</v>
       </c>
       <c r="L35" t="s">
-        <v>826</v>
+        <v>842</v>
       </c>
       <c r="M35" t="s">
-        <v>959</v>
+        <v>779</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
@@ -5204,22 +5249,22 @@
         <v>435</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>991</v>
+        <v>1006</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>992</v>
+        <v>1007</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>993</v>
+        <v>1008</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>994</v>
+        <v>1009</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>811</v>
+        <v>827</v>
       </c>
       <c r="I1" t="s">
-        <v>813</v>
+        <v>829</v>
       </c>
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5234,60 +5279,60 @@
     </row>
     <row r="3" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>995</v>
+        <v>1010</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>996</v>
+        <v>1011</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>867</v>
+        <v>883</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>997</v>
+        <v>1012</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>997</v>
+        <v>1012</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>998</v>
+        <v>1013</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>999</v>
+        <v>1014</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>1000</v>
+        <v>1015</v>
       </c>
       <c r="I3" t="s">
-        <v>948</v>
+        <v>964</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>1001</v>
+        <v>1016</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>1002</v>
+        <v>1017</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>867</v>
+        <v>883</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>1003</v>
+        <v>1018</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>1004</v>
+        <v>1019</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>1005</v>
+        <v>1020</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>999</v>
+        <v>1014</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>953</v>
+        <v>969</v>
       </c>
       <c r="I4" t="s">
-        <v>954</v>
+        <v>970</v>
       </c>
     </row>
   </sheetData>
@@ -5326,63 +5371,63 @@
         <v>437</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>1021</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>1022</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>1023</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>1024</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>828</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>1025</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>1026</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>1027</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>826</v>
+      </c>
+      <c r="L1" s="4" t="s">
         <v>1006</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>1007</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>1008</v>
-      </c>
-      <c r="F1" s="4" t="s">
+      <c r="N1" s="4" t="s">
         <v>1009</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>812</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>1010</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>1011</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>1012</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>810</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>991</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>992</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>994</v>
       </c>
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>1013</v>
+        <v>1028</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>818</v>
+        <v>834</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>1014</v>
+        <v>1029</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>1015</v>
+        <v>1030</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>1016</v>
+        <v>1031</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>1017</v>
+        <v>1032</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>1018</v>
+        <v>1033</v>
       </c>
       <c r="H2" s="6" t="s">
         <v>32</v>
@@ -5390,48 +5435,48 @@
     </row>
     <row r="3" ht="18.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>1019</v>
+        <v>1034</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>1020</v>
+        <v>1035</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>1021</v>
+        <v>1036</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>1022</v>
+        <v>1037</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>957</v>
+        <v>973</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>1023</v>
+        <v>1038</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>829</v>
+        <v>845</v>
       </c>
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>1024</v>
+        <v>1039</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>1025</v>
+        <v>1040</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>1026</v>
+        <v>1041</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>1027</v>
+        <v>1042</v>
       </c>
       <c r="L4" s="6" t="s">
-        <v>1028</v>
+        <v>1043</v>
       </c>
       <c r="M4" s="6" t="s">
-        <v>1029</v>
+        <v>1044</v>
       </c>
       <c r="N4" s="6" t="s">
-        <v>1030</v>
+        <v>1045</v>
       </c>
     </row>
   </sheetData>
@@ -5458,7 +5503,7 @@
         <v>435</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>1031</v>
+        <v>1046</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>6</v>
@@ -5472,7 +5517,7 @@
         <v>160</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
     </row>
     <row r="3" ht="18.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -5483,7 +5528,7 @@
         <v>150</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -5494,7 +5539,7 @@
         <v>150</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
     </row>
     <row r="5" ht="18.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -5505,7 +5550,7 @@
         <v>150</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
     </row>
     <row r="6" ht="18.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -5516,7 +5561,7 @@
         <v>150</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -6378,45 +6423,45 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>1032</v>
+        <v>1047</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>1033</v>
+        <v>1048</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>1034</v>
+        <v>1049</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>1035</v>
+        <v>1050</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>1036</v>
+        <v>1051</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>1037</v>
+        <v>1052</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>1038</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>1039</v>
+        <v>1054</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>1040</v>
+        <v>1055</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>1041</v>
+        <v>1056</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>1042</v>
+        <v>1057</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>1043</v>
+        <v>1058</v>
       </c>
       <c r="G2" s="6" t="s">
         <v>120</v>
@@ -6424,22 +6469,22 @@
     </row>
     <row r="3" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>1044</v>
+        <v>1059</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>1040</v>
+        <v>1055</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>1045</v>
+        <v>1060</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>41</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>1046</v>
+        <v>1061</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>1043</v>
+        <v>1058</v>
       </c>
       <c r="G3" s="6" t="s">
         <v>137</v>
@@ -6447,22 +6492,22 @@
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>1047</v>
+        <v>1062</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>1040</v>
+        <v>1055</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>1048</v>
+        <v>1063</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>1049</v>
+        <v>1064</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>1050</v>
+        <v>1065</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>1043</v>
+        <v>1058</v>
       </c>
       <c r="G4" s="6" t="s">
         <v>150</v>
@@ -6470,22 +6515,22 @@
     </row>
     <row r="5" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>1051</v>
+        <v>1066</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>1040</v>
+        <v>1055</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>1052</v>
+        <v>1067</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>1053</v>
+        <v>1068</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>1054</v>
+        <v>1069</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>1043</v>
+        <v>1058</v>
       </c>
       <c r="G5" s="6" t="s">
         <v>160</v>
@@ -6493,22 +6538,22 @@
     </row>
     <row r="6" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
+        <v>1070</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>1055</v>
       </c>
-      <c r="B6" s="6" t="s">
-        <v>1040</v>
-      </c>
       <c r="C6" s="6" t="s">
-        <v>1056</v>
+        <v>1071</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>54</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>1057</v>
+        <v>1072</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>1043</v>
+        <v>1058</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>173</v>
@@ -6516,22 +6561,22 @@
     </row>
     <row r="7" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>1055</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>1074</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>1075</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>1076</v>
+      </c>
+      <c r="F7" s="6" t="s">
         <v>1058</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>1040</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>1059</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>1060</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>1061</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>1043</v>
       </c>
       <c r="G7" s="6" t="s">
         <v>187</v>
@@ -6539,22 +6584,22 @@
     </row>
     <row r="8" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>1062</v>
+        <v>1077</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>1040</v>
+        <v>1055</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>1063</v>
+        <v>1078</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>1064</v>
+        <v>1079</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>1065</v>
+        <v>1080</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>1043</v>
+        <v>1058</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>196</v>
@@ -6562,22 +6607,22 @@
     </row>
     <row r="9" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>1066</v>
+        <v>1081</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>1040</v>
+        <v>1055</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>1067</v>
+        <v>1082</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>634</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>1068</v>
+        <v>1083</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>1069</v>
+        <v>1084</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>632</v>
@@ -6585,22 +6630,22 @@
     </row>
     <row r="10" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>1070</v>
+        <v>1085</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>1040</v>
+        <v>1055</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>1071</v>
+        <v>1086</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>638</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>1072</v>
+        <v>1087</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>1069</v>
+        <v>1084</v>
       </c>
       <c r="G10" s="6" t="s">
         <v>636</v>
@@ -6608,22 +6653,22 @@
     </row>
     <row r="11" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>1073</v>
+        <v>1088</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>1040</v>
+        <v>1055</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>1074</v>
+        <v>1089</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>642</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>1075</v>
+        <v>1090</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>1069</v>
+        <v>1084</v>
       </c>
       <c r="G11" s="6" t="s">
         <v>640</v>
@@ -6631,22 +6676,22 @@
     </row>
     <row r="12" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>1076</v>
+        <v>1091</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>1040</v>
+        <v>1055</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>1077</v>
+        <v>1092</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>646</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>1078</v>
+        <v>1093</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>1069</v>
+        <v>1084</v>
       </c>
       <c r="G12" s="6" t="s">
         <v>644</v>
@@ -6654,22 +6699,22 @@
     </row>
     <row r="13" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>1079</v>
+        <v>1094</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>1040</v>
+        <v>1055</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>1080</v>
+        <v>1095</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>650</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>1081</v>
+        <v>1096</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>1069</v>
+        <v>1084</v>
       </c>
       <c r="G13" s="6" t="s">
         <v>648</v>
@@ -6677,22 +6722,22 @@
     </row>
     <row r="14" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>1082</v>
+        <v>1097</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>1040</v>
+        <v>1055</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>1083</v>
+        <v>1098</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>654</v>
       </c>
       <c r="E14" s="6" t="s">
+        <v>1099</v>
+      </c>
+      <c r="F14" s="6" t="s">
         <v>1084</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>1069</v>
       </c>
       <c r="G14" s="6" t="s">
         <v>652</v>
@@ -6700,22 +6745,22 @@
     </row>
     <row r="15" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>1085</v>
+        <v>1100</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>1040</v>
+        <v>1055</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>1086</v>
+        <v>1101</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>658</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>1087</v>
+        <v>1102</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>1069</v>
+        <v>1084</v>
       </c>
       <c r="G15" s="6" t="s">
         <v>656</v>
@@ -6723,22 +6768,22 @@
     </row>
     <row r="16" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>1088</v>
+        <v>1103</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>1040</v>
+        <v>1055</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>1089</v>
+        <v>1104</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>662</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>1090</v>
+        <v>1105</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>1069</v>
+        <v>1084</v>
       </c>
       <c r="G16" s="6" t="s">
         <v>660</v>
@@ -6746,22 +6791,22 @@
     </row>
     <row r="17" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>1091</v>
+        <v>1106</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>1040</v>
+        <v>1055</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>1092</v>
+        <v>1107</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>666</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>1093</v>
+        <v>1108</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>1069</v>
+        <v>1084</v>
       </c>
       <c r="G17" s="6" t="s">
         <v>664</v>
@@ -6769,22 +6814,22 @@
     </row>
     <row r="18" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>1094</v>
+        <v>1109</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>1040</v>
+        <v>1055</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>1095</v>
+        <v>1110</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>670</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>1096</v>
+        <v>1111</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>1069</v>
+        <v>1084</v>
       </c>
       <c r="G18" s="6" t="s">
         <v>668</v>
@@ -6792,22 +6837,22 @@
     </row>
     <row r="19" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>1097</v>
+        <v>1112</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>1040</v>
+        <v>1055</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>1098</v>
+        <v>1113</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>674</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>1099</v>
+        <v>1114</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>1069</v>
+        <v>1084</v>
       </c>
       <c r="G19" s="6" t="s">
         <v>672</v>
@@ -6815,22 +6860,22 @@
     </row>
     <row r="20" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>1100</v>
+        <v>1115</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>1040</v>
+        <v>1055</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>1101</v>
+        <v>1116</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>678</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>1102</v>
+        <v>1117</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>1069</v>
+        <v>1084</v>
       </c>
       <c r="G20" s="6" t="s">
         <v>676</v>
@@ -6838,22 +6883,22 @@
     </row>
     <row r="21" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>1103</v>
+        <v>1118</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>1040</v>
+        <v>1055</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>1104</v>
+        <v>1119</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>682</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>1105</v>
+        <v>1120</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>1069</v>
+        <v>1084</v>
       </c>
       <c r="G21" s="6" t="s">
         <v>680</v>
@@ -6861,71 +6906,71 @@
     </row>
     <row r="22" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>1106</v>
+        <v>1121</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>1040</v>
+        <v>1055</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>1107</v>
+        <v>1122</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>1108</v>
+        <v>1123</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>1109</v>
+        <v>1124</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>1110</v>
+        <v>1125</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>1111</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="23" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>1112</v>
+        <v>1127</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>1113</v>
+        <v>1128</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>1114</v>
+        <v>1129</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>824</v>
+        <v>840</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>1115</v>
+        <v>1130</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>1116</v>
+        <v>1131</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>817</v>
+        <v>833</v>
       </c>
     </row>
     <row r="24" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>1117</v>
+        <v>1132</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>1040</v>
+        <v>1055</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>1118</v>
+        <v>1133</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>825</v>
+        <v>841</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>1119</v>
+        <v>1134</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>1116</v>
+        <v>1131</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>817</v>
+        <v>833</v>
       </c>
     </row>
   </sheetData>
@@ -6970,7 +7015,7 @@
         <v>35</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>1120</v>
+        <v>1135</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -6984,7 +7029,7 @@
         <v>35</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>1121</v>
+        <v>1136</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -6998,7 +7043,7 @@
         <v>35</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>1122</v>
+        <v>1137</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -7012,7 +7057,7 @@
         <v>41</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>1120</v>
+        <v>1135</v>
       </c>
       <c r="D5" s="1">
         <v>1</v>
@@ -7026,7 +7071,7 @@
         <v>41</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>1121</v>
+        <v>1136</v>
       </c>
       <c r="D6" s="1">
         <v>2</v>
@@ -7040,7 +7085,7 @@
         <v>41</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>1122</v>
+        <v>1137</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -7054,7 +7099,7 @@
         <v>46</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>1120</v>
+        <v>1135</v>
       </c>
       <c r="D8" s="1">
         <v>1</v>
@@ -7068,7 +7113,7 @@
         <v>46</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>1121</v>
+        <v>1136</v>
       </c>
       <c r="D9" s="1">
         <v>2</v>
@@ -7082,7 +7127,7 @@
         <v>46</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>1122</v>
+        <v>1137</v>
       </c>
       <c r="D10" s="1">
         <v>3</v>
@@ -7096,7 +7141,7 @@
         <v>50</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>1120</v>
+        <v>1135</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
@@ -7110,7 +7155,7 @@
         <v>50</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>1121</v>
+        <v>1136</v>
       </c>
       <c r="D12" s="1">
         <v>2</v>
@@ -7124,7 +7169,7 @@
         <v>50</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>1122</v>
+        <v>1137</v>
       </c>
       <c r="D13" s="1">
         <v>3</v>
@@ -7138,7 +7183,7 @@
         <v>54</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>1120</v>
+        <v>1135</v>
       </c>
       <c r="D14" s="1">
         <v>1</v>
@@ -7152,7 +7197,7 @@
         <v>54</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>1121</v>
+        <v>1136</v>
       </c>
       <c r="D15" s="1">
         <v>2</v>
@@ -7166,7 +7211,7 @@
         <v>54</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>1122</v>
+        <v>1137</v>
       </c>
       <c r="D16" s="1">
         <v>3</v>
@@ -7180,7 +7225,7 @@
         <v>58</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>1120</v>
+        <v>1135</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
@@ -7194,7 +7239,7 @@
         <v>58</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>1121</v>
+        <v>1136</v>
       </c>
       <c r="D18" s="1">
         <v>2</v>
@@ -7208,7 +7253,7 @@
         <v>58</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>1122</v>
+        <v>1137</v>
       </c>
       <c r="D19" s="1">
         <v>3</v>
@@ -7222,7 +7267,7 @@
         <v>63</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>1120</v>
+        <v>1135</v>
       </c>
       <c r="D20" s="1">
         <v>1</v>
@@ -7236,7 +7281,7 @@
         <v>63</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>1121</v>
+        <v>1136</v>
       </c>
       <c r="D21" s="1">
         <v>2</v>
@@ -7250,7 +7295,7 @@
         <v>63</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>1122</v>
+        <v>1137</v>
       </c>
       <c r="D22" s="1">
         <v>3</v>
@@ -7264,7 +7309,7 @@
         <v>68</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>1120</v>
+        <v>1135</v>
       </c>
       <c r="D23" s="1">
         <v>1</v>
@@ -7278,7 +7323,7 @@
         <v>68</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>1121</v>
+        <v>1136</v>
       </c>
       <c r="D24" s="1">
         <v>2</v>
@@ -7292,7 +7337,7 @@
         <v>68</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>1122</v>
+        <v>1137</v>
       </c>
       <c r="D25" s="1">
         <v>3</v>
@@ -7306,7 +7351,7 @@
         <v>227</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>1120</v>
+        <v>1135</v>
       </c>
       <c r="D26" s="1">
         <v>1</v>
@@ -7320,7 +7365,7 @@
         <v>227</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>1121</v>
+        <v>1136</v>
       </c>
       <c r="D27" s="1">
         <v>2</v>
@@ -7334,7 +7379,7 @@
         <v>227</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>1122</v>
+        <v>1137</v>
       </c>
       <c r="D28" s="1">
         <v>3</v>
@@ -7348,7 +7393,7 @@
         <v>237</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>1120</v>
+        <v>1135</v>
       </c>
       <c r="D29" s="1">
         <v>1</v>
@@ -7362,7 +7407,7 @@
         <v>237</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>1121</v>
+        <v>1136</v>
       </c>
       <c r="D30" s="1">
         <v>2</v>
@@ -7376,7 +7421,7 @@
         <v>237</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>1122</v>
+        <v>1137</v>
       </c>
       <c r="D31" s="1">
         <v>3</v>
@@ -7390,7 +7435,7 @@
         <v>247</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>1120</v>
+        <v>1135</v>
       </c>
       <c r="D32" s="1">
         <v>1</v>
@@ -7404,7 +7449,7 @@
         <v>247</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>1121</v>
+        <v>1136</v>
       </c>
       <c r="D33" s="1">
         <v>2</v>
@@ -7418,7 +7463,7 @@
         <v>247</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>1122</v>
+        <v>1137</v>
       </c>
       <c r="D34" s="1">
         <v>3</v>
@@ -7432,7 +7477,7 @@
         <v>255</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>1120</v>
+        <v>1135</v>
       </c>
       <c r="D35" s="1">
         <v>1</v>
@@ -7446,7 +7491,7 @@
         <v>255</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>1121</v>
+        <v>1136</v>
       </c>
       <c r="D36" s="1">
         <v>2</v>
@@ -7460,7 +7505,7 @@
         <v>255</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>1122</v>
+        <v>1137</v>
       </c>
       <c r="D37" s="1">
         <v>3</v>
@@ -7474,7 +7519,7 @@
         <v>268</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>1120</v>
+        <v>1135</v>
       </c>
       <c r="D38" s="1">
         <v>1</v>
@@ -7488,7 +7533,7 @@
         <v>268</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>1121</v>
+        <v>1136</v>
       </c>
       <c r="D39" s="1">
         <v>2</v>
@@ -7502,7 +7547,7 @@
         <v>268</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>1122</v>
+        <v>1137</v>
       </c>
       <c r="D40" s="1">
         <v>3</v>
@@ -7516,7 +7561,7 @@
         <v>278</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>1120</v>
+        <v>1135</v>
       </c>
       <c r="D41" s="1">
         <v>1</v>
@@ -7530,7 +7575,7 @@
         <v>278</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>1121</v>
+        <v>1136</v>
       </c>
       <c r="D42" s="1">
         <v>2</v>
@@ -7544,7 +7589,7 @@
         <v>278</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>1122</v>
+        <v>1137</v>
       </c>
       <c r="D43" s="1">
         <v>3</v>
@@ -7558,7 +7603,7 @@
         <v>286</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>1120</v>
+        <v>1135</v>
       </c>
       <c r="D44" s="1">
         <v>1</v>
@@ -7572,7 +7617,7 @@
         <v>286</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>1121</v>
+        <v>1136</v>
       </c>
       <c r="D45" s="1">
         <v>2</v>
@@ -7586,7 +7631,7 @@
         <v>286</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>1122</v>
+        <v>1137</v>
       </c>
       <c r="D46" s="1">
         <v>3</v>
@@ -7600,7 +7645,7 @@
         <v>296</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>1120</v>
+        <v>1135</v>
       </c>
       <c r="D47" s="1">
         <v>1</v>
@@ -7614,7 +7659,7 @@
         <v>296</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>1121</v>
+        <v>1136</v>
       </c>
       <c r="D48" s="1">
         <v>2</v>
@@ -7628,7 +7673,7 @@
         <v>296</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>1122</v>
+        <v>1137</v>
       </c>
       <c r="D49" s="1">
         <v>3</v>
@@ -7642,7 +7687,7 @@
         <v>307</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>1120</v>
+        <v>1135</v>
       </c>
       <c r="D50" s="1">
         <v>1</v>
@@ -7656,7 +7701,7 @@
         <v>307</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>1121</v>
+        <v>1136</v>
       </c>
       <c r="D51" s="1">
         <v>2</v>
@@ -7670,7 +7715,7 @@
         <v>307</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>1122</v>
+        <v>1137</v>
       </c>
       <c r="D52" s="1">
         <v>3</v>
@@ -7684,7 +7729,7 @@
         <v>41</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>1120</v>
+        <v>1135</v>
       </c>
       <c r="D53" s="1">
         <v>1</v>
@@ -7698,7 +7743,7 @@
         <v>41</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>1121</v>
+        <v>1136</v>
       </c>
       <c r="D54" s="1">
         <v>2</v>
@@ -7712,7 +7757,7 @@
         <v>41</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>1122</v>
+        <v>1137</v>
       </c>
       <c r="D55" s="1">
         <v>3</v>
@@ -7726,7 +7771,7 @@
         <v>73</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>1120</v>
+        <v>1135</v>
       </c>
       <c r="D56" s="1">
         <v>1</v>
@@ -7740,7 +7785,7 @@
         <v>73</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>1121</v>
+        <v>1136</v>
       </c>
       <c r="D57" s="1">
         <v>2</v>
@@ -7754,7 +7799,7 @@
         <v>73</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>1122</v>
+        <v>1137</v>
       </c>
       <c r="D58" s="1">
         <v>3</v>
@@ -7768,7 +7813,7 @@
         <v>77</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>1120</v>
+        <v>1135</v>
       </c>
       <c r="D59" s="1">
         <v>1</v>
@@ -7782,7 +7827,7 @@
         <v>77</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>1121</v>
+        <v>1136</v>
       </c>
       <c r="D60" s="1">
         <v>2</v>
@@ -7796,7 +7841,7 @@
         <v>77</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>1122</v>
+        <v>1137</v>
       </c>
       <c r="D61" s="1">
         <v>3</v>
@@ -7810,7 +7855,7 @@
         <v>81</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>1120</v>
+        <v>1135</v>
       </c>
       <c r="D62" s="1">
         <v>1</v>
@@ -7824,7 +7869,7 @@
         <v>81</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>1121</v>
+        <v>1136</v>
       </c>
       <c r="D63" s="1">
         <v>2</v>
@@ -7838,7 +7883,7 @@
         <v>81</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>1122</v>
+        <v>1137</v>
       </c>
       <c r="D64" s="1">
         <v>3</v>
@@ -7852,7 +7897,7 @@
         <v>85</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>1120</v>
+        <v>1135</v>
       </c>
       <c r="D65" s="1">
         <v>1</v>
@@ -7866,7 +7911,7 @@
         <v>85</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>1121</v>
+        <v>1136</v>
       </c>
       <c r="D66" s="1">
         <v>2</v>
@@ -7880,7 +7925,7 @@
         <v>85</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>1122</v>
+        <v>1137</v>
       </c>
       <c r="D67" s="1">
         <v>3</v>
@@ -7894,7 +7939,7 @@
         <v>90</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>1120</v>
+        <v>1135</v>
       </c>
       <c r="D68" s="1">
         <v>1</v>
@@ -7908,7 +7953,7 @@
         <v>90</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>1121</v>
+        <v>1136</v>
       </c>
       <c r="D69" s="1">
         <v>2</v>
@@ -7922,7 +7967,7 @@
         <v>90</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>1122</v>
+        <v>1137</v>
       </c>
       <c r="D70" s="1">
         <v>3</v>
@@ -7936,7 +7981,7 @@
         <v>27</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>1120</v>
+        <v>1135</v>
       </c>
       <c r="D71" s="1">
         <v>1</v>
@@ -7950,7 +7995,7 @@
         <v>27</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>1121</v>
+        <v>1136</v>
       </c>
       <c r="D72" s="1">
         <v>2</v>
@@ -7964,7 +8009,7 @@
         <v>27</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>1122</v>
+        <v>1137</v>
       </c>
       <c r="D73" s="1">
         <v>3</v>
@@ -7990,114 +8035,114 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>1123</v>
+        <v>1138</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>1124</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>1125</v>
+        <v>1140</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>1126</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="3" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>1127</v>
+        <v>1142</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>1128</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>1129</v>
+        <v>1144</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>1130</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="5" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>1131</v>
+        <v>1146</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>1132</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="6" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>1133</v>
+        <v>1148</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>1134</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="7" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>1135</v>
+        <v>1150</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>1136</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="8" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>1137</v>
+        <v>1152</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>1138</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="9" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>1139</v>
+        <v>1154</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>1140</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="10" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>1141</v>
+        <v>1156</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>1142</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="11" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>1143</v>
+        <v>1158</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>1144</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="12" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>1145</v>
+        <v>1160</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>1146</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="13" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>1147</v>
+        <v>1162</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>1148</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="14" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>1149</v>
+        <v>1164</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>1150</v>
+        <v>1165</v>
       </c>
     </row>
   </sheetData>
@@ -13372,7 +13417,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:E122"/>
+  <dimension ref="A1:F122"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.453125"/>
   <cols>
     <col min="1" max="1" width="14.01" style="1" customWidth="1"/>
@@ -13380,7 +13425,7 @@
     <col min="3" max="3" width="10.01" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" ht="18.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>435</v>
       </c>
@@ -13395,6 +13440,9 @@
       </c>
       <c r="E1" t="s">
         <v>686</v>
+      </c>
+      <c r="F1" t="s">
+        <v>687</v>
       </c>
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -13405,7 +13453,7 @@
         <v>632</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="3" ht="18.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -13416,7 +13464,7 @@
         <v>636</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -13438,7 +13486,7 @@
         <v>636</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="6" ht="18.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -13460,7 +13508,7 @@
         <v>644</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
     </row>
     <row r="8" ht="18.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -13471,7 +13519,7 @@
         <v>644</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="9" ht="18.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -13482,7 +13530,7 @@
         <v>644</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
     </row>
     <row r="10" ht="18.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -13493,7 +13541,7 @@
         <v>632</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="11" ht="18.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -13504,7 +13552,7 @@
         <v>636</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
     </row>
     <row r="12" ht="18.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -13958,10 +14006,10 @@
         <v>1</v>
       </c>
       <c r="D52" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="E52" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
     </row>
     <row r="53" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -13975,10 +14023,10 @@
         <v>2</v>
       </c>
       <c r="D53" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="E53" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="54" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -13992,10 +14040,10 @@
         <v>3</v>
       </c>
       <c r="D54" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="E54" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
     </row>
     <row r="55" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -14009,10 +14057,10 @@
         <v>4</v>
       </c>
       <c r="D55" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="E55" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="56" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -14026,10 +14074,10 @@
         <v>5</v>
       </c>
       <c r="D56" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="E56" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
     </row>
     <row r="57" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -14043,10 +14091,10 @@
         <v>1</v>
       </c>
       <c r="D57" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="E57" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -14060,10 +14108,10 @@
         <v>2</v>
       </c>
       <c r="D58" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="E58" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="59" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -14077,10 +14125,10 @@
         <v>3</v>
       </c>
       <c r="D59" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="E59" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
     </row>
     <row r="60" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -14094,10 +14142,10 @@
         <v>4</v>
       </c>
       <c r="D60" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="E60" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
     </row>
     <row r="61" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -14111,10 +14159,10 @@
         <v>5</v>
       </c>
       <c r="D61" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="E61" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
     </row>
     <row r="62" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -14128,10 +14176,10 @@
         <v>6</v>
       </c>
       <c r="D62" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="E62" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
     </row>
     <row r="63" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -14145,10 +14193,10 @@
         <v>1</v>
       </c>
       <c r="D63" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="E63" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
     </row>
     <row r="64" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -14162,10 +14210,10 @@
         <v>2</v>
       </c>
       <c r="D64" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="E64" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
     </row>
     <row r="65" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -14179,10 +14227,10 @@
         <v>3</v>
       </c>
       <c r="D65" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="E65" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
     </row>
     <row r="66" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -14196,10 +14244,10 @@
         <v>4</v>
       </c>
       <c r="D66" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="E66" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -14213,10 +14261,10 @@
         <v>5</v>
       </c>
       <c r="D67" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="E67" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
     </row>
     <row r="68" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -14230,10 +14278,10 @@
         <v>6</v>
       </c>
       <c r="D68" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="E68" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -14247,10 +14295,10 @@
         <v>7</v>
       </c>
       <c r="D69" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="E69" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -14264,10 +14312,10 @@
         <v>1</v>
       </c>
       <c r="D70" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="E70" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -14281,10 +14329,10 @@
         <v>2</v>
       </c>
       <c r="D71" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="E71" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -14298,10 +14346,10 @@
         <v>3</v>
       </c>
       <c r="D72" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="E72" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -14315,10 +14363,10 @@
         <v>4</v>
       </c>
       <c r="D73" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="E73" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="74" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -14332,10 +14380,10 @@
         <v>5</v>
       </c>
       <c r="D74" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="E74" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -14349,10 +14397,10 @@
         <v>6</v>
       </c>
       <c r="D75" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="E75" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
     </row>
     <row r="76" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -14366,10 +14414,10 @@
         <v>1</v>
       </c>
       <c r="D76" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="E76" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
     </row>
     <row r="77" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -14383,10 +14431,10 @@
         <v>2</v>
       </c>
       <c r="D77" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="E77" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
     </row>
     <row r="78" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -14400,10 +14448,10 @@
         <v>3</v>
       </c>
       <c r="D78" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="E78" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -14417,10 +14465,10 @@
         <v>4</v>
       </c>
       <c r="D79" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="E79" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -14434,10 +14482,10 @@
         <v>5</v>
       </c>
       <c r="D80" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="E80" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -14451,10 +14499,10 @@
         <v>1</v>
       </c>
       <c r="D81" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="E81" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -14468,10 +14516,10 @@
         <v>2</v>
       </c>
       <c r="D82" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="E82" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -14485,10 +14533,10 @@
         <v>3</v>
       </c>
       <c r="D83" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="E83" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="84" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -14502,10 +14550,10 @@
         <v>4</v>
       </c>
       <c r="D84" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="E84" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -14519,10 +14567,10 @@
         <v>5</v>
       </c>
       <c r="D85" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="E85" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -14536,10 +14584,10 @@
         <v>1</v>
       </c>
       <c r="D86" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="E86" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -14553,10 +14601,10 @@
         <v>2</v>
       </c>
       <c r="D87" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="E87" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
     </row>
     <row r="88" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -14570,10 +14618,10 @@
         <v>3</v>
       </c>
       <c r="D88" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="E88" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
     </row>
     <row r="89" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -14587,10 +14635,10 @@
         <v>4</v>
       </c>
       <c r="D89" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="E89" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
     </row>
     <row r="90" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -14604,10 +14652,10 @@
         <v>5</v>
       </c>
       <c r="D90" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="E90" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
     </row>
     <row r="91" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -14621,10 +14669,10 @@
         <v>1</v>
       </c>
       <c r="D91" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="E91" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
     </row>
     <row r="92" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -14638,10 +14686,10 @@
         <v>2</v>
       </c>
       <c r="D92" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="E92" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
     </row>
     <row r="93" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -14655,10 +14703,10 @@
         <v>3</v>
       </c>
       <c r="D93" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E93" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
     </row>
     <row r="94" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -14672,10 +14720,10 @@
         <v>4</v>
       </c>
       <c r="D94" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="E94" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
     </row>
     <row r="95" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -14689,10 +14737,10 @@
         <v>5</v>
       </c>
       <c r="D95" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="E95" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
     </row>
     <row r="96" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -14706,10 +14754,10 @@
         <v>6</v>
       </c>
       <c r="D96" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="E96" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
     </row>
     <row r="97" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -14723,10 +14771,10 @@
         <v>1</v>
       </c>
       <c r="D97" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="E97" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
     </row>
     <row r="98" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -14740,10 +14788,10 @@
         <v>2</v>
       </c>
       <c r="D98" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="E98" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
     </row>
     <row r="99" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -14757,66 +14805,231 @@
         <v>3</v>
       </c>
       <c r="D99" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="E99" t="s">
-        <v>776</v>
-      </c>
-    </row>
-    <row r="100" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A100" s="1"/>
-      <c r="B100" s="1"/>
-      <c r="C100" s="1"/>
-    </row>
-    <row r="101" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A101" s="1"/>
-      <c r="B101" s="1"/>
-      <c r="C101" s="1"/>
-    </row>
-    <row r="102" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A102" s="1"/>
-      <c r="B102" s="1"/>
-      <c r="C102" s="1"/>
-    </row>
-    <row r="103" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A103" s="1"/>
-      <c r="B103" s="1"/>
-      <c r="C103" s="1"/>
-    </row>
-    <row r="104" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A104" s="1"/>
-      <c r="B104" s="1"/>
-      <c r="C104" s="1"/>
-    </row>
-    <row r="105" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A105" s="1"/>
-      <c r="B105" s="1"/>
-      <c r="C105" s="1"/>
-    </row>
-    <row r="106" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A106" s="1"/>
-      <c r="B106" s="1"/>
-      <c r="C106" s="1"/>
-    </row>
-    <row r="107" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A107" s="1"/>
-      <c r="B107" s="1"/>
-      <c r="C107" s="1"/>
-    </row>
-    <row r="108" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A108" s="1"/>
-      <c r="B108" s="1"/>
-      <c r="C108" s="1"/>
-    </row>
-    <row r="109" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A109" s="1"/>
-      <c r="B109" s="1"/>
-      <c r="C109" s="1"/>
-    </row>
-    <row r="110" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A110" s="1"/>
-      <c r="B110" s="1"/>
-      <c r="C110" s="1"/>
+        <v>777</v>
+      </c>
+    </row>
+    <row r="100" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A100" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>636</v>
+      </c>
+      <c r="C100" s="1">
+        <v>1</v>
+      </c>
+      <c r="D100" t="s">
+        <v>778</v>
+      </c>
+      <c r="E100" t="s">
+        <v>779</v>
+      </c>
+      <c r="F100" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="101" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A101" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>636</v>
+      </c>
+      <c r="C101" s="1">
+        <v>2</v>
+      </c>
+      <c r="D101" t="s">
+        <v>781</v>
+      </c>
+      <c r="E101" t="s">
+        <v>779</v>
+      </c>
+      <c r="F101" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="102" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A102" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>636</v>
+      </c>
+      <c r="C102" s="1">
+        <v>3</v>
+      </c>
+      <c r="D102" t="s">
+        <v>783</v>
+      </c>
+      <c r="E102" t="s">
+        <v>779</v>
+      </c>
+      <c r="F102" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="103" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A103" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>636</v>
+      </c>
+      <c r="C103" s="1">
+        <v>4</v>
+      </c>
+      <c r="D103" t="s">
+        <v>785</v>
+      </c>
+      <c r="E103" t="s">
+        <v>779</v>
+      </c>
+      <c r="F103" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="104" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A104" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>636</v>
+      </c>
+      <c r="C104" s="1">
+        <v>5</v>
+      </c>
+      <c r="D104" t="s">
+        <v>786</v>
+      </c>
+      <c r="E104" t="s">
+        <v>779</v>
+      </c>
+      <c r="F104" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="105" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A105" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>636</v>
+      </c>
+      <c r="C105" s="1">
+        <v>6</v>
+      </c>
+      <c r="D105" t="s">
+        <v>787</v>
+      </c>
+      <c r="E105" t="s">
+        <v>779</v>
+      </c>
+      <c r="F105" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="106" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A106" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>636</v>
+      </c>
+      <c r="C106" s="1">
+        <v>7</v>
+      </c>
+      <c r="D106" t="s">
+        <v>788</v>
+      </c>
+      <c r="E106" t="s">
+        <v>779</v>
+      </c>
+      <c r="F106" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="107" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A107" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>636</v>
+      </c>
+      <c r="C107" s="1">
+        <v>8</v>
+      </c>
+      <c r="D107" t="s">
+        <v>789</v>
+      </c>
+      <c r="E107" t="s">
+        <v>779</v>
+      </c>
+      <c r="F107" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="108" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A108" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>636</v>
+      </c>
+      <c r="C108" s="1">
+        <v>9</v>
+      </c>
+      <c r="D108" t="s">
+        <v>790</v>
+      </c>
+      <c r="E108" t="s">
+        <v>779</v>
+      </c>
+      <c r="F108" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="109" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A109" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>636</v>
+      </c>
+      <c r="C109" s="1">
+        <v>10</v>
+      </c>
+      <c r="D109" t="s">
+        <v>791</v>
+      </c>
+      <c r="E109" t="s">
+        <v>779</v>
+      </c>
+      <c r="F109" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="110" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A110" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>636</v>
+      </c>
+      <c r="C110" s="1">
+        <v>11</v>
+      </c>
+      <c r="D110" t="s">
+        <v>792</v>
+      </c>
+      <c r="E110" t="s">
+        <v>779</v>
+      </c>
+      <c r="F110" t="s">
+        <v>784</v>
+      </c>
     </row>
     <row r="111" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" s="1"/>
@@ -14901,16 +15114,16 @@
         <v>435</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>777</v>
+        <v>793</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>778</v>
+        <v>794</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>779</v>
+        <v>795</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>780</v>
+        <v>796</v>
       </c>
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -15020,21 +15233,21 @@
         <v>196</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>781</v>
+        <v>797</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>782</v>
+        <v>798</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>783</v>
+        <v>799</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>784</v>
+        <v>800</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>785</v>
+        <v>801</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>136</v>
@@ -15054,10 +15267,10 @@
         <v>220</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>786</v>
+        <v>802</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>787</v>
+        <v>803</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>455</v>
@@ -15068,10 +15281,10 @@
         <v>230</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>788</v>
+        <v>804</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>789</v>
+        <v>805</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>472</v>
@@ -15082,13 +15295,13 @@
         <v>248</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>790</v>
+        <v>806</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>791</v>
+        <v>807</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>792</v>
+        <v>808</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -15096,16 +15309,16 @@
         <v>261</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>793</v>
+        <v>809</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>794</v>
+        <v>810</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>795</v>
+        <v>811</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>796</v>
+        <v>812</v>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -15113,10 +15326,10 @@
         <v>271</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>797</v>
+        <v>813</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>798</v>
+        <v>814</v>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -15124,7 +15337,7 @@
         <v>279</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>799</v>
+        <v>815</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>547</v>
@@ -15135,13 +15348,13 @@
         <v>289</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>800</v>
+        <v>816</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>801</v>
+        <v>817</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>802</v>
+        <v>818</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>557</v>
@@ -15160,10 +15373,10 @@
         <v>309</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>803</v>
+        <v>819</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>804</v>
+        <v>820</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -15171,7 +15384,7 @@
         <v>351</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>805</v>
+        <v>821</v>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -15179,7 +15392,7 @@
         <v>379</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>806</v>
+        <v>822</v>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -15187,7 +15400,7 @@
         <v>388</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>807</v>
+        <v>823</v>
       </c>
     </row>
   </sheetData>

--- a/MAX-SEAL-main/catalog/MAXSEAL_CATALOG.xlsx
+++ b/MAX-SEAL-main/catalog/MAXSEAL_CATALOG.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2861" uniqueCount="1201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2877" uniqueCount="1228">
   <si>
     <t>Id</t>
   </si>
@@ -2844,10 +2844,13 @@
     <t>hp-series</t>
   </si>
   <si>
-    <t>High Performance Series Catalog (501-24 High Performance Series_v02 COMPRESSED.pdf)</t>
-  </si>
-  <si>
-    <t>/assets/maxseal/docs/501-24 High Performance Series_v02 COMPRESSED.pdf</t>
+    <t>High Performance Series Catalog (501-24 High Performance Series_v03.pdf)</t>
+  </si>
+  <si>
+    <t>4.0 MB</t>
+  </si>
+  <si>
+    <t>/assets/maxseal/docs/501-24 High Performance Series_v03.pdf</t>
   </si>
   <si>
     <t>d16</t>
@@ -3516,6 +3519,18 @@
     <t>View 3</t>
   </si>
   <si>
+    <t>/assets/maxseal/products/Series 52DF Large Angle.png</t>
+  </si>
+  <si>
+    <t>Large – Angle</t>
+  </si>
+  <si>
+    <t>/assets/maxseal/products/Series 52DF Large Front.png</t>
+  </si>
+  <si>
+    <t>Large – Front</t>
+  </si>
+  <si>
     <t>/assets/maxseal/products/Hayward BYV Series Butterfly Valve Angle.png</t>
   </si>
   <si>
@@ -3556,6 +3571,72 @@
   </si>
   <si>
     <t>/assets/maxseal/products/Chem-Flo Series Ball Valve.png</t>
+  </si>
+  <si>
+    <t>/assets/maxseal/products/Performance Series Handle.png</t>
+  </si>
+  <si>
+    <t>With Handle</t>
+  </si>
+  <si>
+    <t>/assets/maxseal/products/Performance Series Cutaway.png</t>
+  </si>
+  <si>
+    <t>Cutaway</t>
+  </si>
+  <si>
+    <t>/assets/maxseal/products/Performance Series 6in Bare.png</t>
+  </si>
+  <si>
+    <t>6" Bare</t>
+  </si>
+  <si>
+    <t>/assets/maxseal/products/Chem-Tek Series Bare.png</t>
+  </si>
+  <si>
+    <t>Bare Valve</t>
+  </si>
+  <si>
+    <t>/assets/maxseal/products/Chem-Tek Series Actuated.png</t>
+  </si>
+  <si>
+    <t>Actuated</t>
+  </si>
+  <si>
+    <t>/assets/maxseal/products/Chem-Tek Series Top Works.png</t>
+  </si>
+  <si>
+    <t>/assets/maxseal/products/HP Series Double Offset Actuated.jpg</t>
+  </si>
+  <si>
+    <t>/assets/maxseal/products/HP Series Lug Scotch Yoke.jpg</t>
+  </si>
+  <si>
+    <t>Scotch Yoke</t>
+  </si>
+  <si>
+    <t>/assets/maxseal/products/HP Series Actuated Lineup.png</t>
+  </si>
+  <si>
+    <t>Lineup</t>
+  </si>
+  <si>
+    <t>/assets/maxseal/products/Hi-Tek Series Actuated.png</t>
+  </si>
+  <si>
+    <t>/assets/maxseal/products/Hi-Tek Series Stainless Gear Operated.png</t>
+  </si>
+  <si>
+    <t>Stainless</t>
+  </si>
+  <si>
+    <t>/assets/maxseal/products/Hi-Tek Series Scotch Yoke.png</t>
+  </si>
+  <si>
+    <t>/assets/maxseal/products/Hi-Tek Series AirCon Actuated.png</t>
+  </si>
+  <si>
+    <t>AirCon Actuated</t>
   </si>
   <si>
     <t>Section</t>
@@ -4636,10 +4717,12 @@
       </c>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
+      <c r="H16" s="1" t="s">
+        <v>936</v>
+      </c>
       <c r="I16" s="1"/>
       <c r="J16" s="1" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="K16" s="1"/>
       <c r="L16" t="s">
@@ -4648,16 +4731,16 @@
     </row>
     <row r="17" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>853</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>281</v>
@@ -4667,7 +4750,7 @@
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="K17" s="1"/>
       <c r="L17" t="s">
@@ -4676,16 +4759,16 @@
     </row>
     <row r="18" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>853</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>289</v>
@@ -4695,7 +4778,7 @@
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
       <c r="J18" s="1" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="K18" s="1"/>
       <c r="L18" t="s">
@@ -4704,16 +4787,16 @@
     </row>
     <row r="19" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>853</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>299</v>
@@ -4723,7 +4806,7 @@
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
       <c r="J19" s="1" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="K19" s="1"/>
       <c r="L19" t="s">
@@ -4732,16 +4815,16 @@
     </row>
     <row r="20" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>853</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>310</v>
@@ -4751,7 +4834,7 @@
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="K20" s="1"/>
       <c r="L20" t="s">
@@ -4760,16 +4843,16 @@
     </row>
     <row r="21" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>853</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>319</v>
@@ -4779,7 +4862,7 @@
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="K21" s="1"/>
       <c r="L21" t="s">
@@ -4788,16 +4871,16 @@
     </row>
     <row r="22" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>853</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>250</v>
@@ -4807,7 +4890,7 @@
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="K22" s="1"/>
       <c r="L22" t="s">
@@ -4816,16 +4899,16 @@
     </row>
     <row r="23" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>853</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>206</v>
@@ -4837,7 +4920,7 @@
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="K23" s="1"/>
       <c r="L23" t="s">
@@ -4846,16 +4929,16 @@
     </row>
     <row r="24" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>853</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>206</v>
@@ -4863,11 +4946,11 @@
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
       <c r="H24" s="1" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="I24" s="1"/>
       <c r="J24" s="1" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="K24" s="1"/>
       <c r="L24" t="s">
@@ -4876,28 +4959,28 @@
     </row>
     <row r="25" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>853</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>354</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="K25" s="1"/>
       <c r="L25" t="s">
@@ -4906,28 +4989,28 @@
     </row>
     <row r="26" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>853</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>361</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="K26" s="1"/>
       <c r="L26" t="s">
@@ -4936,28 +5019,28 @@
     </row>
     <row r="27" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>853</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>425</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="K27" s="1"/>
       <c r="L27" t="s">
@@ -4966,30 +5049,30 @@
     </row>
     <row r="28" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>853</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>902</v>
       </c>
       <c r="F28" s="1"/>
       <c r="G28" s="1" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="I28" s="1"/>
       <c r="J28" s="1" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="K28" s="1"/>
       <c r="L28" t="s">
@@ -4998,16 +5081,16 @@
     </row>
     <row r="29" ht="15" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>230</v>
@@ -5019,13 +5102,13 @@
         <v>104</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="I29" s="1" t="s">
         <v>104</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="K29" s="1" t="s">
         <v>104</v>
@@ -5039,16 +5122,16 @@
     </row>
     <row r="30" ht="15" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>902</v>
@@ -5060,13 +5143,13 @@
         <v>104</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="I30" s="1" t="s">
         <v>104</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="K30" s="1" t="s">
         <v>104</v>
@@ -5080,16 +5163,16 @@
     </row>
     <row r="31" ht="15" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>895</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>230</v>
@@ -5101,13 +5184,13 @@
         <v>104</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="I31" s="1" t="s">
         <v>104</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="K31" s="1" t="s">
         <v>104</v>
@@ -5121,16 +5204,16 @@
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>853</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>195</v>
@@ -5148,7 +5231,7 @@
         <v>104</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="K32" s="1" t="s">
         <v>104</v>
@@ -5162,16 +5245,16 @@
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>895</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>902</v>
@@ -5183,13 +5266,13 @@
         <v>104</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="I33" s="1" t="s">
         <v>104</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="K33" s="1" t="s">
         <v>104</v>
@@ -5203,16 +5286,16 @@
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>882</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>902</v>
@@ -5224,13 +5307,13 @@
         <v>104</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="I34" s="1" t="s">
         <v>104</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="K34" s="1" t="s">
         <v>104</v>
@@ -5244,16 +5327,16 @@
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>902</v>
@@ -5271,7 +5354,7 @@
         <v>104</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="K35" s="1" t="s">
         <v>104</v>
@@ -5356,16 +5439,16 @@
         <v>445</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="H1" s="4" t="s">
         <v>846</v>
@@ -5386,60 +5469,60 @@
     </row>
     <row r="3" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>902</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="I3" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>902</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="I4" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
     </row>
   </sheetData>
@@ -5478,63 +5561,63 @@
         <v>447</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="G1" s="4" t="s">
         <v>847</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="K1" s="4" t="s">
         <v>845</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>853</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="H2" s="6" t="s">
         <v>32</v>
@@ -5542,22 +5625,22 @@
     </row>
     <row r="3" ht="18.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="K3" s="6" t="s">
         <v>864</v>
@@ -5565,25 +5648,25 @@
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="L4" s="6" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="M4" s="6" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="N4" s="6" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
     </row>
   </sheetData>
@@ -5610,7 +5693,7 @@
         <v>445</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>6</v>
@@ -6530,45 +6613,45 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="G2" s="6" t="s">
         <v>128</v>
@@ -6576,22 +6659,22 @@
     </row>
     <row r="3" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>41</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="G3" s="6" t="s">
         <v>144</v>
@@ -6599,22 +6682,22 @@
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="G4" s="6" t="s">
         <v>157</v>
@@ -6622,22 +6705,22 @@
     </row>
     <row r="5" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="G5" s="6" t="s">
         <v>167</v>
@@ -6645,22 +6728,22 @@
     </row>
     <row r="6" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>180</v>
@@ -6668,22 +6751,22 @@
     </row>
     <row r="7" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="G7" s="6" t="s">
         <v>195</v>
@@ -6691,22 +6774,22 @@
     </row>
     <row r="8" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>206</v>
@@ -6714,22 +6797,22 @@
     </row>
     <row r="9" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>653</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>651</v>
@@ -6737,22 +6820,22 @@
     </row>
     <row r="10" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>657</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="G10" s="6" t="s">
         <v>655</v>
@@ -6760,22 +6843,22 @@
     </row>
     <row r="11" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>661</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="G11" s="6" t="s">
         <v>659</v>
@@ -6783,22 +6866,22 @@
     </row>
     <row r="12" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>665</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="G12" s="6" t="s">
         <v>663</v>
@@ -6806,22 +6889,22 @@
     </row>
     <row r="13" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>669</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="G13" s="6" t="s">
         <v>667</v>
@@ -6829,22 +6912,22 @@
     </row>
     <row r="14" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>673</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="G14" s="6" t="s">
         <v>671</v>
@@ -6852,22 +6935,22 @@
     </row>
     <row r="15" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>677</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="G15" s="6" t="s">
         <v>675</v>
@@ -6875,22 +6958,22 @@
     </row>
     <row r="16" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>681</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="G16" s="6" t="s">
         <v>679</v>
@@ -6898,22 +6981,22 @@
     </row>
     <row r="17" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>685</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="G17" s="6" t="s">
         <v>683</v>
@@ -6921,22 +7004,22 @@
     </row>
     <row r="18" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>689</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="G18" s="6" t="s">
         <v>687</v>
@@ -6944,22 +7027,22 @@
     </row>
     <row r="19" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>693</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="G19" s="6" t="s">
         <v>691</v>
@@ -6967,22 +7050,22 @@
     </row>
     <row r="20" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>697</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="G20" s="6" t="s">
         <v>695</v>
@@ -6990,22 +7073,22 @@
     </row>
     <row r="21" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>701</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="G21" s="6" t="s">
         <v>699</v>
@@ -7013,45 +7096,45 @@
     </row>
     <row r="22" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="23" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>859</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="G23" s="6" t="s">
         <v>852</v>
@@ -7059,22 +7142,22 @@
     </row>
     <row r="24" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>860</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="G24" s="6" t="s">
         <v>852</v>
@@ -7091,7 +7174,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:D75"/>
+  <dimension ref="A1:D80"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.453125"/>
   <cols>
     <col min="1" max="1" width="14.01" style="1" customWidth="1"/>
@@ -7122,7 +7205,7 @@
         <v>35</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -7136,7 +7219,7 @@
         <v>35</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
@@ -7150,7 +7233,7 @@
         <v>35</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -7164,7 +7247,7 @@
         <v>41</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="D5" s="1">
         <v>1</v>
@@ -7178,7 +7261,7 @@
         <v>41</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="D6" s="1">
         <v>2</v>
@@ -7192,7 +7275,7 @@
         <v>41</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -7206,7 +7289,7 @@
         <v>46</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="D8" s="1">
         <v>1</v>
@@ -7217,10 +7300,10 @@
         <v>157</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>46</v>
+        <v>1160</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>1157</v>
+        <v>1161</v>
       </c>
       <c r="D9" s="1">
         <v>2</v>
@@ -7231,10 +7314,10 @@
         <v>157</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>46</v>
+        <v>1162</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>1158</v>
+        <v>1163</v>
       </c>
       <c r="D10" s="1">
         <v>3</v>
@@ -7248,7 +7331,7 @@
         <v>50</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
@@ -7262,7 +7345,7 @@
         <v>50</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="D12" s="1">
         <v>2</v>
@@ -7276,7 +7359,7 @@
         <v>50</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="D13" s="1">
         <v>3</v>
@@ -7290,7 +7373,7 @@
         <v>54</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="D14" s="1">
         <v>1</v>
@@ -7301,10 +7384,10 @@
         <v>180</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>1159</v>
+        <v>1164</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>1160</v>
+        <v>1165</v>
       </c>
       <c r="D15" s="1">
         <v>2</v>
@@ -7315,10 +7398,10 @@
         <v>180</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>1161</v>
+        <v>1166</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>1162</v>
+        <v>1167</v>
       </c>
       <c r="D16" s="1">
         <v>3</v>
@@ -7332,7 +7415,7 @@
         <v>58</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
@@ -7343,10 +7426,10 @@
         <v>195</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>1163</v>
+        <v>1168</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>1160</v>
+        <v>1165</v>
       </c>
       <c r="D18" s="1">
         <v>2</v>
@@ -7357,10 +7440,10 @@
         <v>195</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>1164</v>
+        <v>1169</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>1165</v>
+        <v>1170</v>
       </c>
       <c r="D19" s="1">
         <v>3</v>
@@ -7371,10 +7454,10 @@
         <v>195</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>1166</v>
+        <v>1171</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>1167</v>
+        <v>1172</v>
       </c>
       <c r="D20" s="1">
         <v>4</v>
@@ -7388,7 +7471,7 @@
         <v>63</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="D21" s="1">
         <v>1</v>
@@ -7399,10 +7482,10 @@
         <v>206</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>1168</v>
+        <v>1173</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>1169</v>
+        <v>1174</v>
       </c>
       <c r="D22" s="1">
         <v>2</v>
@@ -7413,10 +7496,10 @@
         <v>206</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>1170</v>
+        <v>1175</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>1171</v>
+        <v>1176</v>
       </c>
       <c r="D23" s="1">
         <v>3</v>
@@ -7427,7 +7510,7 @@
         <v>206</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>1172</v>
+        <v>1177</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>821</v>
@@ -7444,7 +7527,7 @@
         <v>66</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="D25" s="1">
         <v>1</v>
@@ -7458,7 +7541,7 @@
         <v>66</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="D26" s="1">
         <v>2</v>
@@ -7472,7 +7555,7 @@
         <v>66</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="D27" s="1">
         <v>3</v>
@@ -7486,7 +7569,7 @@
         <v>237</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="D28" s="1">
         <v>1</v>
@@ -7497,10 +7580,10 @@
         <v>230</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>237</v>
+        <v>1178</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>1157</v>
+        <v>1179</v>
       </c>
       <c r="D29" s="1">
         <v>2</v>
@@ -7511,10 +7594,10 @@
         <v>230</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>237</v>
+        <v>1180</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>1158</v>
+        <v>1181</v>
       </c>
       <c r="D30" s="1">
         <v>3</v>
@@ -7522,16 +7605,16 @@
     </row>
     <row r="31" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>247</v>
+        <v>1182</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>1156</v>
+        <v>1183</v>
       </c>
       <c r="D31" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -7545,7 +7628,7 @@
         <v>1157</v>
       </c>
       <c r="D32" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -7559,21 +7642,21 @@
         <v>1158</v>
       </c>
       <c r="D33" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>1156</v>
+        <v>1159</v>
       </c>
       <c r="D34" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -7587,7 +7670,7 @@
         <v>1157</v>
       </c>
       <c r="D35" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -7601,21 +7684,21 @@
         <v>1158</v>
       </c>
       <c r="D36" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>1156</v>
+        <v>1159</v>
       </c>
       <c r="D37" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -7629,7 +7712,7 @@
         <v>1157</v>
       </c>
       <c r="D38" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -7637,41 +7720,41 @@
         <v>258</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>265</v>
+        <v>1184</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>1158</v>
+        <v>1185</v>
       </c>
       <c r="D39" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>278</v>
+        <v>1186</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>1156</v>
+        <v>1187</v>
       </c>
       <c r="D40" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>278</v>
+        <v>1188</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>1157</v>
+        <v>1172</v>
       </c>
       <c r="D41" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -7682,63 +7765,63 @@
         <v>278</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="D42" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>288</v>
+        <v>1189</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>1156</v>
+        <v>1187</v>
       </c>
       <c r="D43" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>288</v>
+        <v>1190</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>1157</v>
+        <v>1191</v>
       </c>
       <c r="D44" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>288</v>
+        <v>1192</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>1158</v>
+        <v>1193</v>
       </c>
       <c r="D45" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="D46" s="1">
         <v>1</v>
@@ -7746,13 +7829,13 @@
     </row>
     <row r="47" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="D47" s="1">
         <v>2</v>
@@ -7760,13 +7843,13 @@
     </row>
     <row r="48" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="D48" s="1">
         <v>3</v>
@@ -7774,13 +7857,13 @@
     </row>
     <row r="49" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="D49" s="1">
         <v>1</v>
@@ -7788,13 +7871,13 @@
     </row>
     <row r="50" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>306</v>
+        <v>1194</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>1157</v>
+        <v>1187</v>
       </c>
       <c r="D50" s="1">
         <v>2</v>
@@ -7802,13 +7885,13 @@
     </row>
     <row r="51" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>306</v>
+        <v>1195</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>1158</v>
+        <v>1196</v>
       </c>
       <c r="D51" s="1">
         <v>3</v>
@@ -7816,337 +7899,407 @@
     </row>
     <row r="52" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>310</v>
+        <v>289</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>317</v>
+        <v>1197</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>1156</v>
+        <v>1191</v>
       </c>
       <c r="D52" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>310</v>
+        <v>289</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>317</v>
+        <v>1198</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>1157</v>
+        <v>1199</v>
       </c>
       <c r="D53" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>310</v>
+        <v>299</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>317</v>
+        <v>306</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="D54" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>319</v>
+        <v>299</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>41</v>
+        <v>306</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="D55" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>319</v>
+        <v>299</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>41</v>
+        <v>306</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="D56" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>41</v>
+        <v>317</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="D57" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>331</v>
+        <v>310</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>72</v>
+        <v>317</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="D58" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>331</v>
+        <v>310</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>72</v>
+        <v>317</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="D59" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>72</v>
+        <v>41</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="D60" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>340</v>
+        <v>319</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>76</v>
+        <v>41</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="D61" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>340</v>
+        <v>319</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>76</v>
+        <v>41</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="D62" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="63" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="D63" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>354</v>
+        <v>331</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="D64" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>354</v>
+        <v>331</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="D65" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>354</v>
+        <v>340</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="D66" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>361</v>
+        <v>340</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="D67" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>361</v>
+        <v>340</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="D68" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="D69" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>371</v>
+        <v>354</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="D70" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>371</v>
+        <v>354</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="D71" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="D72" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>379</v>
+        <v>361</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>27</v>
+        <v>84</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="D73" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>379</v>
+        <v>361</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>27</v>
+        <v>84</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="D74" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>1157</v>
+      </c>
+      <c r="D75" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>1158</v>
+      </c>
+      <c r="D76" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="77" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>1159</v>
+      </c>
+      <c r="D77" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="78" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="B75" s="1" t="s">
+      <c r="B78" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C75" s="1" t="s">
+      <c r="C78" s="1" t="s">
+        <v>1157</v>
+      </c>
+      <c r="D78" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C79" s="1" t="s">
         <v>1158</v>
       </c>
-      <c r="D75" s="1">
+      <c r="D79" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="80" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>1159</v>
+      </c>
+      <c r="D80" s="1">
         <v>3</v>
       </c>
     </row>
@@ -8170,114 +8323,114 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>1173</v>
+        <v>1200</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>1174</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>1175</v>
+        <v>1202</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>1176</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="3" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>1177</v>
+        <v>1204</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>1178</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>1179</v>
+        <v>1206</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>1180</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="5" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>1181</v>
+        <v>1208</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>1182</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="6" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>1183</v>
+        <v>1210</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>1184</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="7" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>1185</v>
+        <v>1212</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>1186</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="8" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>1187</v>
+        <v>1214</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>1188</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="9" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>1189</v>
+        <v>1216</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>1190</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="10" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>1191</v>
+        <v>1218</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>1192</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="11" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>1193</v>
+        <v>1220</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>1194</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="12" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>1195</v>
+        <v>1222</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>1196</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="13" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>1197</v>
+        <v>1224</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>1198</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="14" ht="18.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>1199</v>
+        <v>1226</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>1200</v>
+        <v>1227</v>
       </c>
     </row>
   </sheetData>

--- a/MAX-SEAL-main/catalog/MAXSEAL_CATALOG.xlsx
+++ b/MAX-SEAL-main/catalog/MAXSEAL_CATALOG.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3146" uniqueCount="1394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3128" uniqueCount="1394">
   <si>
     <t>Id</t>
   </si>
@@ -3090,7 +3090,7 @@
     <t>Mounting / Manual Override Catalog (150-22 Easy Link for Max-Seal Compressed.pdf)</t>
   </si>
   <si>
-    <t>PROD-026,PROD-027,PROD-028,PROD-029</t>
+    <t>PROD-026,PROD-027,PROD-028</t>
   </si>
   <si>
     <t>/assets/maxseal/docs/150-22 Easy Link for Max-Seal Compressed.pdf</t>
@@ -5364,7 +5364,7 @@
       </c>
       <c r="K21" s="1"/>
       <c r="L21" t="s">
-        <v>675</v>
+        <v>899</v>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -6334,7 +6334,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C82"/>
+  <dimension ref="A1:C73"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.453125"/>
   <cols>
     <col min="1" max="1" width="14.01" style="1" customWidth="1"/>
@@ -6586,13 +6586,13 @@
     </row>
     <row r="23" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>332</v>
-      </c>
       <c r="C23" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -6600,10 +6600,10 @@
         <v>290</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>280</v>
+        <v>302</v>
       </c>
       <c r="C24" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -6611,10 +6611,10 @@
         <v>290</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="C25" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -6622,32 +6622,32 @@
         <v>290</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>312</v>
+        <v>323</v>
       </c>
       <c r="C26" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>323</v>
+        <v>280</v>
       </c>
       <c r="C27" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="B28" s="1" t="s">
-        <v>332</v>
-      </c>
       <c r="C28" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -6655,10 +6655,10 @@
         <v>302</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>280</v>
+        <v>312</v>
       </c>
       <c r="C29" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -6666,43 +6666,43 @@
         <v>302</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>290</v>
+        <v>323</v>
       </c>
       <c r="C30" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>312</v>
+        <v>280</v>
       </c>
       <c r="C31" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>323</v>
+        <v>290</v>
       </c>
       <c r="C32" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="B33" s="1" t="s">
-        <v>332</v>
-      </c>
       <c r="C33" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -6710,59 +6710,59 @@
         <v>312</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>280</v>
+        <v>323</v>
       </c>
       <c r="C34" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>312</v>
+        <v>323</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="C35" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>312</v>
+        <v>323</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="C36" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>312</v>
+        <v>323</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>323</v>
+        <v>302</v>
       </c>
       <c r="C37" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="B38" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="B38" s="1" t="s">
-        <v>332</v>
-      </c>
       <c r="C38" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>280</v>
@@ -6773,7 +6773,7 @@
     </row>
     <row r="40" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>290</v>
@@ -6784,7 +6784,7 @@
     </row>
     <row r="41" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>302</v>
@@ -6795,7 +6795,7 @@
     </row>
     <row r="42" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>312</v>
@@ -6806,10 +6806,10 @@
     </row>
     <row r="43" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="B43" s="1" t="s">
         <v>323</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>332</v>
       </c>
       <c r="C43" s="1">
         <v>5</v>
@@ -6817,10 +6817,10 @@
     </row>
     <row r="44" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>332</v>
+        <v>227</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>280</v>
+        <v>215</v>
       </c>
       <c r="C44" s="1">
         <v>1</v>
@@ -6828,10 +6828,10 @@
     </row>
     <row r="45" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>332</v>
+        <v>227</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>290</v>
+        <v>204</v>
       </c>
       <c r="C45" s="1">
         <v>2</v>
@@ -6839,10 +6839,10 @@
     </row>
     <row r="46" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>332</v>
+        <v>227</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>302</v>
+        <v>189</v>
       </c>
       <c r="C46" s="1">
         <v>3</v>
@@ -6850,32 +6850,32 @@
     </row>
     <row r="47" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>332</v>
+        <v>353</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>312</v>
+        <v>394</v>
       </c>
       <c r="C47" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>332</v>
+        <v>353</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>323</v>
+        <v>386</v>
       </c>
       <c r="C48" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>227</v>
+        <v>375</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>215</v>
+        <v>394</v>
       </c>
       <c r="C49" s="1">
         <v>1</v>
@@ -6883,76 +6883,76 @@
     </row>
     <row r="50" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>227</v>
+        <v>375</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>204</v>
+        <v>353</v>
       </c>
       <c r="C50" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>227</v>
+        <v>386</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>189</v>
+        <v>394</v>
       </c>
       <c r="C51" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="B52" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="B52" s="1" t="s">
-        <v>394</v>
-      </c>
       <c r="C52" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="B53" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="B53" s="1" t="s">
-        <v>386</v>
-      </c>
       <c r="C53" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="B54" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="B54" s="1" t="s">
-        <v>394</v>
-      </c>
       <c r="C54" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>375</v>
+        <v>394</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>353</v>
+        <v>386</v>
       </c>
       <c r="C55" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="56" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>386</v>
+        <v>375</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>394</v>
+        <v>404</v>
       </c>
       <c r="C56" s="1">
         <v>1</v>
@@ -6960,10 +6960,10 @@
     </row>
     <row r="57" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>386</v>
+        <v>375</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>353</v>
+        <v>414</v>
       </c>
       <c r="C57" s="1">
         <v>2</v>
@@ -6971,276 +6971,177 @@
     </row>
     <row r="58" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>394</v>
+        <v>375</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>353</v>
+        <v>424</v>
       </c>
       <c r="C58" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>394</v>
+        <v>404</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>375</v>
       </c>
       <c r="C59" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="60" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>394</v>
+        <v>404</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>386</v>
+        <v>414</v>
       </c>
       <c r="C60" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="61" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>375</v>
+        <v>404</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>404</v>
+        <v>424</v>
       </c>
       <c r="C61" s="1">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="62" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="B62" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="B62" s="1" t="s">
-        <v>414</v>
-      </c>
       <c r="C62" s="1">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="63" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>375</v>
+        <v>414</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>424</v>
+        <v>404</v>
       </c>
       <c r="C63" s="1">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="64" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>375</v>
+        <v>414</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>434</v>
+        <v>424</v>
       </c>
       <c r="C64" s="1">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="65" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>404</v>
+        <v>424</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>375</v>
       </c>
       <c r="C65" s="1">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="66" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="B66" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="B66" s="1" t="s">
-        <v>414</v>
-      </c>
       <c r="C66" s="1">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>404</v>
+        <v>424</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>424</v>
+        <v>414</v>
       </c>
       <c r="C67" s="1">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="68" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>404</v>
+        <v>434</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>434</v>
+        <v>375</v>
       </c>
       <c r="C68" s="1">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>414</v>
+        <v>434</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>375</v>
+        <v>404</v>
       </c>
       <c r="C69" s="1">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="B70" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="B70" s="1" t="s">
-        <v>404</v>
-      </c>
       <c r="C70" s="1">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>414</v>
+        <v>434</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>424</v>
       </c>
       <c r="C71" s="1">
-        <v>11</v>
+        <v>20</v>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>414</v>
+        <v>394</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>434</v>
+        <v>463</v>
       </c>
       <c r="C72" s="1">
-        <v>12</v>
+        <v>90</v>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>424</v>
+        <v>463</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>375</v>
+        <v>394</v>
       </c>
       <c r="C73" s="1">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="74" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A74" s="1" t="s">
-        <v>424</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="C74" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="75" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75" s="1" t="s">
-        <v>424</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="C75" s="1">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="76" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A76" s="1" t="s">
-        <v>424</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="C76" s="1">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="77" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>375</v>
-      </c>
-      <c r="C77" s="1">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="78" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="C78" s="1">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="79" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A79" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="C79" s="1">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="80" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>424</v>
-      </c>
-      <c r="C80" s="1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="81" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="B81" s="1" t="s">
-        <v>463</v>
-      </c>
-      <c r="C81" s="1">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="82" ht="15" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" s="1" t="s">
-        <v>463</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="C82" s="1">
         <v>91</v>
       </c>
     </row>
@@ -11758,7 +11659,7 @@
         <v>152</v>
       </c>
       <c r="T19" s="1" t="s">
-        <v>12</v>
+        <v>67</v>
       </c>
       <c r="U19" s="1" t="b">
         <f>FALSE()</f>
@@ -12331,7 +12232,7 @@
         <v>442</v>
       </c>
       <c r="T29" s="1" t="s">
-        <v>12</v>
+        <v>67</v>
       </c>
       <c r="V29" s="2">
         <v>5</v>

--- a/MAX-SEAL-main/catalog/MAXSEAL_CATALOG.xlsx
+++ b/MAX-SEAL-main/catalog/MAXSEAL_CATALOG.xlsx
@@ -4065,13 +4065,13 @@
     <t>/assets/maxseal/products/automation/Filter Regulator.png</t>
   </si>
   <si>
-    <t>Filter Regulator</t>
+    <t>SMC AW20-N02C-2Z-A</t>
   </si>
   <si>
     <t>/assets/maxseal/products/automation/Filter Regulator with Gauge.png</t>
   </si>
   <si>
-    <t>With Gauge</t>
+    <t>SMC AW40-N04C-Z-A</t>
   </si>
   <si>
     <t>/assets/maxseal/products/automation/Couplers Set Screws.png</t>
